--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Deep_CBM_Knowledge_Base\00_Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3115A6B0-8F78-42DD-8E6C-B2F4C169565D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1912C42A-662A-4CDD-BDFE-1B9454C6A448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1644" yWindow="0" windowWidth="15372" windowHeight="12240" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="完整文献矩阵" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5767" uniqueCount="2787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5908" uniqueCount="2879">
   <si>
     <t>序号</t>
   </si>
@@ -8984,12 +8984,303 @@
   <si>
     <t>新增13篇基于官方题录/DOI初步核验；全文精读后可继续补充定量参数与局限性。</t>
   </si>
+  <si>
+    <t>DCBM-119</t>
+  </si>
+  <si>
+    <t>ZhiDi Liu</t>
+  </si>
+  <si>
+    <t>ZhiDi Liu; Duo Wang; Binrui Yang; Jidong Tang; Chengwang Wang; Wei Wang; Xinsi Hu; Jingnan Zhang</t>
+  </si>
+  <si>
+    <t>Evaluating deep coal rock gas fracturing sweet spot intervals using PSO-ELM algorithm and petrophysical logging data</t>
+  </si>
+  <si>
+    <t>基于 PSO-ELM 算法与岩石物理测井资料的深部煤岩气压裂甜点段评价</t>
+  </si>
+  <si>
+    <t>Early access article</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-026-54924-z</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-026-54924-z</t>
+  </si>
+  <si>
+    <t>Journal article</t>
+  </si>
+  <si>
+    <t>Ordos Basin; Daning-Jixian Block</t>
+  </si>
+  <si>
+    <t>Deep coal rock gas; No. 5 and No. 8 coal seams</t>
+  </si>
+  <si>
+    <t>深部煤岩气储层</t>
+  </si>
+  <si>
+    <t>识别深部煤岩气压裂甜点段</t>
+  </si>
+  <si>
+    <t>PSO-ELM、测井资料、10 个地质工程控制因素、甜点分级</t>
+  </si>
+  <si>
+    <t>X-11 井预测准确率超过 85%；I、II 类甜点段资源丰富</t>
+  </si>
+  <si>
+    <t>将 PSO-ELM 用于地质工程一体化压裂甜点评价</t>
+  </si>
+  <si>
+    <t>跨区块泛化需验证；机器学习可解释性需增强</t>
+  </si>
+  <si>
+    <t>可作为响应差异的地质工程背景变量参考</t>
+  </si>
+  <si>
+    <t>第二章；第三章；第五章</t>
+  </si>
+  <si>
+    <t>PSO-ELM; fracturing sweet spot; logging; geologic-engineering integration</t>
+  </si>
+  <si>
+    <t>Nature 页面、DOI、题名、作者、摘要已核验</t>
+  </si>
+  <si>
+    <t>DCBM-120</t>
+  </si>
+  <si>
+    <t>Hui Pan</t>
+  </si>
+  <si>
+    <t>Hui Pan; Wanjin Zhao; Mengbo Zhang; Run He; Guoliang Yan; Dongyang He</t>
+  </si>
+  <si>
+    <t>Prediction Methods for Gas-bearing Properties in Deep Coal Measures in the Ordos Basin</t>
+  </si>
+  <si>
+    <t>鄂尔多斯盆地深部煤系含气性预测方法</t>
+  </si>
+  <si>
+    <t>Journal of Geophysics and Engineering</t>
+  </si>
+  <si>
+    <t>gxag082</t>
+  </si>
+  <si>
+    <t>10.1093/jge/gxag082</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jge/advance-article/doi/10.1093/jge/gxag082/8708932</t>
+  </si>
+  <si>
+    <t>Advance article / accepted manuscript</t>
+  </si>
+  <si>
+    <t>Ordos Basin</t>
+  </si>
+  <si>
+    <t>Deep coal measures; No. 8 coal seam</t>
+  </si>
+  <si>
+    <t>No. 8 seam thickness 6-16 m, average 7.8 m</t>
+  </si>
+  <si>
+    <t>建立深部煤系含气性预测方法</t>
+  </si>
+  <si>
+    <t>地质约束、岩石物理、Bayesian AVO、频变地震反演</t>
+  </si>
+  <si>
+    <t>新评价参数可增强气敏感性和岩性区分能力，提高含气性预测精度</t>
+  </si>
+  <si>
+    <t>面向煤系气的地质—岩石物理—频变反演框架</t>
+  </si>
+  <si>
+    <t>依赖高质量地震和井震标定；与生产动态关联需进一步建立</t>
+  </si>
+  <si>
+    <t>可作为地质背景变量和含气性解释依据</t>
+  </si>
+  <si>
+    <t>gas-bearing prediction; deep coal measures; Ordos Basin; seismic inversion</t>
+  </si>
+  <si>
+    <t>Oxford 页面、DOI、题名、作者、摘要已核验</t>
+  </si>
+  <si>
+    <t>DCBM-121</t>
+  </si>
+  <si>
+    <t>YANG Jiaosheng; WANG Nan; WANG Meizhu; DENG Jia; LU Xiuqin; SONG Hongqing</t>
+  </si>
+  <si>
+    <t>Productivity prediction and production performances of deep coalbed methane horizontal wells throughout full life cycle</t>
+  </si>
+  <si>
+    <t>深部煤层气水平井全生命周期产能预测与生产动态</t>
+  </si>
+  <si>
+    <t>3551-3561</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.QH25.0479</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/en/article/doi/10.13225/j.cnki.jccs.QH25.0479</t>
+  </si>
+  <si>
+    <t>Deep CBM fractured horizontal well</t>
+  </si>
+  <si>
+    <t>建立全生命周期产能预测模型</t>
+  </si>
+  <si>
+    <t>Langmuir 等温吸附、气水两相两区流、10 年生产预测</t>
+  </si>
+  <si>
+    <t>早期游离气贡献高；后期解吸气贡献升高；10 年累产中解吸气 63.54%、游离气 36.46%</t>
+  </si>
+  <si>
+    <t>将游离气—解吸气动态贡献纳入深部煤层气水平井全生命周期预测</t>
+  </si>
+  <si>
+    <t>参数不确定性较高；需结合现场排采制度进一步验证</t>
+  </si>
+  <si>
+    <t>强相关，可解释早期响应和中长期产能关系</t>
+  </si>
+  <si>
+    <t>第二章；第四章；第五章</t>
+  </si>
+  <si>
+    <t>productivity prediction; full life cycle; free gas; desorbed gas; horizontal well</t>
+  </si>
+  <si>
+    <t>煤炭学报页面、DOI、卷期页码、摘要已核验</t>
+  </si>
+  <si>
+    <t>研究区/对象：Ordos Basin; Daning-Jixian Block；Deep coal rock gas; No. 5 and No. 8 coal seams；深度：深部煤岩气储层。</t>
+  </si>
+  <si>
+    <t>【研究目的】识别深部煤岩气压裂甜点段
+【数据/方法】PSO-ELM、测井资料、10 个地质工程控制因素、甜点分级
+【核心发现】X-11 井预测准确率超过 85%；I、II 类甜点段资源丰富
+【创新点】将 PSO-ELM 用于地质工程一体化压裂甜点评价
+【局限性】跨区块泛化需验证；机器学习可解释性需增强
+【与你课题的关系】可作为响应差异的地质工程背景变量参考</t>
+  </si>
+  <si>
+    <t>研究区/对象：Ordos Basin；Deep coal measures; No. 8 coal seam；深度：No. 8 seam thickness 6-16 m, average 7.8 m。</t>
+  </si>
+  <si>
+    <t>【研究目的】建立深部煤系含气性预测方法
+【数据/方法】地质约束、岩石物理、Bayesian AVO、频变地震反演
+【核心发现】新评价参数可增强气敏感性和岩性区分能力，提高含气性预测精度
+【创新点】面向煤系气的地质—岩石物理—频变反演框架
+【局限性】依赖高质量地震和井震标定；与生产动态关联需进一步建立
+【与你课题的关系】可作为地质背景变量和含气性解释依据</t>
+  </si>
+  <si>
+    <t>研究区/对象：Ordos Basin; Daning-Jixian Block；Deep CBM fractured horizontal well；深度：深部煤层气储层。</t>
+  </si>
+  <si>
+    <t>【研究目的】建立全生命周期产能预测模型
+【数据/方法】Langmuir 等温吸附、气水两相两区流、10 年生产预测
+【核心发现】早期游离气贡献高；后期解吸气贡献升高；10 年累产中解吸气 63.54%、游离气 36.46%
+【创新点】将游离气—解吸气动态贡献纳入深部煤层气水平井全生命周期预测
+【局限性】参数不确定性较高；需结合现场排采制度进一步验证
+【与你课题的关系】强相关，可解释早期响应和中长期产能关系</t>
+  </si>
+  <si>
+    <t>2026-07-09 Daily Brief corrected update</t>
+  </si>
+  <si>
+    <t>Added DCBM-119 to DCBM-121</t>
+  </si>
+  <si>
+    <t>Skipped duplicate candidate</t>
+  </si>
+  <si>
+    <t>flowback characteristics, existing DCBM-028</t>
+  </si>
+  <si>
+    <t>Master record count</t>
+  </si>
+  <si>
+    <t>118 -&gt; 121</t>
+  </si>
+  <si>
+    <t>Daily Brief</t>
+  </si>
+  <si>
+    <t>09_Daily_Brief/2026-07-09/Deep_CBM_daily_brief_20260709.md</t>
+  </si>
+  <si>
+    <t>原DCBM-119</t>
+  </si>
+  <si>
+    <t>10.3389/feart.2026.1772109 / Evaluation of development effectiveness of deep coalbed methane based on flowback characteristics-a case study of the Daning-Jixian block</t>
+  </si>
+  <si>
+    <t>DOI完全一致；英文题名一致；中文题名一致</t>
+  </si>
+  <si>
+    <t>跳过</t>
+  </si>
+  <si>
+    <t>原DCBM-120</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-026-54924-z / Evaluating deep coal rock gas fracturing sweet spot intervals using PSO-ELM algorithm and petrophysical logging data</t>
+  </si>
+  <si>
+    <t>不重复</t>
+  </si>
+  <si>
+    <t>DOI、英文题名、中文题名、作者年份均未检出</t>
+  </si>
+  <si>
+    <t>原DCBM-121</t>
+  </si>
+  <si>
+    <t>10.1093/jge/gxag082 / Prediction Methods for Gas-bearing Properties in Deep Coal Measures in the Ordos Basin</t>
+  </si>
+  <si>
+    <t>原DCBM-122</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.QH25.0479 / Productivity prediction and production performances of deep coalbed methane horizontal wells throughout full life cycle</t>
+  </si>
+  <si>
+    <t>Daily Brief corrected</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Added records</t>
+  </si>
+  <si>
+    <t>DCBM-119 to DCBM-121</t>
+  </si>
+  <si>
+    <t>Skipped duplicate</t>
+  </si>
+  <si>
+    <t>Original DCBM-119 already exists as DCBM-028</t>
+  </si>
+  <si>
+    <t>Duplicate DOI/title check</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -9009,6 +9300,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="8">
@@ -9065,11 +9362,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9091,10 +9389,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9309,7 +9611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA119"/>
+  <dimension ref="A1:AA122"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -19150,11 +19452,257 @@
         <v>2217</v>
       </c>
     </row>
+    <row r="120" spans="1:27" ht="41.4">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E120" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1" t="s">
+        <v>2792</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>2793</v>
+      </c>
+      <c r="M120" s="9" t="s">
+        <v>2794</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>2795</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>2796</v>
+      </c>
+      <c r="P120" s="1" t="s">
+        <v>2797</v>
+      </c>
+      <c r="Q120" s="1" t="s">
+        <v>2798</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>2799</v>
+      </c>
+      <c r="S120" s="1" t="s">
+        <v>2800</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>2801</v>
+      </c>
+      <c r="U120" s="1" t="s">
+        <v>2802</v>
+      </c>
+      <c r="V120" s="1" t="s">
+        <v>2803</v>
+      </c>
+      <c r="W120" s="1" t="s">
+        <v>2804</v>
+      </c>
+      <c r="X120" s="1" t="s">
+        <v>2805</v>
+      </c>
+      <c r="Y120" s="1" t="s">
+        <v>2806</v>
+      </c>
+      <c r="Z120" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA120" s="1" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" ht="41.4">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>2809</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>2810</v>
+      </c>
+      <c r="E121" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>2812</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>2813</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1" t="s">
+        <v>2814</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>2815</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>2816</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>2817</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>2818</v>
+      </c>
+      <c r="P121" s="1" t="s">
+        <v>2819</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>2820</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>2821</v>
+      </c>
+      <c r="S121" s="1" t="s">
+        <v>2822</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>2823</v>
+      </c>
+      <c r="U121" s="1" t="s">
+        <v>2824</v>
+      </c>
+      <c r="V121" s="1" t="s">
+        <v>2825</v>
+      </c>
+      <c r="W121" s="1" t="s">
+        <v>2826</v>
+      </c>
+      <c r="X121" s="1" t="s">
+        <v>2805</v>
+      </c>
+      <c r="Y121" s="1" t="s">
+        <v>2827</v>
+      </c>
+      <c r="Z121" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA121" s="1" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27" ht="41.4">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>2830</v>
+      </c>
+      <c r="E122" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>2831</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>2832</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I122" s="1">
+        <v>51</v>
+      </c>
+      <c r="J122" s="1">
+        <v>6</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>2833</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>2834</v>
+      </c>
+      <c r="M122" s="9" t="s">
+        <v>2835</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>2795</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>2796</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>2836</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>2837</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>2838</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>2839</v>
+      </c>
+      <c r="U122" s="1" t="s">
+        <v>2840</v>
+      </c>
+      <c r="V122" s="1" t="s">
+        <v>2841</v>
+      </c>
+      <c r="W122" s="1" t="s">
+        <v>2842</v>
+      </c>
+      <c r="X122" s="1" t="s">
+        <v>2843</v>
+      </c>
+      <c r="Y122" s="1" t="s">
+        <v>2844</v>
+      </c>
+      <c r="Z122" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA122" s="1" t="s">
+        <v>2845</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="M120" r:id="rId1" xr:uid="{CC16D580-FDCE-4E16-95A4-6D8C719BCB74}"/>
+    <hyperlink ref="M121" r:id="rId2" xr:uid="{61B660BB-0451-434D-861F-5A2A7A017BCD}"/>
+    <hyperlink ref="M122" r:id="rId3" xr:uid="{BBC8EAEE-6B77-43F7-8540-3A99CD9FC4B3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -22427,7 +22975,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -27680,6 +28228,120 @@
         <v>2515</v>
       </c>
     </row>
+    <row r="120" spans="1:14" ht="82.8">
+      <c r="A120" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B120" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>2799</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>2800</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>2802</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>2803</v>
+      </c>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N120" s="1"/>
+    </row>
+    <row r="121" spans="1:14" ht="82.8">
+      <c r="A121" s="1" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B121" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>2848</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>2849</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>2821</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>2822</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>2825</v>
+      </c>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N121" s="1"/>
+    </row>
+    <row r="122" spans="1:14" ht="82.8">
+      <c r="A122" s="1" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B122" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>2850</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>2851</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>2837</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>2838</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>2839</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>2840</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>2841</v>
+      </c>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N122" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27688,7 +28350,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -27750,6 +28412,38 @@
         <v>2778</v>
       </c>
     </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2859</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27758,7 +28452,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:6" ht="27.6">
@@ -28099,6 +28793,86 @@
       </c>
       <c r="F17" s="1" t="s">
         <v>2765</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="303.60000000000002">
+      <c r="A18" s="1" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>2862</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="276">
+      <c r="A19" s="1" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="193.2">
+      <c r="A20" s="1" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>2808</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="276">
+      <c r="A21" s="1" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>2829</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2762</v>
       </c>
     </row>
   </sheetData>
@@ -28109,7 +28883,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="42" customWidth="1"/>
@@ -28163,6 +28937,46 @@
         <v>2786</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2873</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3148">
   <si>
     <t>序号</t>
   </si>
@@ -7765,340 +7765,628 @@
     <t>DCBM-125</t>
   </si>
   <si>
+    <t>Xi, Zhaodong</t>
+  </si>
+  <si>
+    <t>Xi, Zhaodong; Tang, Shuheng; Duan, Lijiang; Zhang, Songhang; Wang, Zhizhen</t>
+  </si>
+  <si>
     <t>Mechanism of gas breakthrough time control in deep CBM wells and optimization of production strategies</t>
   </si>
   <si>
     <t>深部煤层气井见气时间控制机理与排采制度优化</t>
   </si>
   <si>
+    <t>1463-1475</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.XH25.1256</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.XH25.1256</t>
+  </si>
+  <si>
+    <t>鄂尔多斯盆地东缘北部；百余口井地质和动态资料。</t>
+  </si>
+  <si>
+    <t>深部煤层气井；百余口井地质和动态资料</t>
+  </si>
+  <si>
+    <t>深部煤层气储层（鄂尔多斯盆地东缘北部）</t>
+  </si>
+  <si>
+    <t>揭示深部煤层气井见气时间控制机理，优化排采制度</t>
+  </si>
+  <si>
+    <t>见气饱和度、状态方程、Langmuir、气水两相渗流、实验和 COMET3 模拟。</t>
+  </si>
+  <si>
+    <t>见气时间 0–276 d，平均 30.6 d；研究区单相排水阶段合理压降速率 0.10–0.25 MPa/d；典型井模拟见气时间缩短 8%–80%，平均日产气提高 5.9%–11.8%。</t>
+  </si>
+  <si>
+    <t>定量连接游离气富集、压降和首次见气。</t>
+  </si>
+  <si>
+    <t>模式和压降区间具有区块适用性，不得反向用于用户项目正式分型或最优制度。</t>
+  </si>
+  <si>
+    <t>引言、首次见气对齐方法、压力传播/解吸讨论、局限。</t>
+  </si>
+  <si>
+    <t>gas breakthrough; deep CBM; production; 见气时间; 排采制度; 解吸; 游离气; 鄂尔多斯盆地</t>
+  </si>
+  <si>
+    <t>DCBM-126</t>
+  </si>
+  <si>
+    <t>Qiu, Peng</t>
+  </si>
+  <si>
+    <t>Qiu, Peng; Chen, Heqing; Yang, Zhaobiao; Zhong, Junbing; Liu, Changqing; Li, Cunlei; Zhang, Baoxin; Liang, Yuhui; Wang, Yuqiang</t>
+  </si>
+  <si>
+    <t>Progress and prospect of exploration and development of deep coalbed methane in the Junggar Basin</t>
+  </si>
+  <si>
+    <t>准噶尔盆地深部煤层气勘探开发进展及前景展望</t>
+  </si>
+  <si>
+    <t>299-312</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.2025.0522</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.0522</t>
+  </si>
+  <si>
+    <t>准噶尔盆地深部煤层气勘探开发进展及前景展望**  
+英文：*Progress and prospect o</t>
+  </si>
+  <si>
+    <t>准噶尔盆地侏罗系中低煤阶深部煤层气。</t>
+  </si>
+  <si>
+    <t>吸附气临界深度约1000–1500 m；总含气量临界深度约2500–3000 m</t>
+  </si>
+  <si>
+    <t>系统总结准噶尔盆地侏罗系中低煤阶深部煤层气勘探开发进展与前景</t>
+  </si>
+  <si>
+    <t>盆地尺度地质、含气性、成藏、压裂和水平井动态综合。</t>
+  </si>
+  <si>
+    <t>吸附气临界深度约 1000–1500 m，总含气量临界深度约 2500–3000 m；2000 m 后游离气比例可接近 50%；水平井常见气快、产水和返排率低，早中期游离气、后期吸附气贡献增强。</t>
+  </si>
+  <si>
+    <t>提供中低煤阶、强润湿性盆地案例。</t>
+  </si>
+  <si>
+    <t>深度阈值和压裂体系不可直接外推。</t>
+  </si>
+  <si>
+    <t>盆地进展、游离/吸附气、返排与液相滞留、区域差异。</t>
+  </si>
+  <si>
+    <t>deep coalbed methane; Junggar Basin; 压裂; 润湿性; 吸附; 游离气; 返排液; 准噶尔盆地</t>
+  </si>
+  <si>
+    <t>DCBM-127</t>
+  </si>
+  <si>
+    <t>Zhang, Tao</t>
+  </si>
+  <si>
+    <t>Zhang, Tao; Guo, Jianchun; Zhao, Zhihong; Zeng, Jie</t>
+  </si>
+  <si>
+    <t>Mechanism of Wettability Alteration to Unlock Adsorbed-State Methane in Deep Coal Rock: Insight from Experiment and Molecular Simulation</t>
+  </si>
+  <si>
+    <t>深部煤岩润湿性调控促进吸附态甲烷释放机理</t>
+  </si>
+  <si>
+    <t>10.1021/acs.energyfuels.6c02337</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/acs.energyfuels.6c02337</t>
+  </si>
+  <si>
+    <t>未指定具体区块（实验与分子模拟研究）</t>
+  </si>
+  <si>
+    <t>深部煤岩；吸附态甲烷</t>
+  </si>
+  <si>
+    <t>深部煤岩储层（实验条件模拟深部温压）</t>
+  </si>
+  <si>
+    <t>揭示润湿性调控对深部煤岩吸附态甲烷释放的促进机理</t>
+  </si>
+  <si>
+    <t>渗吸、孔隙表征、吸附/解吸和分子动力学。</t>
+  </si>
+  <si>
+    <t>0.3–1.5 nm 孔尺度增加 59.6%，2–10 nm 增加 44.8%；CH₄—煤配位数 16.2→12.3，水—煤 0→9.6；模拟能垒约 1500→800 kJ/mol。</t>
+  </si>
+  <si>
+    <t>统一解释润湿性、孔隙重构和水膜竞争吸附。</t>
+  </si>
+  <si>
+    <t>微观和实验结果不能直接证明井级长期增产。</t>
+  </si>
+  <si>
+    <t>水锁、液相滞留、解吸启动、裂缝—基质传质。</t>
+  </si>
+  <si>
+    <t>水锁与液相滞留；解吸启动；裂缝-基质传质</t>
+  </si>
+  <si>
+    <t>Wettability; Deep Coal; 润湿性; 吸附; 解吸; 孔隙结构; Energy &amp; Fuels</t>
+  </si>
+  <si>
+    <t>DCBM-128</t>
+  </si>
+  <si>
+    <t>Chang, Xiangchun</t>
+  </si>
+  <si>
+    <t>Chang, Xiangchun; Wang, Shangbin; Zhang, Junjian; Shi, Bingbing; Vandeginste, Veerle; Liu, Yu; Zhang, Pengfei</t>
+  </si>
+  <si>
+    <t>Adsorption Thermodynamic Property of Deep Coal Reservoirs and Adsorption Capacity Prediction under Different Temperature and Pressure Conditions</t>
+  </si>
+  <si>
+    <t>深部煤储层吸附热力学性质及不同温压条件下吸附容量预测</t>
+  </si>
+  <si>
+    <t>10.1021/acs.energyfuels.6c02529</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/acs.energyfuels.6c02529</t>
+  </si>
+  <si>
+    <t>鄂尔多斯东缘本溪组 3 口井、17 件煤样。
+- 方法：工业分析、CO₂ 吸附、高温高压甲烷吸附、等量吸附热</t>
+  </si>
+  <si>
+    <t>鄂尔多斯东缘本溪组深部煤储层；3口井17件煤样</t>
+  </si>
+  <si>
+    <t>鄂尔多斯东缘本溪组深部煤层</t>
+  </si>
+  <si>
+    <t>揭示深部煤储层吸附热力学性质，预测不同温压条件下吸附容量</t>
+  </si>
+  <si>
+    <t>工业分析、CO₂ 吸附、高温高压甲烷吸附、等量吸附热和模型预测。</t>
+  </si>
+  <si>
+    <t>灰分总体削弱微孔和吸附，固定碳/微孔与 Langmuir 体积正相关；升温降低吸附，升压提高吸附。</t>
+  </si>
+  <si>
+    <t>建立灰分-微孔-吸附容量的定量关联；等量吸附热和模型预测</t>
+  </si>
+  <si>
+    <t>模型受煤阶和实验温压范围约束，吸附容量不等于可采气量。</t>
+  </si>
+  <si>
+    <t>温压背景、吸附/游离气和资料边界。</t>
+  </si>
+  <si>
+    <t>温压背景；吸附/游离气；资料边界与不确定性</t>
+  </si>
+  <si>
+    <t>Adsorption; Deep Coal; 吸附; 游离气; 吸附热力学; 鄂尔多斯盆地; Energy &amp; Fuels</t>
+  </si>
+  <si>
+    <t>DCBM-129</t>
+  </si>
+  <si>
+    <t>Liu, Pingli</t>
+  </si>
+  <si>
+    <t>Liu, Pingli; Zuo, Chengwei; Du, Juan; Li, Jiahao; Zhang, Xin; Zhao, Renyin</t>
+  </si>
+  <si>
+    <t>Bioinspired by Mussels: Construction of an Ultrasalt-Tolerant, Tunable-Viscosity Slickwater Fracturing Fluid for the Reuse of Deep Coalbed Methane Flowback Fluids</t>
+  </si>
+  <si>
+    <t>贻贝仿生超耐盐可调黏滑溜水压裂液及返排液回用</t>
+  </si>
+  <si>
+    <t>Langmuir</t>
+  </si>
+  <si>
+    <t>10.1021/acs.langmuir.6c01692</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/acs.langmuir.6c01692</t>
+  </si>
+  <si>
+    <t>未指定具体区块（材料研发与室内实验）</t>
+  </si>
+  <si>
+    <t>深部煤层气返排液；超耐盐滑溜水压裂液</t>
+  </si>
+  <si>
+    <t>深部煤层气储层（TDS &gt;120,000 mg/L 高矿化度条件）</t>
+  </si>
+  <si>
+    <t>开发贻贝仿生超耐盐可调黏滑溜水压裂液，实现返排液回用</t>
+  </si>
+  <si>
+    <t>超高矿化度配伍、流变、减阻、携砂、破胶、残渣和分子模拟。</t>
+  </si>
+  <si>
+    <t>TDS &gt;120,000 mg/L 时黏度约 75 mPa·s；最大减阻率 79.58%；60 ℃ 约 3 h 破胶，残渣约 310 mg/L。</t>
+  </si>
+  <si>
+    <t>整合返排液回用、耐盐、减阻和携砂。</t>
+  </si>
+  <si>
+    <t>材料性能不能直接证明产气提升，需现场地层伤害验证。</t>
+  </si>
+  <si>
+    <t>返排、水锁、液相滞留和压裂液差异。</t>
+  </si>
+  <si>
+    <t>返排与水锁；液相滞留；压裂液体系差异</t>
+  </si>
+  <si>
+    <t>Slickwater; Fracturing; Deep Coalbed Methane; Flowback; 压裂; 返排液</t>
+  </si>
+  <si>
+    <t>DCBM-130</t>
+  </si>
+  <si>
+    <t>Shi, Yunhe</t>
+  </si>
+  <si>
+    <t>Shi, Yunhe; Xu, Chang; Wang, Kangle; Zhang, Hui; Liang, Chen; Wang, Huaichang; Cao, Jingjing; Jing, Xueyuan; Du, Yi</t>
+  </si>
+  <si>
+    <t>Multifractal Characteristics of Pore Structure in Deep Coal Reservoirs of the Suide Block, Ordos Basin</t>
+  </si>
+  <si>
+    <t>绥德区块深部煤储层孔隙结构多重分形特征</t>
+  </si>
+  <si>
+    <t>10.1021/acsomega.6c04169</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/acsomega.6c04169</t>
+  </si>
+  <si>
+    <t>Ordos Basin*  
+Yunhe Shi 等 9 人. ACS Omega, online 2026-</t>
+  </si>
+  <si>
+    <t>本溪组 8 号深部煤。</t>
+  </si>
+  <si>
+    <t>绥德区块本溪组8号深部煤层</t>
+  </si>
+  <si>
+    <t>揭示绥德区块本溪组8号深部煤储层孔隙结构多重分形特征</t>
+  </si>
+  <si>
+    <t>FESEM、低温 CO₂/N₂ 吸附、高压压汞和多重分形。</t>
+  </si>
+  <si>
+    <t>微孔约占 86.26%；各级孔隙均多重分形；大孔非均质性最高、连通性最差；灰分降低孔容并削弱中大孔连通。</t>
+  </si>
+  <si>
+    <t>微孔约占86.26%；各级孔隙均多重分形；大孔非均质性最高、连通性最差</t>
+  </si>
+  <si>
+    <t>样本量有限，分形参数与井级产能缺乏跨尺度验证。</t>
+  </si>
+  <si>
+    <t>微孔吸附、中大孔渗流、裂缝—基质传质。</t>
+  </si>
+  <si>
+    <t>微孔吸附；中大孔渗流；裂缝-基质传质</t>
+  </si>
+  <si>
+    <t>Multifractal; Pore Structure; Deep Coal; Ordos Basin; 吸附; 孔隙结构; 绥德区块</t>
+  </si>
+  <si>
+    <t>DCBM-131</t>
+  </si>
+  <si>
+    <t>Zhuo, Hong</t>
+  </si>
+  <si>
+    <t>Zhuo, Hong; Han, Zhangying; Li, Shaohua; He, Xiuling; Zhang, Demei; Song, Haibin; Hui, Gang</t>
+  </si>
+  <si>
+    <t>Fracturing Tracer Monitoring and Machine Learning-Assisted Geology-Engineering Coupled Optimization for Deep Coalbed Methane Horizontal Wells</t>
+  </si>
+  <si>
+    <t>深部煤层气水平井压裂示踪监测与机器学习辅助地质—工程耦合优化</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>10.3390/pr14121890</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2227-9717/14/12/1890</t>
+  </si>
+  <si>
+    <t>长庆矿区 10 口井、132 个压裂段；8 口完整井 105 段用于主分析，2 口井 27 段用于独立验</t>
+  </si>
+  <si>
+    <t>长庆矿区10口深部煤层气水平井；132个压裂段</t>
+  </si>
+  <si>
+    <t>长庆矿区深部煤层气储层</t>
+  </si>
+  <si>
+    <t>利用压裂示踪监测和机器学习实现深部煤层气水平井地质-工程耦合优化</t>
+  </si>
+  <si>
+    <t>水相/气相示踪、Pearson、Random Forest 和段级生产贡献解释。</t>
+  </si>
+  <si>
+    <t>外部研究识别 3 种段间产出形态；一类煤钻遇长度与初始产气的幂律 R²=0.71；保留测试集 R²=0.83；提出差异化压裂窗口。</t>
+  </si>
+  <si>
+    <t>把段级示踪、生产剖面和机器学习闭环结合。</t>
+  </si>
+  <si>
+    <t>外部分类和特征重要性不得变成用户项目正式类型或主控因素排序。</t>
+  </si>
+  <si>
+    <t>压裂差异、段间非均质性、独立监测资料缺口、exploratory ML 边界。</t>
+  </si>
+  <si>
+    <t>Fracturing; Tracer; Machine Learning; Deep Coalbed Methane; 压裂; 压裂示踪; 机器学习; 深部煤层气</t>
+  </si>
+  <si>
+    <t>DCBM-132</t>
+  </si>
+  <si>
+    <t>Guo, Jianchun</t>
+  </si>
+  <si>
+    <t>Guo, Jianchun; Zeng, Jie; Zhao, Zhihong; Lu, Qianli; Zhou, Hangyu; Ren, Wenxi; Zhang, Tao; Liu, Yuxuan; Zhang, Tao; Wu, Tianyu</t>
+  </si>
+  <si>
+    <t>Several key issues and insights in full-scale proppant-support fracturing for deep coal rock gas formations</t>
+  </si>
+  <si>
+    <t>煤岩气全域支撑压裂的几个关键问题与思考</t>
+  </si>
+  <si>
+    <t>613-629</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.2025.1460</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.1460</t>
+  </si>
+  <si>
+    <t>未指定具体区块（理论与工程思考）</t>
+  </si>
+  <si>
+    <t>深部煤岩气储层；人工裂缝与天然割理系统</t>
+  </si>
+  <si>
+    <t>提出煤岩气全域支撑压裂的关键问题与技术思考</t>
+  </si>
+  <si>
+    <t>提出点解吸、线疏通、面促缝、体支撑理念；讨论基质孔隙改造、渗吸置换、割理激活、长缝网、多级缝宽-支撑剂匹配</t>
+  </si>
+  <si>
+    <t>从吸附气-游离气连续供气角度连接基质、割理和人工裂缝；提出全域支撑技术框架</t>
+  </si>
+  <si>
+    <t>从吸附气—游离气连续供气角度连接基质、割理和人工裂缝。</t>
+  </si>
+  <si>
+    <t>以理论和工程思考为主，不能替代用户项目压裂施工、示踪或导流能力资料。</t>
+  </si>
+  <si>
+    <t>压裂导流、裂缝网络、连续供气、压裂改造差异。</t>
+  </si>
+  <si>
+    <t>proppant; fracturing; deep coal; 压裂; 吸附; 解吸; 游离气; 孔隙结构</t>
+  </si>
+  <si>
+    <t>DCBM-133</t>
+  </si>
+  <si>
+    <t>Li, Sihao</t>
+  </si>
+  <si>
+    <t>Li, Sihao; Li, Xin; Tang, Yong; Chen, Yanpeng; Quaye, Jonathan Atuquaye; Hu, Chenlin</t>
+  </si>
+  <si>
+    <t>Mechanisms of deep coalbed methane occurrence: Review and perspectives</t>
+  </si>
+  <si>
+    <t>深部煤层气赋存机理：研究进展与展望</t>
+  </si>
+  <si>
+    <t>Advances in Geo-Energy Research</t>
+  </si>
+  <si>
+    <t>42-59</t>
+  </si>
+  <si>
+    <t>https://ager.yandypress.com/index.php/2207-9963/article/view/871</t>
+  </si>
+  <si>
+    <t>Review article</t>
+  </si>
+  <si>
+    <t>综述（未限定具体区块）</t>
+  </si>
+  <si>
+    <t>深部煤层气赋存机理（成因、演化、温压应力、吸附/游离气等）</t>
+  </si>
+  <si>
+    <t>综述（涵盖不同深度范围）</t>
+  </si>
+  <si>
+    <t>系统综述深部煤层气赋存机理的研究进展与展望</t>
+  </si>
+  <si>
+    <t>综述成因、埋藏演化、温压应力、吸附/游离气、构造盖层、水动力封闭、裂缝渗流和基质扩散</t>
+  </si>
+  <si>
+    <t>热成因气重要；游离气比例通常随深度增加；构造、盖层和裂缝共同控制保存和富集；尝试整合临界深度、裂缝渗流-基质扩散及生产模型</t>
+  </si>
+  <si>
+    <t>尝试整合临界深度、裂缝渗流—基质扩散及生产模型。</t>
+  </si>
+  <si>
+    <t>综述不能替代项目证据；不得编造 DOI。</t>
+  </si>
+  <si>
+    <t>临界深度、裂缝渗流-基质扩散及生产模型整合；可作为论文综述参考</t>
+  </si>
+  <si>
+    <t>文献综述；赋存机理；吸附/游离气讨论</t>
+  </si>
+  <si>
+    <t>deep coalbed methane; occurrence; 吸附; 游离气; 赋存机理; 深部煤层气</t>
+  </si>
+  <si>
+    <t>题名、作者、卷期页码已核验；DOI待确认</t>
+  </si>
+  <si>
+    <t>DCBM-134</t>
+  </si>
+  <si>
+    <t>Yang, Wei</t>
+  </si>
+  <si>
+    <t>Yang, Wei; Yao, Yanbin; Feng, Dong; Sun, Xiaoxiao; Wang, Zefan; Duan, Shulei</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>Nanoconfinement effects on adsorbed and free methane densities: Revisiting coalbed methane content evaluation</t>
+  </si>
+  <si>
+    <t>纳米限域对吸附态与游离态甲烷密度的影响：煤层气含量评价再认识</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>Part C</t>
+  </si>
+  <si>
+    <t>139801</t>
+  </si>
+  <si>
+    <t>10.1016/j.fuel.2026.139801</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0016236126015553</t>
+  </si>
+  <si>
+    <t>未指定具体区块（分子模拟研究）</t>
+  </si>
+  <si>
+    <t>纳米狭缝孔中甲烷吸附态与游离态密度</t>
+  </si>
+  <si>
+    <t>深部煤层纳米孔隙（模拟深部温压条件）</t>
+  </si>
+  <si>
+    <t>研究纳米限域效应对吸附态与游离态甲烷密度的影响，重新认识煤层气含量评价</t>
+  </si>
+  <si>
+    <t>狭缝纳米孔模拟、Peng–Robinson 状态方程修正、限域逸度—压力、吸附相/游离相密度和煤阶修正。</t>
+  </si>
+  <si>
+    <t>以体相密度处理纳米孔会系统偏置吸附/游离气分配；忽略限域可能低估深部煤层中的真实游离气比例。</t>
+  </si>
+  <si>
+    <t>把孔隙尺度限域热力学传递到储层含气量评价。</t>
+  </si>
+  <si>
+    <t>依赖孔形、状态方程和煤阶修正，需保压取心和现场数据验证。</t>
+  </si>
+  <si>
+    <t>早期游离气贡献和相态评价边界。</t>
+  </si>
+  <si>
+    <t>早期游离气贡献；相态评价边界；煤层气含量评价方法</t>
+  </si>
+  <si>
+    <t>Nanoconfinement; coalbed methane; 吸附; 游离气; 纳米限域; 孔隙结构; 吸附热力学</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>累计文献数</t>
+  </si>
+  <si>
+    <t>2026-07-10 更新</t>
+  </si>
+  <si>
+    <t>本批新增</t>
+  </si>
+  <si>
+    <t>第五批，DCBM-085 至 DCBM-105</t>
+  </si>
+  <si>
+    <t>当前主表版本</t>
+  </si>
+  <si>
+    <t>v1_134_daily_brief_update_2026-07-23</t>
+  </si>
+  <si>
+    <t>Deep_CBM_complete_literature_matrix_v1_105.xlsx</t>
+  </si>
+  <si>
+    <t>RIS完整库</t>
+  </si>
+  <si>
+    <t>Deep_CBM_complete_v1_105.ris</t>
+  </si>
+  <si>
+    <t>Zotero 从零导入使用</t>
+  </si>
+  <si>
+    <t>增量RIS</t>
+  </si>
+  <si>
+    <t>Deep_CBM_verified_batch5_21.ris</t>
+  </si>
+  <si>
+    <t>已导入前84篇时使用</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>煤炭学报</t>
-  </si>
-  <si>
-    <t>1463–1475.</t>
-  </si>
-  <si>
-    <t>10.13225/j.cnki.jccs.XH25.1256</t>
-  </si>
-  <si>
-    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.XH25.1256</t>
-  </si>
-  <si>
-    <t>鄂尔多斯盆地东缘北部；百余口井地质和动态资料。</t>
-  </si>
-  <si>
-    <t>见气饱和度、状态方程、Langmuir、气水两相渗流、实验和 COMET3 模拟。</t>
-  </si>
-  <si>
-    <t>见气时间 0–276 d，平均 30.6 d；研究区单相排水阶段合理压降速率 0.10–0.25 MPa/d；典型井模拟见气时间缩短 8%–80%，平均日产气提高 5.9%–11.8%。</t>
-  </si>
-  <si>
-    <t>定量连接游离气富集、压降和首次见气。</t>
-  </si>
-  <si>
-    <t>模式和压降区间具有区块适用性，不得反向用于用户项目正式分型或最优制度。</t>
-  </si>
-  <si>
-    <t>引言、首次见气对齐方法、压力传播/解吸讨论、局限。</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>DCBM-126</t>
-  </si>
-  <si>
-    <t>Progress and prospect of exploration and development of deep coalbed methane in the Junggar Basin</t>
-  </si>
-  <si>
-    <t>准噶尔盆地深部煤层气勘探开发进展及前景展望</t>
-  </si>
-  <si>
-    <t>299–312.</t>
-  </si>
-  <si>
-    <t>10.13225/j.cnki.jccs.2025.0522</t>
-  </si>
-  <si>
-    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.0522</t>
-  </si>
-  <si>
-    <t>准噶尔盆地侏罗系中低煤阶深部煤层气。</t>
-  </si>
-  <si>
-    <t>盆地尺度地质、含气性、成藏、压裂和水平井动态综合。</t>
-  </si>
-  <si>
-    <t>吸附气临界深度约 1000–1500 m，总含气量临界深度约 2500–3000 m；2000 m 后游离气比例可接近 50%；水平井常见气快、产水和返排率低，早中期游离气、后期吸附气贡献增强。</t>
-  </si>
-  <si>
-    <t>提供中低煤阶、强润湿性盆地案例。</t>
-  </si>
-  <si>
-    <t>深度阈值和压裂体系不可直接外推。</t>
-  </si>
-  <si>
-    <t>盆地进展、游离/吸附气、返排与液相滞留、区域差异。</t>
-  </si>
-  <si>
-    <t>DCBM-127</t>
-  </si>
-  <si>
-    <t>深部煤岩润湿性调控促进吸附态甲烷释放机理</t>
-  </si>
-  <si>
-    <t>10.1021/acs.energyfuels.6c02337</t>
-  </si>
-  <si>
-    <t>https://pubs.acs.org/doi/10.1021/acs.energyfuels.6c02337</t>
-  </si>
-  <si>
-    <t>渗吸、孔隙表征、吸附/解吸和分子动力学。</t>
-  </si>
-  <si>
-    <t>0.3–1.5 nm 孔尺度增加 59.6%，2–10 nm 增加 44.8%；CH₄—煤配位数 16.2→12.3，水—煤 0→9.6；模拟能垒约 1500→800 kJ/mol。</t>
-  </si>
-  <si>
-    <t>统一解释润湿性、孔隙重构和水膜竞争吸附。</t>
-  </si>
-  <si>
-    <t>微观和实验结果不能直接证明井级长期增产。</t>
-  </si>
-  <si>
-    <t>水锁、液相滞留、解吸启动、裂缝—基质传质。</t>
-  </si>
-  <si>
-    <t>DCBM-128</t>
-  </si>
-  <si>
-    <t>深部煤储层吸附热力学性质及不同温压条件下吸附容量预测</t>
-  </si>
-  <si>
-    <t>10.1021/acs.energyfuels.6c02529</t>
-  </si>
-  <si>
-    <t>https://pubs.acs.org/doi/10.1021/acs.energyfuels.6c02529</t>
-  </si>
-  <si>
-    <t>工业分析、CO₂ 吸附、高温高压甲烷吸附、等量吸附热和模型预测。</t>
-  </si>
-  <si>
-    <t>灰分总体削弱微孔和吸附，固定碳/微孔与 Langmuir 体积正相关；升温降低吸附，升压提高吸附。</t>
-  </si>
-  <si>
-    <t>模型受煤阶和实验温压范围约束，吸附容量不等于可采气量。</t>
-  </si>
-  <si>
-    <t>温压背景、吸附/游离气和资料边界。</t>
-  </si>
-  <si>
-    <t>DCBM-129</t>
-  </si>
-  <si>
-    <t>贻贝仿生超耐盐可调黏滑溜水压裂液及返排液回用</t>
-  </si>
-  <si>
-    <t>10.1021/acs.langmuir.6c01692</t>
-  </si>
-  <si>
-    <t>https://pubs.acs.org/doi/10.1021/acs.langmuir.6c01692</t>
-  </si>
-  <si>
-    <t>超高矿化度配伍、流变、减阻、携砂、破胶、残渣和分子模拟。</t>
-  </si>
-  <si>
-    <t>TDS &gt;120,000 mg/L 时黏度约 75 mPa·s；最大减阻率 79.58%；60 ℃ 约 3 h 破胶，残渣约 310 mg/L。</t>
-  </si>
-  <si>
-    <t>整合返排液回用、耐盐、减阻和携砂。</t>
-  </si>
-  <si>
-    <t>材料性能不能直接证明产气提升，需现场地层伤害验证。</t>
-  </si>
-  <si>
-    <t>返排、水锁、液相滞留和压裂液差异。</t>
-  </si>
-  <si>
-    <t>DCBM-130</t>
-  </si>
-  <si>
-    <t>绥德区块深部煤储层孔隙结构多重分形特征</t>
-  </si>
-  <si>
-    <t>10.1021/acsomega.6c04169</t>
-  </si>
-  <si>
-    <t>https://pubs.acs.org/doi/10.1021/acsomega.6c04169</t>
-  </si>
-  <si>
-    <t>本溪组 8 号深部煤。</t>
-  </si>
-  <si>
-    <t>FESEM、低温 CO₂/N₂ 吸附、高压压汞和多重分形。</t>
-  </si>
-  <si>
-    <t>微孔约占 86.26%；各级孔隙均多重分形；大孔非均质性最高、连通性最差；灰分降低孔容并削弱中大孔连通。</t>
-  </si>
-  <si>
-    <t>样本量有限，分形参数与井级产能缺乏跨尺度验证。</t>
-  </si>
-  <si>
-    <t>微孔吸附、中大孔渗流、裂缝—基质传质。</t>
-  </si>
-  <si>
-    <t>DCBM-131</t>
-  </si>
-  <si>
-    <t>深部煤层气水平井压裂示踪监测与机器学习辅助地质—工程耦合优化</t>
-  </si>
-  <si>
-    <t>10.3390/pr14121890</t>
-  </si>
-  <si>
-    <t>https://www.mdpi.com/2227-9717/14/12/1890</t>
-  </si>
-  <si>
-    <t>水相/气相示踪、Pearson、Random Forest 和段级生产贡献解释。</t>
-  </si>
-  <si>
-    <t>外部研究识别 3 种段间产出形态；一类煤钻遇长度与初始产气的幂律 R²=0.71；保留测试集 R²=0.83；提出差异化压裂窗口。</t>
-  </si>
-  <si>
-    <t>把段级示踪、生产剖面和机器学习闭环结合。</t>
-  </si>
-  <si>
-    <t>外部分类和特征重要性不得变成用户项目正式类型或主控因素排序。</t>
-  </si>
-  <si>
-    <t>压裂差异、段间非均质性、独立监测资料缺口、exploratory ML 边界。</t>
-  </si>
-  <si>
-    <t>DCBM-132</t>
-  </si>
-  <si>
-    <t>Several key issues and insights in full-scale proppant-support fracturing for deep coal rock gas formations</t>
-  </si>
-  <si>
-    <t>煤岩气全域支撑压裂的几个关键问题与思考</t>
-  </si>
-  <si>
-    <t>613–629.</t>
-  </si>
-  <si>
-    <t>10.13225/j.cnki.jccs.2025.1460</t>
-  </si>
-  <si>
-    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.1460</t>
-  </si>
-  <si>
-    <t>从吸附气—游离气连续供气角度连接基质、割理和人工裂缝。</t>
-  </si>
-  <si>
-    <t>以理论和工程思考为主，不能替代用户项目压裂施工、示踪或导流能力资料。</t>
-  </si>
-  <si>
-    <t>压裂导流、裂缝网络、连续供气、压裂改造差异。</t>
-  </si>
-  <si>
-    <t>DCBM-133</t>
-  </si>
-  <si>
-    <t>深部煤层气赋存机理：研究进展与展望</t>
-  </si>
-  <si>
-    <t>https://ager.yandypress.com/index.php/2207-9963/article/view/871</t>
-  </si>
-  <si>
-    <t>尝试整合临界深度、裂缝渗流—基质扩散及生产模型。</t>
-  </si>
-  <si>
-    <t>综述不能替代项目证据；不得编造 DOI。</t>
-  </si>
-  <si>
-    <t>DCBM-134</t>
-  </si>
-  <si>
-    <t>纳米限域对吸附态与游离态甲烷密度的影响：煤层气含量评价再认识</t>
-  </si>
-  <si>
-    <t>10.1016/j.fuel.2026.139801</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0016236126015553</t>
-  </si>
-  <si>
-    <t>狭缝纳米孔模拟、Peng–Robinson 状态方程修正、限域逸度—压力、吸附相/游离相密度和煤阶修正。</t>
-  </si>
-  <si>
-    <t>以体相密度处理纳米孔会系统偏置吸附/游离气分配；忽略限域可能低估深部煤层中的真实游离气比例。</t>
-  </si>
-  <si>
-    <t>把孔隙尺度限域热力学传递到储层含气量评价。</t>
-  </si>
-  <si>
-    <t>依赖孔形、状态方程和煤阶修正，需保压取心和现场数据验证。</t>
-  </si>
-  <si>
-    <t>早期游离气贡献和相态评价边界。</t>
-  </si>
-  <si>
-    <t>指标</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>累计文献数</t>
-  </si>
-  <si>
-    <t>2026-07-10 更新</t>
-  </si>
-  <si>
-    <t>本批新增</t>
-  </si>
-  <si>
-    <t>第五批，DCBM-085 至 DCBM-105</t>
-  </si>
-  <si>
-    <t>当前主表版本</t>
-  </si>
-  <si>
-    <t>v1_134_daily_brief_update_2026-07-23</t>
-  </si>
-  <si>
-    <t>Deep_CBM_complete_literature_matrix_v1_105.xlsx</t>
-  </si>
-  <si>
-    <t>RIS完整库</t>
-  </si>
-  <si>
-    <t>Deep_CBM_complete_v1_105.ris</t>
-  </si>
-  <si>
-    <t>Zotero 从零导入使用</t>
-  </si>
-  <si>
-    <t>增量RIS</t>
-  </si>
-  <si>
-    <t>Deep_CBM_verified_batch5_21.ris</t>
-  </si>
-  <si>
-    <t>已导入前84篇时使用</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
   </si>
   <si>
     <t>字段</t>
@@ -9582,6 +9870,9 @@
 【核心发现】见气时间 0–276 d，平均 30.6 d；研究区单相排水阶段合理压降速率 0.10–0.25 MPa/d；典型井模拟见气时间缩短 8%–80%，平均日产气提高 5.9%–11.8%。
 【创新点】定量连接游离气富集、压降和首次见气。
 【局限性】模式和压降区间具有区块适用性，不得反向用于用户项目正式分型或最优制度。</t>
+  </si>
+  <si>
+    <t>A+</t>
   </si>
   <si>
     <t>【数据/方法】盆地尺度地质、含气性、成藏、压裂和水平井动态综合。
@@ -20524,19 +20815,23 @@
       <c r="B129" s="10" t="s">
         <v>2574</v>
       </c>
-      <c r="C129" s="10" t="s"/>
-      <c r="D129" s="10" t="s"/>
+      <c r="C129" s="10" t="s">
+        <v>2575</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>2576</v>
+      </c>
       <c r="E129" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>2577</v>
+        <v>34</v>
       </c>
       <c r="I129" s="10" t="s">
         <v>35</v>
@@ -20545,42 +20840,56 @@
         <v>36</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="L129" s="10" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="M129" s="11" t="s">
-        <v>2580</v>
-      </c>
-      <c r="N129" s="10" t="s"/>
+        <v>2581</v>
+      </c>
+      <c r="N129" s="10" t="s">
+        <v>2466</v>
+      </c>
       <c r="O129" s="10" t="s">
-        <v>2581</v>
-      </c>
-      <c r="P129" s="10" t="s"/>
-      <c r="Q129" s="10" t="s"/>
-      <c r="R129" s="10" t="s"/>
+        <v>2582</v>
+      </c>
+      <c r="P129" s="10" t="s">
+        <v>2583</v>
+      </c>
+      <c r="Q129" s="10" t="s">
+        <v>2584</v>
+      </c>
+      <c r="R129" s="10" t="s">
+        <v>2585</v>
+      </c>
       <c r="S129" s="10" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="T129" s="10" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="U129" s="10" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="V129" s="10" t="s">
-        <v>2585</v>
-      </c>
-      <c r="W129" s="10" t="s"/>
+        <v>2589</v>
+      </c>
+      <c r="W129" s="10" t="s">
+        <v>2590</v>
+      </c>
       <c r="X129" s="10" t="s">
-        <v>2586</v>
-      </c>
-      <c r="Y129" s="10" t="s"/>
+        <v>2590</v>
+      </c>
+      <c r="Y129" s="10" t="s">
+        <v>2591</v>
+      </c>
       <c r="Z129" s="10" t="s">
-        <v>2587</v>
-      </c>
-      <c r="AA129" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA129" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="130" spans="1:27"/>
     <row r="131" spans="1:27">
@@ -20588,21 +20897,25 @@
         <v>126</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>2588</v>
-      </c>
-      <c r="C131" s="10" t="s"/>
-      <c r="D131" s="10" t="s"/>
+        <v>2592</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>2594</v>
+      </c>
       <c r="E131" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>2589</v>
+        <v>2595</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>2590</v>
+        <v>2596</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>2577</v>
+        <v>34</v>
       </c>
       <c r="I131" s="10" t="s">
         <v>35</v>
@@ -20611,42 +20924,56 @@
         <v>2402</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>2591</v>
+        <v>2597</v>
       </c>
       <c r="L131" s="10" t="s">
-        <v>2592</v>
+        <v>2598</v>
       </c>
       <c r="M131" s="11" t="s">
-        <v>2593</v>
-      </c>
-      <c r="N131" s="10" t="s"/>
-      <c r="O131" s="10" t="s"/>
+        <v>2599</v>
+      </c>
+      <c r="N131" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O131" s="10" t="s">
+        <v>2600</v>
+      </c>
       <c r="P131" s="10" t="s">
-        <v>2594</v>
-      </c>
-      <c r="Q131" s="10" t="s"/>
-      <c r="R131" s="10" t="s"/>
+        <v>2601</v>
+      </c>
+      <c r="Q131" s="10" t="s">
+        <v>2602</v>
+      </c>
+      <c r="R131" s="10" t="s">
+        <v>2603</v>
+      </c>
       <c r="S131" s="10" t="s">
-        <v>2595</v>
+        <v>2604</v>
       </c>
       <c r="T131" s="10" t="s">
-        <v>2596</v>
+        <v>2605</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>2597</v>
+        <v>2606</v>
       </c>
       <c r="V131" s="10" t="s">
-        <v>2598</v>
-      </c>
-      <c r="W131" s="10" t="s"/>
+        <v>2607</v>
+      </c>
+      <c r="W131" s="10" t="s">
+        <v>2608</v>
+      </c>
       <c r="X131" s="10" t="s">
-        <v>2599</v>
-      </c>
-      <c r="Y131" s="10" t="s"/>
+        <v>2608</v>
+      </c>
+      <c r="Y131" s="10" t="s">
+        <v>2609</v>
+      </c>
       <c r="Z131" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA131" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA131" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="132" spans="1:27"/>
     <row r="133" spans="1:27"/>
@@ -20655,51 +20982,77 @@
         <v>127</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>2600</v>
-      </c>
-      <c r="C134" s="10" t="s"/>
-      <c r="D134" s="10" t="s"/>
-      <c r="E134" s="10" t="s"/>
-      <c r="F134" s="10" t="s"/>
+        <v>2610</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>2612</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>2613</v>
+      </c>
       <c r="G134" s="10" t="s">
-        <v>2601</v>
-      </c>
-      <c r="H134" s="10" t="s"/>
-      <c r="I134" s="10" t="s"/>
-      <c r="J134" s="10" t="s"/>
-      <c r="K134" s="10" t="s"/>
+        <v>2614</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="I134" s="10" t="n"/>
+      <c r="J134" s="10" t="n"/>
+      <c r="K134" s="10" t="n"/>
       <c r="L134" s="10" t="s">
-        <v>2602</v>
+        <v>2615</v>
       </c>
       <c r="M134" s="11" t="s">
-        <v>2603</v>
-      </c>
-      <c r="N134" s="10" t="s"/>
-      <c r="O134" s="10" t="s"/>
-      <c r="P134" s="10" t="s"/>
-      <c r="Q134" s="10" t="s"/>
-      <c r="R134" s="10" t="s"/>
+        <v>2616</v>
+      </c>
+      <c r="N134" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O134" s="10" t="s">
+        <v>2617</v>
+      </c>
+      <c r="P134" s="10" t="s">
+        <v>2618</v>
+      </c>
+      <c r="Q134" s="10" t="s">
+        <v>2619</v>
+      </c>
+      <c r="R134" s="10" t="s">
+        <v>2620</v>
+      </c>
       <c r="S134" s="10" t="s">
-        <v>2604</v>
+        <v>2621</v>
       </c>
       <c r="T134" s="10" t="s">
-        <v>2605</v>
+        <v>2622</v>
       </c>
       <c r="U134" s="10" t="s">
-        <v>2606</v>
+        <v>2623</v>
       </c>
       <c r="V134" s="10" t="s">
-        <v>2607</v>
+        <v>2624</v>
       </c>
       <c r="W134" s="10" t="s">
-        <v>2608</v>
-      </c>
-      <c r="X134" s="10" t="s"/>
-      <c r="Y134" s="10" t="s"/>
+        <v>2625</v>
+      </c>
+      <c r="X134" s="10" t="s">
+        <v>2626</v>
+      </c>
+      <c r="Y134" s="10" t="s">
+        <v>2627</v>
+      </c>
       <c r="Z134" s="10" t="s">
-        <v>2587</v>
-      </c>
-      <c r="AA134" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA134" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="135" spans="1:27"/>
     <row r="136" spans="1:27"/>
@@ -20709,49 +21062,77 @@
         <v>128</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>2609</v>
-      </c>
-      <c r="C138" s="10" t="s"/>
-      <c r="D138" s="10" t="s"/>
-      <c r="E138" s="10" t="s"/>
-      <c r="F138" s="10" t="s"/>
+        <v>2628</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>2630</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>2631</v>
+      </c>
       <c r="G138" s="10" t="s">
-        <v>2610</v>
-      </c>
-      <c r="H138" s="10" t="s"/>
-      <c r="I138" s="10" t="s"/>
-      <c r="J138" s="10" t="s"/>
-      <c r="K138" s="10" t="s"/>
+        <v>2632</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="I138" s="10" t="n"/>
+      <c r="J138" s="10" t="n"/>
+      <c r="K138" s="10" t="n"/>
       <c r="L138" s="10" t="s">
-        <v>2611</v>
+        <v>2633</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>2612</v>
-      </c>
-      <c r="N138" s="10" t="s"/>
-      <c r="O138" s="10" t="s"/>
-      <c r="P138" s="10" t="s"/>
-      <c r="Q138" s="10" t="s"/>
-      <c r="R138" s="10" t="s"/>
+        <v>2634</v>
+      </c>
+      <c r="N138" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O138" s="10" t="s">
+        <v>2635</v>
+      </c>
+      <c r="P138" s="10" t="s">
+        <v>2636</v>
+      </c>
+      <c r="Q138" s="10" t="s">
+        <v>2637</v>
+      </c>
+      <c r="R138" s="10" t="s">
+        <v>2638</v>
+      </c>
       <c r="S138" s="10" t="s">
-        <v>2613</v>
+        <v>2639</v>
       </c>
       <c r="T138" s="10" t="s">
-        <v>2614</v>
-      </c>
-      <c r="U138" s="10" t="s"/>
+        <v>2640</v>
+      </c>
+      <c r="U138" s="10" t="s">
+        <v>2641</v>
+      </c>
       <c r="V138" s="10" t="s">
-        <v>2615</v>
+        <v>2642</v>
       </c>
       <c r="W138" s="10" t="s">
-        <v>2616</v>
-      </c>
-      <c r="X138" s="10" t="s"/>
-      <c r="Y138" s="10" t="s"/>
+        <v>2643</v>
+      </c>
+      <c r="X138" s="10" t="s">
+        <v>2644</v>
+      </c>
+      <c r="Y138" s="10" t="s">
+        <v>2645</v>
+      </c>
       <c r="Z138" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA138" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA138" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="139" spans="1:27"/>
     <row r="140" spans="1:27"/>
@@ -20762,51 +21143,77 @@
         <v>129</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>2617</v>
-      </c>
-      <c r="C143" s="10" t="s"/>
-      <c r="D143" s="10" t="s"/>
-      <c r="E143" s="10" t="s"/>
-      <c r="F143" s="10" t="s"/>
+        <v>2646</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>2648</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>2649</v>
+      </c>
       <c r="G143" s="10" t="s">
-        <v>2618</v>
-      </c>
-      <c r="H143" s="10" t="s"/>
-      <c r="I143" s="10" t="s"/>
-      <c r="J143" s="10" t="s"/>
-      <c r="K143" s="10" t="s"/>
+        <v>2650</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I143" s="10" t="n"/>
+      <c r="J143" s="10" t="n"/>
+      <c r="K143" s="10" t="n"/>
       <c r="L143" s="10" t="s">
-        <v>2619</v>
+        <v>2652</v>
       </c>
       <c r="M143" s="11" t="s">
-        <v>2620</v>
-      </c>
-      <c r="N143" s="10" t="s"/>
-      <c r="O143" s="10" t="s"/>
-      <c r="P143" s="10" t="s"/>
-      <c r="Q143" s="10" t="s"/>
-      <c r="R143" s="10" t="s"/>
+        <v>2653</v>
+      </c>
+      <c r="N143" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O143" s="10" t="s">
+        <v>2654</v>
+      </c>
+      <c r="P143" s="10" t="s">
+        <v>2655</v>
+      </c>
+      <c r="Q143" s="10" t="s">
+        <v>2656</v>
+      </c>
+      <c r="R143" s="10" t="s">
+        <v>2657</v>
+      </c>
       <c r="S143" s="10" t="s">
-        <v>2621</v>
+        <v>2658</v>
       </c>
       <c r="T143" s="10" t="s">
-        <v>2622</v>
+        <v>2659</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>2623</v>
+        <v>2660</v>
       </c>
       <c r="V143" s="10" t="s">
-        <v>2624</v>
+        <v>2661</v>
       </c>
       <c r="W143" s="10" t="s">
-        <v>2625</v>
-      </c>
-      <c r="X143" s="10" t="s"/>
-      <c r="Y143" s="10" t="s"/>
+        <v>2662</v>
+      </c>
+      <c r="X143" s="10" t="s">
+        <v>2663</v>
+      </c>
+      <c r="Y143" s="10" t="s">
+        <v>2664</v>
+      </c>
       <c r="Z143" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA143" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA143" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="144" spans="1:27"/>
     <row r="145" spans="1:27"/>
@@ -20818,51 +21225,77 @@
         <v>130</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>2626</v>
-      </c>
-      <c r="C149" s="10" t="s"/>
-      <c r="D149" s="10" t="s"/>
-      <c r="E149" s="10" t="s"/>
-      <c r="F149" s="10" t="s"/>
+        <v>2665</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>2668</v>
+      </c>
       <c r="G149" s="10" t="s">
-        <v>2627</v>
-      </c>
-      <c r="H149" s="10" t="s"/>
-      <c r="I149" s="10" t="s"/>
-      <c r="J149" s="10" t="s"/>
-      <c r="K149" s="10" t="s"/>
+        <v>2669</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I149" s="10" t="n"/>
+      <c r="J149" s="10" t="n"/>
+      <c r="K149" s="10" t="n"/>
       <c r="L149" s="10" t="s">
-        <v>2628</v>
+        <v>2670</v>
       </c>
       <c r="M149" s="11" t="s">
-        <v>2629</v>
-      </c>
-      <c r="N149" s="10" t="s"/>
-      <c r="O149" s="10" t="s"/>
+        <v>2671</v>
+      </c>
+      <c r="N149" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O149" s="10" t="s">
+        <v>2672</v>
+      </c>
       <c r="P149" s="10" t="s">
-        <v>2630</v>
-      </c>
-      <c r="Q149" s="10" t="s"/>
-      <c r="R149" s="10" t="s"/>
+        <v>2673</v>
+      </c>
+      <c r="Q149" s="10" t="s">
+        <v>2674</v>
+      </c>
+      <c r="R149" s="10" t="s">
+        <v>2675</v>
+      </c>
       <c r="S149" s="10" t="s">
-        <v>2631</v>
+        <v>2676</v>
       </c>
       <c r="T149" s="10" t="s">
-        <v>2632</v>
-      </c>
-      <c r="U149" s="10" t="s"/>
+        <v>2677</v>
+      </c>
+      <c r="U149" s="10" t="s">
+        <v>2678</v>
+      </c>
       <c r="V149" s="10" t="s">
-        <v>2633</v>
+        <v>2679</v>
       </c>
       <c r="W149" s="10" t="s">
-        <v>2634</v>
-      </c>
-      <c r="X149" s="10" t="s"/>
-      <c r="Y149" s="10" t="s"/>
+        <v>2680</v>
+      </c>
+      <c r="X149" s="10" t="s">
+        <v>2681</v>
+      </c>
+      <c r="Y149" s="10" t="s">
+        <v>2682</v>
+      </c>
       <c r="Z149" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA149" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA149" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="150" spans="1:27"/>
     <row r="151" spans="1:27"/>
@@ -20875,51 +21308,83 @@
         <v>131</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>2635</v>
-      </c>
-      <c r="C156" s="10" t="s"/>
-      <c r="D156" s="10" t="s"/>
-      <c r="E156" s="10" t="s"/>
-      <c r="F156" s="10" t="s"/>
+        <v>2683</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>2686</v>
+      </c>
       <c r="G156" s="10" t="s">
-        <v>2636</v>
-      </c>
-      <c r="H156" s="10" t="s"/>
-      <c r="I156" s="10" t="s"/>
-      <c r="J156" s="10" t="s"/>
-      <c r="K156" s="10" t="s"/>
+        <v>2687</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>2063</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="K156" s="10" t="s">
+        <v>2688</v>
+      </c>
       <c r="L156" s="10" t="s">
-        <v>2637</v>
+        <v>2689</v>
       </c>
       <c r="M156" s="11" t="s">
-        <v>2638</v>
-      </c>
-      <c r="N156" s="10" t="s"/>
-      <c r="O156" s="10" t="s"/>
-      <c r="P156" s="10" t="s"/>
-      <c r="Q156" s="10" t="s"/>
-      <c r="R156" s="10" t="s"/>
+        <v>2690</v>
+      </c>
+      <c r="N156" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O156" s="10" t="s">
+        <v>2691</v>
+      </c>
+      <c r="P156" s="10" t="s">
+        <v>2692</v>
+      </c>
+      <c r="Q156" s="10" t="s">
+        <v>2693</v>
+      </c>
+      <c r="R156" s="10" t="s">
+        <v>2694</v>
+      </c>
       <c r="S156" s="10" t="s">
-        <v>2639</v>
+        <v>2695</v>
       </c>
       <c r="T156" s="10" t="s">
-        <v>2640</v>
+        <v>2696</v>
       </c>
       <c r="U156" s="10" t="s">
-        <v>2641</v>
+        <v>2697</v>
       </c>
       <c r="V156" s="10" t="s">
-        <v>2642</v>
-      </c>
-      <c r="W156" s="10" t="s"/>
+        <v>2698</v>
+      </c>
+      <c r="W156" s="10" t="s">
+        <v>2699</v>
+      </c>
       <c r="X156" s="10" t="s">
-        <v>2643</v>
-      </c>
-      <c r="Y156" s="10" t="s"/>
+        <v>2699</v>
+      </c>
+      <c r="Y156" s="10" t="s">
+        <v>2700</v>
+      </c>
       <c r="Z156" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA156" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA156" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="157" spans="1:27"/>
     <row r="158" spans="1:27"/>
@@ -20933,21 +21398,25 @@
         <v>132</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>2644</v>
-      </c>
-      <c r="C164" s="10" t="s"/>
-      <c r="D164" s="10" t="s"/>
+        <v>2701</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>2702</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>2703</v>
+      </c>
       <c r="E164" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>2645</v>
+        <v>2704</v>
       </c>
       <c r="G164" s="10" t="s">
-        <v>2646</v>
+        <v>2705</v>
       </c>
       <c r="H164" s="10" t="s">
-        <v>2577</v>
+        <v>34</v>
       </c>
       <c r="I164" s="10" t="s">
         <v>35</v>
@@ -20956,36 +21425,56 @@
         <v>27</v>
       </c>
       <c r="K164" s="10" t="s">
-        <v>2647</v>
+        <v>2706</v>
       </c>
       <c r="L164" s="10" t="s">
-        <v>2648</v>
+        <v>2707</v>
       </c>
       <c r="M164" s="11" t="s">
-        <v>2649</v>
-      </c>
-      <c r="N164" s="10" t="s"/>
-      <c r="O164" s="10" t="s"/>
-      <c r="P164" s="10" t="s"/>
-      <c r="Q164" s="10" t="s"/>
-      <c r="R164" s="10" t="s"/>
-      <c r="S164" s="10" t="s"/>
-      <c r="T164" s="10" t="s"/>
+        <v>2708</v>
+      </c>
+      <c r="N164" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O164" s="10" t="s">
+        <v>2709</v>
+      </c>
+      <c r="P164" s="10" t="s">
+        <v>2710</v>
+      </c>
+      <c r="Q164" s="10" t="s">
+        <v>2469</v>
+      </c>
+      <c r="R164" s="10" t="s">
+        <v>2711</v>
+      </c>
+      <c r="S164" s="10" t="s">
+        <v>2712</v>
+      </c>
+      <c r="T164" s="10" t="s">
+        <v>2713</v>
+      </c>
       <c r="U164" s="10" t="s">
-        <v>2650</v>
+        <v>2714</v>
       </c>
       <c r="V164" s="10" t="s">
-        <v>2651</v>
-      </c>
-      <c r="W164" s="10" t="s"/>
+        <v>2715</v>
+      </c>
+      <c r="W164" s="10" t="s">
+        <v>2716</v>
+      </c>
       <c r="X164" s="10" t="s">
-        <v>2652</v>
-      </c>
-      <c r="Y164" s="10" t="s"/>
+        <v>2716</v>
+      </c>
+      <c r="Y164" s="10" t="s">
+        <v>2717</v>
+      </c>
       <c r="Z164" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA164" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA164" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="165" spans="1:27"/>
     <row r="166" spans="1:27"/>
@@ -21000,43 +21489,81 @@
         <v>133</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>2653</v>
-      </c>
-      <c r="C173" s="10" t="s"/>
-      <c r="D173" s="10" t="s"/>
-      <c r="E173" s="10" t="s"/>
-      <c r="F173" s="10" t="s"/>
+        <v>2718</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>2720</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>2721</v>
+      </c>
       <c r="G173" s="10" t="s">
-        <v>2654</v>
-      </c>
-      <c r="H173" s="10" t="s"/>
-      <c r="I173" s="10" t="s"/>
-      <c r="J173" s="10" t="s"/>
-      <c r="K173" s="10" t="s"/>
-      <c r="L173" s="10" t="s"/>
+        <v>2722</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I173" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="J173" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K173" s="10" t="s">
+        <v>2724</v>
+      </c>
+      <c r="L173" s="10" t="n"/>
       <c r="M173" s="11" t="s">
-        <v>2655</v>
-      </c>
-      <c r="N173" s="10" t="s"/>
-      <c r="O173" s="10" t="s"/>
-      <c r="P173" s="10" t="s"/>
-      <c r="Q173" s="10" t="s"/>
-      <c r="R173" s="10" t="s"/>
-      <c r="S173" s="10" t="s"/>
-      <c r="T173" s="10" t="s"/>
+        <v>2725</v>
+      </c>
+      <c r="N173" s="10" t="s">
+        <v>2726</v>
+      </c>
+      <c r="O173" s="10" t="s">
+        <v>2727</v>
+      </c>
+      <c r="P173" s="10" t="s">
+        <v>2728</v>
+      </c>
+      <c r="Q173" s="10" t="s">
+        <v>2729</v>
+      </c>
+      <c r="R173" s="10" t="s">
+        <v>2730</v>
+      </c>
+      <c r="S173" s="10" t="s">
+        <v>2731</v>
+      </c>
+      <c r="T173" s="10" t="s">
+        <v>2732</v>
+      </c>
       <c r="U173" s="10" t="s">
-        <v>2656</v>
+        <v>2733</v>
       </c>
       <c r="V173" s="10" t="s">
-        <v>2657</v>
-      </c>
-      <c r="W173" s="10" t="s"/>
-      <c r="X173" s="10" t="s"/>
-      <c r="Y173" s="10" t="s"/>
+        <v>2734</v>
+      </c>
+      <c r="W173" s="10" t="s">
+        <v>2735</v>
+      </c>
+      <c r="X173" s="10" t="s">
+        <v>2736</v>
+      </c>
+      <c r="Y173" s="10" t="s">
+        <v>2737</v>
+      </c>
       <c r="Z173" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA173" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA173" s="10" t="s">
+        <v>2738</v>
+      </c>
     </row>
     <row r="174" spans="1:27"/>
     <row r="175" spans="1:27"/>
@@ -21052,51 +21579,83 @@
         <v>134</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C183" s="10" t="s"/>
-      <c r="D183" s="10" t="s"/>
-      <c r="E183" s="10" t="s"/>
-      <c r="F183" s="10" t="s"/>
+        <v>2739</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>2742</v>
+      </c>
+      <c r="F183" s="10" t="s">
+        <v>2743</v>
+      </c>
       <c r="G183" s="10" t="s">
-        <v>2659</v>
-      </c>
-      <c r="H183" s="10" t="s"/>
-      <c r="I183" s="10" t="s"/>
-      <c r="J183" s="10" t="s"/>
-      <c r="K183" s="10" t="s"/>
+        <v>2744</v>
+      </c>
+      <c r="H183" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I183" s="10" t="s">
+        <v>2745</v>
+      </c>
+      <c r="J183" s="10" t="s">
+        <v>2746</v>
+      </c>
+      <c r="K183" s="10" t="s">
+        <v>2747</v>
+      </c>
       <c r="L183" s="10" t="s">
-        <v>2660</v>
+        <v>2748</v>
       </c>
       <c r="M183" s="11" t="s">
-        <v>2661</v>
-      </c>
-      <c r="N183" s="10" t="s"/>
-      <c r="O183" s="10" t="s"/>
-      <c r="P183" s="10" t="s"/>
-      <c r="Q183" s="10" t="s"/>
-      <c r="R183" s="10" t="s"/>
+        <v>2749</v>
+      </c>
+      <c r="N183" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O183" s="10" t="s">
+        <v>2750</v>
+      </c>
+      <c r="P183" s="10" t="s">
+        <v>2751</v>
+      </c>
+      <c r="Q183" s="10" t="s">
+        <v>2752</v>
+      </c>
+      <c r="R183" s="10" t="s">
+        <v>2753</v>
+      </c>
       <c r="S183" s="10" t="s">
-        <v>2662</v>
+        <v>2754</v>
       </c>
       <c r="T183" s="10" t="s">
-        <v>2663</v>
+        <v>2755</v>
       </c>
       <c r="U183" s="10" t="s">
-        <v>2664</v>
+        <v>2756</v>
       </c>
       <c r="V183" s="10" t="s">
-        <v>2665</v>
+        <v>2757</v>
       </c>
       <c r="W183" s="10" t="s">
-        <v>2666</v>
-      </c>
-      <c r="X183" s="10" t="s"/>
-      <c r="Y183" s="10" t="s"/>
+        <v>2758</v>
+      </c>
+      <c r="X183" s="10" t="s">
+        <v>2759</v>
+      </c>
+      <c r="Y183" s="10" t="s">
+        <v>2760</v>
+      </c>
       <c r="Z183" s="10" t="s">
-        <v>2536</v>
-      </c>
-      <c r="AA183" s="10" t="s"/>
+        <v>52</v>
+      </c>
+      <c r="AA183" s="10" t="s">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21125,13 +21684,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>2667</v>
+        <v>2761</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2668</v>
+        <v>2762</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2669</v>
+        <v>2763</v>
       </c>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
@@ -21139,13 +21698,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>2670</v>
+        <v>2764</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>134</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2671</v>
+        <v>2765</v>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
@@ -21153,13 +21712,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>2672</v>
+        <v>2766</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2673</v>
+        <v>2767</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -21167,13 +21726,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>2674</v>
+        <v>2768</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2675</v>
+        <v>2769</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2676</v>
+        <v>2770</v>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
@@ -21181,13 +21740,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>2677</v>
+        <v>2771</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2678</v>
+        <v>2772</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2679</v>
+        <v>2773</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
@@ -21195,13 +21754,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>2680</v>
+        <v>2774</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2681</v>
+        <v>2775</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2682</v>
+        <v>2776</v>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
@@ -21220,14 +21779,14 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2683</v>
+        <v>2777</v>
       </c>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2683</v>
+        <v>2777</v>
       </c>
       <c r="F8" s="3" t="n"/>
     </row>
@@ -21265,7 +21824,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>2684</v>
+        <v>2778</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -21281,7 +21840,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>2685</v>
+        <v>2779</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -21297,7 +21856,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>2686</v>
+        <v>2780</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -24241,190 +24800,190 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>2577</v>
+        <v>2781</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="G110" s="12" t="s">
-        <v>2580</v>
-      </c>
-      <c r="H110" s="12" t="s"/>
+        <v>2581</v>
+      </c>
+      <c r="H110" s="12" t="n"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="12" t="n">
         <v>126</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>2589</v>
+        <v>2595</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>2577</v>
+        <v>2781</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>2592</v>
+        <v>2598</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>2593</v>
-      </c>
-      <c r="H111" s="12" t="s"/>
+        <v>2599</v>
+      </c>
+      <c r="H111" s="12" t="n"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="12" t="n">
         <v>127</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>2600</v>
-      </c>
-      <c r="C112" s="12" t="s"/>
-      <c r="D112" s="12" t="s"/>
-      <c r="E112" s="12" t="s"/>
+        <v>2610</v>
+      </c>
+      <c r="C112" s="12" t="n"/>
+      <c r="D112" s="12" t="n"/>
+      <c r="E112" s="12" t="n"/>
       <c r="F112" s="12" t="s">
-        <v>2602</v>
+        <v>2615</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>2603</v>
-      </c>
-      <c r="H112" s="12" t="s"/>
+        <v>2616</v>
+      </c>
+      <c r="H112" s="12" t="n"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="12" t="n">
         <v>128</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>2609</v>
-      </c>
-      <c r="C113" s="12" t="s"/>
-      <c r="D113" s="12" t="s"/>
-      <c r="E113" s="12" t="s"/>
+        <v>2628</v>
+      </c>
+      <c r="C113" s="12" t="n"/>
+      <c r="D113" s="12" t="n"/>
+      <c r="E113" s="12" t="n"/>
       <c r="F113" s="12" t="s">
-        <v>2611</v>
+        <v>2633</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>2612</v>
-      </c>
-      <c r="H113" s="12" t="s"/>
+        <v>2634</v>
+      </c>
+      <c r="H113" s="12" t="n"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="12" t="n">
         <v>129</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>2617</v>
-      </c>
-      <c r="C114" s="12" t="s"/>
-      <c r="D114" s="12" t="s"/>
-      <c r="E114" s="12" t="s"/>
+        <v>2646</v>
+      </c>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="12" t="n"/>
       <c r="F114" s="12" t="s">
-        <v>2619</v>
+        <v>2652</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>2620</v>
-      </c>
-      <c r="H114" s="12" t="s"/>
+        <v>2653</v>
+      </c>
+      <c r="H114" s="12" t="n"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="12" t="n">
         <v>130</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>2626</v>
-      </c>
-      <c r="C115" s="12" t="s"/>
-      <c r="D115" s="12" t="s"/>
-      <c r="E115" s="12" t="s"/>
+        <v>2665</v>
+      </c>
+      <c r="C115" s="12" t="n"/>
+      <c r="D115" s="12" t="n"/>
+      <c r="E115" s="12" t="n"/>
       <c r="F115" s="12" t="s">
-        <v>2628</v>
+        <v>2670</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>2629</v>
-      </c>
-      <c r="H115" s="12" t="s"/>
+        <v>2671</v>
+      </c>
+      <c r="H115" s="12" t="n"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="12" t="n">
         <v>131</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>2635</v>
-      </c>
-      <c r="C116" s="12" t="s"/>
-      <c r="D116" s="12" t="s"/>
-      <c r="E116" s="12" t="s"/>
+        <v>2683</v>
+      </c>
+      <c r="C116" s="12" t="n"/>
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="12" t="n"/>
       <c r="F116" s="12" t="s">
-        <v>2637</v>
+        <v>2689</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>2638</v>
-      </c>
-      <c r="H116" s="12" t="s"/>
+        <v>2690</v>
+      </c>
+      <c r="H116" s="12" t="n"/>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="12" t="n">
         <v>132</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>2644</v>
+        <v>2701</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>2645</v>
+        <v>2704</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>2577</v>
+        <v>2781</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>2648</v>
+        <v>2707</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>2649</v>
-      </c>
-      <c r="H117" s="12" t="s"/>
+        <v>2708</v>
+      </c>
+      <c r="H117" s="12" t="n"/>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="12" t="n">
         <v>133</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>2653</v>
-      </c>
-      <c r="C118" s="12" t="s"/>
-      <c r="D118" s="12" t="s"/>
-      <c r="E118" s="12" t="s"/>
-      <c r="F118" s="12" t="s"/>
+        <v>2718</v>
+      </c>
+      <c r="C118" s="12" t="n"/>
+      <c r="D118" s="12" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="12" t="n"/>
       <c r="G118" s="12" t="s">
-        <v>2655</v>
-      </c>
-      <c r="H118" s="12" t="s"/>
+        <v>2725</v>
+      </c>
+      <c r="H118" s="12" t="n"/>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="12" t="n">
         <v>134</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C119" s="12" t="s"/>
-      <c r="D119" s="12" t="s"/>
-      <c r="E119" s="12" t="s"/>
+        <v>2739</v>
+      </c>
+      <c r="C119" s="12" t="n"/>
+      <c r="D119" s="12" t="n"/>
+      <c r="E119" s="12" t="n"/>
       <c r="F119" s="12" t="s">
-        <v>2660</v>
+        <v>2748</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>2661</v>
-      </c>
-      <c r="H119" s="12" t="s"/>
+        <v>2749</v>
+      </c>
+      <c r="H119" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -24449,10 +25008,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>2687</v>
+        <v>2782</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2669</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -24460,7 +25019,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2688</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -24468,7 +25027,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2689</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -24476,7 +25035,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2690</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -24484,7 +25043,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2691</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -24492,7 +25051,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2692</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -24500,7 +25059,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2693</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -24508,7 +25067,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2694</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -24516,15 +25075,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2695</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>2696</v>
+        <v>2791</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2697</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -24532,7 +25091,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2698</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -24540,7 +25099,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2699</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -24548,7 +25107,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2700</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -24556,7 +25115,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2701</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -24564,7 +25123,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2702</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -24572,7 +25131,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2703</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -24580,7 +25139,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2704</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -24588,7 +25147,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2705</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -24596,7 +25155,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2706</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -24604,7 +25163,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2707</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -24612,7 +25171,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2708</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -24620,7 +25179,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2709</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -24628,7 +25187,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2710</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -24636,7 +25195,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2711</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -24644,7 +25203,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2712</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -24652,7 +25211,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2713</v>
+        <v>2808</v>
       </c>
     </row>
   </sheetData>
@@ -24691,22 +25250,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2714</v>
+        <v>2809</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2715</v>
+        <v>2810</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2716</v>
+        <v>2811</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2717</v>
+        <v>2812</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2718</v>
+        <v>2813</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>20</v>
@@ -24715,16 +25274,16 @@
         <v>21</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>2719</v>
+        <v>2814</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>2720</v>
+        <v>2815</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>2721</v>
+        <v>2816</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="2" spans="1:14">
@@ -24738,10 +25297,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2722</v>
+        <v>2817</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2723</v>
+        <v>2818</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>44</v>
@@ -24768,7 +25327,7 @@
         <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="3" spans="1:14">
@@ -24782,10 +25341,10 @@
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2725</v>
+        <v>2820</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2726</v>
+        <v>2821</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>68</v>
@@ -24812,7 +25371,7 @@
         <v>52</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="4" spans="1:14">
@@ -24826,10 +25385,10 @@
         <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2727</v>
+        <v>2822</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2728</v>
+        <v>2823</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>92</v>
@@ -24856,7 +25415,7 @@
         <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="5" spans="1:14">
@@ -24870,10 +25429,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2729</v>
+        <v>2824</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2730</v>
+        <v>2825</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>115</v>
@@ -24900,7 +25459,7 @@
         <v>52</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="6" spans="1:14">
@@ -24914,10 +25473,10 @@
         <v>128</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2731</v>
+        <v>2826</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2732</v>
+        <v>2827</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>137</v>
@@ -24944,7 +25503,7 @@
         <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="7" spans="1:14">
@@ -24958,10 +25517,10 @@
         <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2733</v>
+        <v>2828</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2734</v>
+        <v>2829</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>160</v>
@@ -24988,7 +25547,7 @@
         <v>145</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="8" spans="1:14">
@@ -25002,10 +25561,10 @@
         <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2735</v>
+        <v>2830</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2736</v>
+        <v>2831</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>181</v>
@@ -25032,7 +25591,7 @@
         <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:14">
@@ -25046,10 +25605,10 @@
         <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2737</v>
+        <v>2832</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2738</v>
+        <v>2833</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>201</v>
@@ -25076,7 +25635,7 @@
         <v>145</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="10" spans="1:14">
@@ -25090,10 +25649,10 @@
         <v>214</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2739</v>
+        <v>2834</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2740</v>
+        <v>2835</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>220</v>
@@ -25120,7 +25679,7 @@
         <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:14">
@@ -25134,10 +25693,10 @@
         <v>233</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2741</v>
+        <v>2836</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2742</v>
+        <v>2837</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>239</v>
@@ -25164,7 +25723,7 @@
         <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:14">
@@ -25178,10 +25737,10 @@
         <v>252</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2743</v>
+        <v>2838</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2744</v>
+        <v>2839</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>258</v>
@@ -25208,7 +25767,7 @@
         <v>145</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="13" spans="1:14">
@@ -25222,10 +25781,10 @@
         <v>272</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2745</v>
+        <v>2840</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2746</v>
+        <v>2841</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>278</v>
@@ -25252,7 +25811,7 @@
         <v>52</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="14" spans="1:14">
@@ -25266,10 +25825,10 @@
         <v>291</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2747</v>
+        <v>2842</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2748</v>
+        <v>2843</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>300</v>
@@ -25296,7 +25855,7 @@
         <v>145</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:14">
@@ -25310,10 +25869,10 @@
         <v>313</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2749</v>
+        <v>2844</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2750</v>
+        <v>2845</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>321</v>
@@ -25340,7 +25899,7 @@
         <v>52</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="16" spans="1:14">
@@ -25354,10 +25913,10 @@
         <v>334</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2751</v>
+        <v>2846</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2752</v>
+        <v>2847</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>343</v>
@@ -25384,7 +25943,7 @@
         <v>52</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:14">
@@ -25398,10 +25957,10 @@
         <v>356</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2753</v>
+        <v>2848</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2754</v>
+        <v>2849</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>363</v>
@@ -25428,7 +25987,7 @@
         <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="18" spans="1:14">
@@ -25442,10 +26001,10 @@
         <v>376</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2755</v>
+        <v>2850</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2756</v>
+        <v>2851</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>383</v>
@@ -25472,7 +26031,7 @@
         <v>145</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="19" spans="1:14">
@@ -25486,10 +26045,10 @@
         <v>397</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2757</v>
+        <v>2852</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2758</v>
+        <v>2853</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>404</v>
@@ -25516,7 +26075,7 @@
         <v>145</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="20" spans="1:14">
@@ -25530,10 +26089,10 @@
         <v>418</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2759</v>
+        <v>2854</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2760</v>
+        <v>2855</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>427</v>
@@ -25560,7 +26119,7 @@
         <v>145</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="21" spans="1:14">
@@ -25574,10 +26133,10 @@
         <v>441</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2761</v>
+        <v>2856</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2762</v>
+        <v>2857</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>448</v>
@@ -25604,7 +26163,7 @@
         <v>145</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="22" spans="1:14">
@@ -25618,10 +26177,10 @@
         <v>462</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2763</v>
+        <v>2858</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2764</v>
+        <v>2859</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>467</v>
@@ -25648,7 +26207,7 @@
         <v>52</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="23" spans="1:14">
@@ -25662,10 +26221,10 @@
         <v>481</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2765</v>
+        <v>2860</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2766</v>
+        <v>2861</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>489</v>
@@ -25692,7 +26251,7 @@
         <v>145</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="24" spans="1:14">
@@ -25706,10 +26265,10 @@
         <v>503</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2767</v>
+        <v>2862</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2768</v>
+        <v>2863</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>511</v>
@@ -25736,7 +26295,7 @@
         <v>52</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="25" spans="1:14">
@@ -25750,10 +26309,10 @@
         <v>524</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2769</v>
+        <v>2864</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2770</v>
+        <v>2865</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>532</v>
@@ -25780,7 +26339,7 @@
         <v>145</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="26" spans="1:14">
@@ -25794,10 +26353,10 @@
         <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2771</v>
+        <v>2866</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2772</v>
+        <v>2867</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>554</v>
@@ -25824,7 +26383,7 @@
         <v>52</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="27" spans="1:14">
@@ -25838,10 +26397,10 @@
         <v>568</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2773</v>
+        <v>2868</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2774</v>
+        <v>2869</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>577</v>
@@ -25868,7 +26427,7 @@
         <v>52</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="28" spans="1:14">
@@ -25882,10 +26441,10 @@
         <v>591</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2775</v>
+        <v>2870</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2776</v>
+        <v>2871</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>600</v>
@@ -25912,7 +26471,7 @@
         <v>52</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="29" spans="1:14">
@@ -25926,10 +26485,10 @@
         <v>614</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2777</v>
+        <v>2872</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2778</v>
+        <v>2873</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>623</v>
@@ -25956,7 +26515,7 @@
         <v>52</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="30" spans="1:14">
@@ -25970,10 +26529,10 @@
         <v>637</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2779</v>
+        <v>2874</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2780</v>
+        <v>2875</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>646</v>
@@ -26000,7 +26559,7 @@
         <v>52</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="31" spans="1:14">
@@ -26014,10 +26573,10 @@
         <v>659</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2781</v>
+        <v>2876</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2782</v>
+        <v>2877</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>668</v>
@@ -26044,7 +26603,7 @@
         <v>52</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="32" spans="1:14">
@@ -26058,10 +26617,10 @@
         <v>682</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2783</v>
+        <v>2878</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2784</v>
+        <v>2879</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>689</v>
@@ -26088,7 +26647,7 @@
         <v>52</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="33" spans="1:14">
@@ -26102,10 +26661,10 @@
         <v>702</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2785</v>
+        <v>2880</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2786</v>
+        <v>2881</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>709</v>
@@ -26132,7 +26691,7 @@
         <v>145</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="34" spans="1:14">
@@ -26146,10 +26705,10 @@
         <v>722</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2787</v>
+        <v>2882</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2788</v>
+        <v>2883</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>731</v>
@@ -26176,7 +26735,7 @@
         <v>52</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="35" spans="1:14">
@@ -26190,10 +26749,10 @@
         <v>744</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2789</v>
+        <v>2884</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2790</v>
+        <v>2885</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>751</v>
@@ -26220,7 +26779,7 @@
         <v>52</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="36" spans="1:14">
@@ -26234,10 +26793,10 @@
         <v>764</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2791</v>
+        <v>2886</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2792</v>
+        <v>2887</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>772</v>
@@ -26264,7 +26823,7 @@
         <v>145</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="37" spans="1:14">
@@ -26278,10 +26837,10 @@
         <v>785</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2793</v>
+        <v>2888</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2794</v>
+        <v>2889</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>792</v>
@@ -26308,7 +26867,7 @@
         <v>145</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="38" spans="1:14">
@@ -26322,10 +26881,10 @@
         <v>806</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2795</v>
+        <v>2890</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2796</v>
+        <v>2891</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>814</v>
@@ -26352,7 +26911,7 @@
         <v>145</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="39" spans="1:14">
@@ -26366,10 +26925,10 @@
         <v>827</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2797</v>
+        <v>2892</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2798</v>
+        <v>2893</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>834</v>
@@ -26396,7 +26955,7 @@
         <v>145</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="40" spans="1:14">
@@ -26410,10 +26969,10 @@
         <v>848</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2799</v>
+        <v>2894</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2800</v>
+        <v>2895</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>856</v>
@@ -26440,7 +26999,7 @@
         <v>52</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="41" spans="1:14">
@@ -26454,10 +27013,10 @@
         <v>870</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2801</v>
+        <v>2896</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2802</v>
+        <v>2897</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>878</v>
@@ -26484,7 +27043,7 @@
         <v>52</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="42" spans="1:14">
@@ -26498,10 +27057,10 @@
         <v>891</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2803</v>
+        <v>2898</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2804</v>
+        <v>2899</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>901</v>
@@ -26528,7 +27087,7 @@
         <v>52</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="43" spans="1:14">
@@ -26542,10 +27101,10 @@
         <v>914</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2805</v>
+        <v>2900</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2806</v>
+        <v>2901</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>921</v>
@@ -26572,7 +27131,7 @@
         <v>52</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="44" spans="1:14">
@@ -26586,10 +27145,10 @@
         <v>933</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2807</v>
+        <v>2902</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2808</v>
+        <v>2903</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>940</v>
@@ -26616,7 +27175,7 @@
         <v>52</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="45" spans="1:14">
@@ -26630,10 +27189,10 @@
         <v>953</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2809</v>
+        <v>2904</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2810</v>
+        <v>2905</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>959</v>
@@ -26660,7 +27219,7 @@
         <v>52</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="46" spans="1:14">
@@ -26674,10 +27233,10 @@
         <v>972</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2811</v>
+        <v>2906</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2812</v>
+        <v>2907</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>978</v>
@@ -26704,7 +27263,7 @@
         <v>52</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="47" spans="1:14">
@@ -26718,10 +27277,10 @@
         <v>990</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2813</v>
+        <v>2908</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2814</v>
+        <v>2909</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>997</v>
@@ -26748,7 +27307,7 @@
         <v>52</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="48" spans="1:14">
@@ -26762,10 +27321,10 @@
         <v>1010</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2815</v>
+        <v>2910</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>2816</v>
+        <v>2911</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>1018</v>
@@ -26792,7 +27351,7 @@
         <v>52</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="49" spans="1:14">
@@ -26806,10 +27365,10 @@
         <v>1030</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2817</v>
+        <v>2912</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2818</v>
+        <v>2913</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>1037</v>
@@ -26836,7 +27395,7 @@
         <v>52</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="50" spans="1:14">
@@ -26850,10 +27409,10 @@
         <v>1049</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2819</v>
+        <v>2914</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2820</v>
+        <v>2915</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>1055</v>
@@ -26880,7 +27439,7 @@
         <v>189</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="51" spans="1:14">
@@ -26894,10 +27453,10 @@
         <v>1067</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2821</v>
+        <v>2916</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2822</v>
+        <v>2917</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>1072</v>
@@ -26924,7 +27483,7 @@
         <v>52</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="52" spans="1:14">
@@ -26938,10 +27497,10 @@
         <v>1084</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2823</v>
+        <v>2918</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2824</v>
+        <v>2919</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>1091</v>
@@ -26968,7 +27527,7 @@
         <v>189</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="53" spans="1:14">
@@ -26982,10 +27541,10 @@
         <v>1104</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2825</v>
+        <v>2920</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>2826</v>
+        <v>2921</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>1109</v>
@@ -27012,7 +27571,7 @@
         <v>145</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="54" spans="1:14">
@@ -27026,10 +27585,10 @@
         <v>1121</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2827</v>
+        <v>2922</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>2828</v>
+        <v>2923</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>1131</v>
@@ -27056,7 +27615,7 @@
         <v>52</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="55" spans="1:14">
@@ -27070,10 +27629,10 @@
         <v>1144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2829</v>
+        <v>2924</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>2830</v>
+        <v>2925</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>1151</v>
@@ -27100,7 +27659,7 @@
         <v>52</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="56" spans="1:14">
@@ -27114,10 +27673,10 @@
         <v>1165</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2831</v>
+        <v>2926</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2832</v>
+        <v>2927</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>1173</v>
@@ -27144,7 +27703,7 @@
         <v>52</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="57" spans="1:14">
@@ -27158,10 +27717,10 @@
         <v>1187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2833</v>
+        <v>2928</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>2834</v>
+        <v>2929</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>1195</v>
@@ -27188,7 +27747,7 @@
         <v>189</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="58" spans="1:14">
@@ -27202,10 +27761,10 @@
         <v>1209</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2835</v>
+        <v>2930</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>2836</v>
+        <v>2931</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>1217</v>
@@ -27232,7 +27791,7 @@
         <v>189</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="59" spans="1:14">
@@ -27246,10 +27805,10 @@
         <v>1231</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2837</v>
+        <v>2932</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>2838</v>
+        <v>2933</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>1239</v>
@@ -27276,7 +27835,7 @@
         <v>189</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="60" spans="1:14">
@@ -27290,10 +27849,10 @@
         <v>1252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2839</v>
+        <v>2934</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>2840</v>
+        <v>2935</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>1261</v>
@@ -27320,7 +27879,7 @@
         <v>52</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="61" spans="1:14">
@@ -27334,10 +27893,10 @@
         <v>1275</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>2841</v>
+        <v>2936</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>2842</v>
+        <v>2937</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>1283</v>
@@ -27364,7 +27923,7 @@
         <v>52</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="62" spans="1:14">
@@ -27378,10 +27937,10 @@
         <v>1297</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2843</v>
+        <v>2938</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2844</v>
+        <v>2939</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>1305</v>
@@ -27408,7 +27967,7 @@
         <v>145</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="63" spans="1:14">
@@ -27422,10 +27981,10 @@
         <v>1319</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2845</v>
+        <v>2940</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>2846</v>
+        <v>2941</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>1327</v>
@@ -27452,7 +28011,7 @@
         <v>189</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="64" spans="1:14">
@@ -27466,10 +28025,10 @@
         <v>1341</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>2847</v>
+        <v>2942</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>2848</v>
+        <v>2943</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>1348</v>
@@ -27496,7 +28055,7 @@
         <v>52</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="65" spans="1:14">
@@ -27510,10 +28069,10 @@
         <v>1361</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>2849</v>
+        <v>2944</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>2850</v>
+        <v>2945</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>1368</v>
@@ -27540,7 +28099,7 @@
         <v>52</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="66" spans="1:14">
@@ -27554,10 +28113,10 @@
         <v>1382</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>2851</v>
+        <v>2946</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>2852</v>
+        <v>2947</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>1389</v>
@@ -27584,7 +28143,7 @@
         <v>52</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="67" spans="1:14">
@@ -27598,10 +28157,10 @@
         <v>1403</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>2853</v>
+        <v>2948</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>2854</v>
+        <v>2949</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>1408</v>
@@ -27628,7 +28187,7 @@
         <v>52</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="68" spans="1:14">
@@ -27642,10 +28201,10 @@
         <v>1421</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>2855</v>
+        <v>2950</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>2856</v>
+        <v>2951</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>1428</v>
@@ -27672,7 +28231,7 @@
         <v>52</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="69" spans="1:14">
@@ -27686,10 +28245,10 @@
         <v>1442</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>2857</v>
+        <v>2952</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>2858</v>
+        <v>2953</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>1448</v>
@@ -27716,7 +28275,7 @@
         <v>52</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="70" spans="1:14">
@@ -27730,10 +28289,10 @@
         <v>1460</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>2859</v>
+        <v>2954</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>2860</v>
+        <v>2955</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>1466</v>
@@ -27760,7 +28319,7 @@
         <v>52</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="71" spans="1:14">
@@ -27774,10 +28333,10 @@
         <v>1480</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>2861</v>
+        <v>2956</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>2862</v>
+        <v>2957</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>1486</v>
@@ -27804,7 +28363,7 @@
         <v>52</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="72" spans="1:14">
@@ -27818,10 +28377,10 @@
         <v>1499</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>2863</v>
+        <v>2958</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>2864</v>
+        <v>2959</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>1505</v>
@@ -27848,7 +28407,7 @@
         <v>52</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="73" spans="1:14">
@@ -27862,10 +28421,10 @@
         <v>1518</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>2865</v>
+        <v>2960</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>2866</v>
+        <v>2961</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>1524</v>
@@ -27892,7 +28451,7 @@
         <v>145</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="74" spans="1:14">
@@ -27906,10 +28465,10 @@
         <v>1537</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>2867</v>
+        <v>2962</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>2868</v>
+        <v>2963</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>1544</v>
@@ -27936,7 +28495,7 @@
         <v>52</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="75" spans="1:14">
@@ -27950,10 +28509,10 @@
         <v>1556</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>2869</v>
+        <v>2964</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>2870</v>
+        <v>2965</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>1563</v>
@@ -27980,7 +28539,7 @@
         <v>52</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="76" spans="1:14">
@@ -27994,10 +28553,10 @@
         <v>1576</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>2871</v>
+        <v>2966</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>2872</v>
+        <v>2967</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>1583</v>
@@ -28024,7 +28583,7 @@
         <v>52</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="77" spans="1:14">
@@ -28038,10 +28597,10 @@
         <v>1596</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>2873</v>
+        <v>2968</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>2874</v>
+        <v>2969</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>1602</v>
@@ -28068,7 +28627,7 @@
         <v>52</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="78" spans="1:14">
@@ -28082,10 +28641,10 @@
         <v>1615</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>2875</v>
+        <v>2970</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>2876</v>
+        <v>2971</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>1621</v>
@@ -28112,7 +28671,7 @@
         <v>52</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="79" spans="1:14">
@@ -28126,10 +28685,10 @@
         <v>1634</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>2877</v>
+        <v>2972</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>2878</v>
+        <v>2973</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>1643</v>
@@ -28156,7 +28715,7 @@
         <v>145</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="80" spans="1:14">
@@ -28170,10 +28729,10 @@
         <v>1657</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>2879</v>
+        <v>2974</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>2880</v>
+        <v>2975</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>1665</v>
@@ -28200,7 +28759,7 @@
         <v>189</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="81" spans="1:14">
@@ -28214,10 +28773,10 @@
         <v>1678</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>2881</v>
+        <v>2976</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>2882</v>
+        <v>2977</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>1686</v>
@@ -28244,7 +28803,7 @@
         <v>52</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="82" spans="1:14">
@@ -28258,10 +28817,10 @@
         <v>1700</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>2883</v>
+        <v>2978</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>2884</v>
+        <v>2979</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>1708</v>
@@ -28288,7 +28847,7 @@
         <v>145</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="83" spans="1:14">
@@ -28302,10 +28861,10 @@
         <v>1721</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>2885</v>
+        <v>2980</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>2886</v>
+        <v>2981</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>1730</v>
@@ -28332,7 +28891,7 @@
         <v>52</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="84" spans="1:14">
@@ -28346,10 +28905,10 @@
         <v>1744</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>2887</v>
+        <v>2982</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>2888</v>
+        <v>2983</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>1751</v>
@@ -28376,7 +28935,7 @@
         <v>52</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="85" spans="1:14">
@@ -28390,10 +28949,10 @@
         <v>1765</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>2889</v>
+        <v>2984</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>2890</v>
+        <v>2985</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>1773</v>
@@ -28420,7 +28979,7 @@
         <v>145</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="86" spans="1:14">
@@ -28434,10 +28993,10 @@
         <v>1785</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>2891</v>
+        <v>2986</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>2892</v>
+        <v>2987</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>1793</v>
@@ -28464,7 +29023,7 @@
         <v>52</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="87" spans="1:14">
@@ -28478,10 +29037,10 @@
         <v>1806</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>2893</v>
+        <v>2988</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>2894</v>
+        <v>2989</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>1813</v>
@@ -28508,7 +29067,7 @@
         <v>145</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="88" spans="1:14">
@@ -28522,10 +29081,10 @@
         <v>1826</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>2895</v>
+        <v>2990</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>2896</v>
+        <v>2991</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>1834</v>
@@ -28552,7 +29111,7 @@
         <v>52</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="89" spans="1:14">
@@ -28566,10 +29125,10 @@
         <v>1846</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>2897</v>
+        <v>2992</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>2898</v>
+        <v>2993</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>1854</v>
@@ -28596,7 +29155,7 @@
         <v>52</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="90" spans="1:14">
@@ -28610,10 +29169,10 @@
         <v>1866</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>2899</v>
+        <v>2994</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>2900</v>
+        <v>2995</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>1873</v>
@@ -28640,7 +29199,7 @@
         <v>52</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="91" spans="1:14">
@@ -28654,10 +29213,10 @@
         <v>1884</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>2901</v>
+        <v>2996</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>2902</v>
+        <v>2997</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>1892</v>
@@ -28684,7 +29243,7 @@
         <v>145</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="92" spans="1:14">
@@ -28698,10 +29257,10 @@
         <v>1904</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>2903</v>
+        <v>2998</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>2904</v>
+        <v>2999</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>1912</v>
@@ -28728,7 +29287,7 @@
         <v>189</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="93" spans="1:14">
@@ -28742,10 +29301,10 @@
         <v>1923</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>2905</v>
+        <v>3000</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>2906</v>
+        <v>3001</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>1931</v>
@@ -28772,7 +29331,7 @@
         <v>52</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="94" spans="1:14">
@@ -28786,10 +29345,10 @@
         <v>1943</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>2907</v>
+        <v>3002</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>2908</v>
+        <v>3003</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>1950</v>
@@ -28816,7 +29375,7 @@
         <v>52</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="95" spans="1:14">
@@ -28830,10 +29389,10 @@
         <v>1961</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>2909</v>
+        <v>3004</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>2910</v>
+        <v>3005</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>1968</v>
@@ -28860,7 +29419,7 @@
         <v>52</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="96" spans="1:14">
@@ -28874,10 +29433,10 @@
         <v>1980</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>2911</v>
+        <v>3006</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>2912</v>
+        <v>3007</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>1988</v>
@@ -28904,7 +29463,7 @@
         <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="97" spans="1:14">
@@ -28918,10 +29477,10 @@
         <v>2000</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>2913</v>
+        <v>3008</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>2914</v>
+        <v>3009</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>2006</v>
@@ -28948,7 +29507,7 @@
         <v>52</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="98" spans="1:14">
@@ -28962,10 +29521,10 @@
         <v>2019</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>2915</v>
+        <v>3010</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>2916</v>
+        <v>3011</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>2028</v>
@@ -28992,7 +29551,7 @@
         <v>145</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="99" spans="1:14">
@@ -29006,10 +29565,10 @@
         <v>2041</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>2917</v>
+        <v>3012</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>2918</v>
+        <v>3013</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>2049</v>
@@ -29036,7 +29595,7 @@
         <v>145</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="100" spans="1:14">
@@ -29050,10 +29609,10 @@
         <v>2062</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>2919</v>
+        <v>3014</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>2920</v>
+        <v>3015</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>2069</v>
@@ -29080,7 +29639,7 @@
         <v>145</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="101" spans="1:14">
@@ -29094,10 +29653,10 @@
         <v>2082</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>2921</v>
+        <v>3016</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>2922</v>
+        <v>3017</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>2090</v>
@@ -29124,7 +29683,7 @@
         <v>52</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="102" spans="1:14">
@@ -29138,10 +29697,10 @@
         <v>2102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>2923</v>
+        <v>3018</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>2924</v>
+        <v>3019</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>2110</v>
@@ -29168,7 +29727,7 @@
         <v>145</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="103" spans="1:14">
@@ -29182,10 +29741,10 @@
         <v>2122</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>2925</v>
+        <v>3020</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>2926</v>
+        <v>3021</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>2129</v>
@@ -29212,7 +29771,7 @@
         <v>145</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="104" spans="1:14">
@@ -29226,10 +29785,10 @@
         <v>2142</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>2927</v>
+        <v>3022</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>2928</v>
+        <v>3023</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>2149</v>
@@ -29256,7 +29815,7 @@
         <v>145</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="105" spans="1:14">
@@ -29270,10 +29829,10 @@
         <v>2161</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>2929</v>
+        <v>3024</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>2930</v>
+        <v>3025</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>2168</v>
@@ -29300,7 +29859,7 @@
         <v>145</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="106" spans="1:14">
@@ -29314,10 +29873,10 @@
         <v>2181</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>2931</v>
+        <v>3026</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>2932</v>
+        <v>3027</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>2187</v>
@@ -29344,7 +29903,7 @@
         <v>189</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="107" spans="1:14">
@@ -29358,10 +29917,10 @@
         <v>2201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>2933</v>
+        <v>3028</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>2934</v>
+        <v>3029</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>2209</v>
@@ -29388,7 +29947,7 @@
         <v>145</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="108" spans="1:14">
@@ -29402,10 +29961,10 @@
         <v>2222</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>2935</v>
+        <v>3030</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>2936</v>
+        <v>3031</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>2228</v>
@@ -29432,7 +29991,7 @@
         <v>52</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="109" spans="1:14">
@@ -29446,10 +30005,10 @@
         <v>2241</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>2937</v>
+        <v>3032</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>2938</v>
+        <v>3033</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>2247</v>
@@ -29476,7 +30035,7 @@
         <v>52</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="110" spans="1:14">
@@ -29490,10 +30049,10 @@
         <v>2259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>2939</v>
+        <v>3034</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>2940</v>
+        <v>3035</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>2268</v>
@@ -29520,7 +30079,7 @@
         <v>145</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="111" spans="1:14">
@@ -29534,10 +30093,10 @@
         <v>2281</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>2941</v>
+        <v>3036</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>2942</v>
+        <v>3037</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>2289</v>
@@ -29564,7 +30123,7 @@
         <v>52</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="112" spans="1:14">
@@ -29578,10 +30137,10 @@
         <v>2302</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>2943</v>
+        <v>3038</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>2944</v>
+        <v>3039</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>2311</v>
@@ -29608,7 +30167,7 @@
         <v>145</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="113" spans="1:14">
@@ -29622,10 +30181,10 @@
         <v>2324</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>2945</v>
+        <v>3040</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>2946</v>
+        <v>3041</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>2331</v>
@@ -29652,7 +30211,7 @@
         <v>145</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="114" spans="1:14">
@@ -29666,10 +30225,10 @@
         <v>2343</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>2947</v>
+        <v>3042</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>2948</v>
+        <v>3043</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>2350</v>
@@ -29696,7 +30255,7 @@
         <v>145</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="115" spans="1:14">
@@ -29710,10 +30269,10 @@
         <v>2362</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>2949</v>
+        <v>3044</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>2950</v>
+        <v>3045</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>2369</v>
@@ -29740,7 +30299,7 @@
         <v>52</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="116" spans="1:14">
@@ -29754,10 +30313,10 @@
         <v>2381</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>2951</v>
+        <v>3046</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>2952</v>
+        <v>3047</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>2389</v>
@@ -29784,7 +30343,7 @@
         <v>145</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="117" spans="1:14">
@@ -29798,10 +30357,10 @@
         <v>2401</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>2953</v>
+        <v>3048</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>2954</v>
+        <v>3049</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>2410</v>
@@ -29828,7 +30387,7 @@
         <v>145</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="118" spans="1:14">
@@ -29842,10 +30401,10 @@
         <v>2423</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>2955</v>
+        <v>3050</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>2956</v>
+        <v>3051</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>2431</v>
@@ -29872,7 +30431,7 @@
         <v>145</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="119" spans="1:14">
@@ -29886,10 +30445,10 @@
         <v>2443</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>2957</v>
+        <v>3052</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>2958</v>
+        <v>3053</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>2450</v>
@@ -29916,7 +30475,7 @@
         <v>52</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>2724</v>
+        <v>2819</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="120" spans="1:14">
@@ -29930,10 +30489,10 @@
         <v>2462</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>2959</v>
+        <v>3054</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>2960</v>
+        <v>3055</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>2470</v>
@@ -29968,10 +30527,10 @@
         <v>2483</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>2961</v>
+        <v>3056</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>2962</v>
+        <v>3057</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>2492</v>
@@ -30006,10 +30565,10 @@
         <v>2503</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>2963</v>
+        <v>3058</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>2964</v>
+        <v>3059</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>2508</v>
@@ -30044,10 +30603,10 @@
         <v>2521</v>
       </c>
       <c r="D123" t="s">
-        <v>2965</v>
+        <v>3060</v>
       </c>
       <c r="E123" t="s">
-        <v>2966</v>
+        <v>3061</v>
       </c>
       <c r="F123" t="s">
         <v>2528</v>
@@ -30074,7 +30633,7 @@
         <v>52</v>
       </c>
       <c r="N123" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -30091,7 +30650,7 @@
         <v>2546</v>
       </c>
       <c r="E124" t="s">
-        <v>2968</v>
+        <v>3063</v>
       </c>
       <c r="F124" t="s">
         <v>2547</v>
@@ -30118,7 +30677,7 @@
         <v>52</v>
       </c>
       <c r="N124" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -30135,7 +30694,7 @@
         <v>2564</v>
       </c>
       <c r="E125" t="s">
-        <v>2969</v>
+        <v>3064</v>
       </c>
       <c r="F125" t="s">
         <v>2565</v>
@@ -30162,7 +30721,7 @@
         <v>189</v>
       </c>
       <c r="N125" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -30173,354 +30732,313 @@
         <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="D126" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="E126" t="s">
-        <v>2970</v>
-      </c>
-      <c r="F126" t="s"/>
+        <v>3065</v>
+      </c>
       <c r="G126" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="H126" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="I126" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="J126" t="s">
-        <v>2585</v>
-      </c>
-      <c r="K126" t="s"/>
+        <v>2589</v>
+      </c>
       <c r="L126" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="M126" t="s">
-        <v>2587</v>
+        <v>3066</v>
       </c>
       <c r="N126" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="B127" t="s">
         <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>2590</v>
+        <v>2596</v>
       </c>
       <c r="D127" t="s">
-        <v>2594</v>
+        <v>2601</v>
       </c>
       <c r="E127" t="s">
-        <v>2971</v>
-      </c>
-      <c r="F127" t="s"/>
+        <v>3067</v>
+      </c>
       <c r="G127" t="s">
-        <v>2595</v>
+        <v>2604</v>
       </c>
       <c r="H127" t="s">
-        <v>2596</v>
+        <v>2605</v>
       </c>
       <c r="I127" t="s">
-        <v>2597</v>
+        <v>2606</v>
       </c>
       <c r="J127" t="s">
-        <v>2598</v>
-      </c>
-      <c r="K127" t="s"/>
+        <v>2607</v>
+      </c>
       <c r="L127" t="s">
-        <v>2599</v>
+        <v>2608</v>
       </c>
       <c r="M127" t="s">
         <v>52</v>
       </c>
       <c r="N127" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
-        <v>2600</v>
-      </c>
-      <c r="B128" t="s"/>
+        <v>2610</v>
+      </c>
       <c r="C128" t="s">
-        <v>2601</v>
-      </c>
-      <c r="D128" t="s"/>
+        <v>2614</v>
+      </c>
       <c r="E128" t="s">
-        <v>2972</v>
-      </c>
-      <c r="F128" t="s"/>
+        <v>3068</v>
+      </c>
       <c r="G128" t="s">
-        <v>2604</v>
+        <v>2621</v>
       </c>
       <c r="H128" t="s">
-        <v>2605</v>
+        <v>2622</v>
       </c>
       <c r="I128" t="s">
-        <v>2606</v>
+        <v>2623</v>
       </c>
       <c r="J128" t="s">
-        <v>2607</v>
+        <v>2624</v>
       </c>
       <c r="K128" t="s">
-        <v>2608</v>
-      </c>
-      <c r="L128" t="s"/>
+        <v>2625</v>
+      </c>
       <c r="M128" t="s">
-        <v>2587</v>
+        <v>3066</v>
       </c>
       <c r="N128" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
-        <v>2609</v>
-      </c>
-      <c r="B129" t="s"/>
+        <v>2628</v>
+      </c>
       <c r="C129" t="s">
-        <v>2610</v>
-      </c>
-      <c r="D129" t="s"/>
+        <v>2632</v>
+      </c>
       <c r="E129" t="s">
-        <v>2973</v>
-      </c>
-      <c r="F129" t="s"/>
+        <v>3069</v>
+      </c>
       <c r="G129" t="s">
-        <v>2613</v>
+        <v>2639</v>
       </c>
       <c r="H129" t="s">
-        <v>2614</v>
-      </c>
-      <c r="I129" t="s"/>
+        <v>2640</v>
+      </c>
       <c r="J129" t="s">
-        <v>2615</v>
+        <v>2642</v>
       </c>
       <c r="K129" t="s">
-        <v>2616</v>
-      </c>
-      <c r="L129" t="s"/>
+        <v>2643</v>
+      </c>
       <c r="M129" t="s">
         <v>52</v>
       </c>
       <c r="N129" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>2617</v>
-      </c>
-      <c r="B130" t="s"/>
+        <v>2646</v>
+      </c>
       <c r="C130" t="s">
-        <v>2618</v>
-      </c>
-      <c r="D130" t="s"/>
+        <v>2650</v>
+      </c>
       <c r="E130" t="s">
-        <v>2974</v>
-      </c>
-      <c r="F130" t="s"/>
+        <v>3070</v>
+      </c>
       <c r="G130" t="s">
-        <v>2621</v>
+        <v>2658</v>
       </c>
       <c r="H130" t="s">
-        <v>2622</v>
+        <v>2659</v>
       </c>
       <c r="I130" t="s">
-        <v>2623</v>
+        <v>2660</v>
       </c>
       <c r="J130" t="s">
-        <v>2624</v>
+        <v>2661</v>
       </c>
       <c r="K130" t="s">
-        <v>2625</v>
-      </c>
-      <c r="L130" t="s"/>
+        <v>2662</v>
+      </c>
       <c r="M130" t="s">
         <v>52</v>
       </c>
       <c r="N130" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
-        <v>2626</v>
-      </c>
-      <c r="B131" t="s"/>
+        <v>2665</v>
+      </c>
       <c r="C131" t="s">
-        <v>2627</v>
+        <v>2669</v>
       </c>
       <c r="D131" t="s">
-        <v>2630</v>
+        <v>2673</v>
       </c>
       <c r="E131" t="s">
-        <v>2975</v>
-      </c>
-      <c r="F131" t="s"/>
+        <v>3071</v>
+      </c>
       <c r="G131" t="s">
-        <v>2631</v>
+        <v>2676</v>
       </c>
       <c r="H131" t="s">
-        <v>2632</v>
-      </c>
-      <c r="I131" t="s"/>
+        <v>2677</v>
+      </c>
       <c r="J131" t="s">
-        <v>2633</v>
+        <v>2679</v>
       </c>
       <c r="K131" t="s">
-        <v>2634</v>
-      </c>
-      <c r="L131" t="s"/>
+        <v>2680</v>
+      </c>
       <c r="M131" t="s">
         <v>52</v>
       </c>
       <c r="N131" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
-        <v>2635</v>
-      </c>
-      <c r="B132" t="s"/>
+        <v>2683</v>
+      </c>
       <c r="C132" t="s">
-        <v>2636</v>
-      </c>
-      <c r="D132" t="s"/>
+        <v>2687</v>
+      </c>
       <c r="E132" t="s">
-        <v>2976</v>
-      </c>
-      <c r="F132" t="s"/>
+        <v>3072</v>
+      </c>
       <c r="G132" t="s">
-        <v>2639</v>
+        <v>2695</v>
       </c>
       <c r="H132" t="s">
-        <v>2640</v>
+        <v>2696</v>
       </c>
       <c r="I132" t="s">
-        <v>2641</v>
+        <v>2697</v>
       </c>
       <c r="J132" t="s">
-        <v>2642</v>
-      </c>
-      <c r="K132" t="s"/>
+        <v>2698</v>
+      </c>
       <c r="L132" t="s">
-        <v>2643</v>
+        <v>2699</v>
       </c>
       <c r="M132" t="s">
         <v>52</v>
       </c>
       <c r="N132" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
-        <v>2644</v>
+        <v>2701</v>
       </c>
       <c r="B133" t="s">
         <v>31</v>
       </c>
       <c r="C133" t="s">
-        <v>2646</v>
-      </c>
-      <c r="D133" t="s"/>
+        <v>2705</v>
+      </c>
       <c r="E133" t="s">
-        <v>2977</v>
-      </c>
-      <c r="F133" t="s"/>
-      <c r="G133" t="s"/>
-      <c r="H133" t="s"/>
+        <v>3073</v>
+      </c>
       <c r="I133" t="s">
-        <v>2650</v>
+        <v>2714</v>
       </c>
       <c r="J133" t="s">
-        <v>2651</v>
-      </c>
-      <c r="K133" t="s"/>
+        <v>2715</v>
+      </c>
       <c r="L133" t="s">
-        <v>2652</v>
+        <v>2716</v>
       </c>
       <c r="M133" t="s">
         <v>52</v>
       </c>
       <c r="N133" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" t="s">
-        <v>2653</v>
-      </c>
-      <c r="B134" t="s"/>
+        <v>2718</v>
+      </c>
       <c r="C134" t="s">
-        <v>2654</v>
-      </c>
-      <c r="D134" t="s"/>
+        <v>2722</v>
+      </c>
       <c r="E134" t="s">
-        <v>2978</v>
-      </c>
-      <c r="F134" t="s"/>
-      <c r="G134" t="s"/>
-      <c r="H134" t="s"/>
+        <v>3074</v>
+      </c>
       <c r="I134" t="s">
-        <v>2656</v>
+        <v>2733</v>
       </c>
       <c r="J134" t="s">
-        <v>2657</v>
-      </c>
-      <c r="K134" t="s"/>
-      <c r="L134" t="s"/>
+        <v>2734</v>
+      </c>
       <c r="M134" t="s">
         <v>52</v>
       </c>
       <c r="N134" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" t="s">
-        <v>2658</v>
-      </c>
-      <c r="B135" t="s"/>
+        <v>2739</v>
+      </c>
       <c r="C135" t="s">
-        <v>2659</v>
-      </c>
-      <c r="D135" t="s"/>
+        <v>2744</v>
+      </c>
       <c r="E135" t="s">
-        <v>2979</v>
-      </c>
-      <c r="F135" t="s"/>
+        <v>3075</v>
+      </c>
       <c r="G135" t="s">
-        <v>2662</v>
+        <v>2754</v>
       </c>
       <c r="H135" t="s">
-        <v>2663</v>
+        <v>2755</v>
       </c>
       <c r="I135" t="s">
-        <v>2664</v>
+        <v>2756</v>
       </c>
       <c r="J135" t="s">
-        <v>2665</v>
+        <v>2757</v>
       </c>
       <c r="K135" t="s">
-        <v>2666</v>
-      </c>
-      <c r="L135" t="s"/>
+        <v>2758</v>
+      </c>
       <c r="M135" t="s">
         <v>52</v>
       </c>
       <c r="N135" t="s">
-        <v>2967</v>
+        <v>3062</v>
       </c>
     </row>
   </sheetData>
@@ -30542,106 +31060,106 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>2980</v>
+        <v>3076</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>2981</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2982</v>
+        <v>3078</v>
       </c>
       <c r="B2" t="s">
-        <v>2676</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2983</v>
+        <v>3079</v>
       </c>
       <c r="B3" t="s">
-        <v>2984</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2985</v>
+        <v>3081</v>
       </c>
       <c r="B4" t="s">
-        <v>2986</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2987</v>
+        <v>3083</v>
       </c>
       <c r="B5" t="s">
-        <v>2988</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2989</v>
+        <v>3085</v>
       </c>
       <c r="B6" t="s">
-        <v>2990</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>2991</v>
+        <v>3087</v>
       </c>
       <c r="B7" t="s">
-        <v>2992</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>2993</v>
+        <v>3089</v>
       </c>
       <c r="B8" t="s">
-        <v>2994</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>2995</v>
+        <v>3091</v>
       </c>
       <c r="B9" t="s">
-        <v>2996</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>2997</v>
+        <v>3093</v>
       </c>
       <c r="B10" t="s">
-        <v>2998</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>2999</v>
+        <v>3095</v>
       </c>
       <c r="B11" t="s">
-        <v>3000</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3001</v>
+        <v>3097</v>
       </c>
       <c r="B12" t="s">
-        <v>3002</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3003</v>
+        <v>3099</v>
       </c>
       <c r="B13" t="s">
-        <v>3004</v>
+        <v>3100</v>
       </c>
     </row>
   </sheetData>
@@ -30660,82 +31178,82 @@
   <sheetData>
     <row customHeight="1" ht="27.6" r="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>3005</v>
+        <v>3101</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3006</v>
+        <v>3102</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>3007</v>
+        <v>3103</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3008</v>
+        <v>3104</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3009</v>
+        <v>3105</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>3010</v>
+        <v>3106</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3011</v>
+        <v>3107</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3012</v>
+        <v>3108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3013</v>
+        <v>3109</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3014</v>
+        <v>3110</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3015</v>
+        <v>3111</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1681</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3012</v>
+        <v>3108</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3013</v>
+        <v>3109</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1674</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3014</v>
+        <v>3110</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3016</v>
+        <v>3112</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3012</v>
+        <v>3108</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3013</v>
+        <v>3109</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3014</v>
+        <v>3110</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="5" spans="1:6">
@@ -30746,16 +31264,16 @@
         <v>2204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="6" spans="1:6">
@@ -30766,16 +31284,16 @@
         <v>2223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="7" spans="1:6">
@@ -30786,16 +31304,16 @@
         <v>2243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="8" spans="1:6">
@@ -30806,16 +31324,16 @@
         <v>2262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:6">
@@ -30826,16 +31344,16 @@
         <v>2283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="10" spans="1:6">
@@ -30846,16 +31364,16 @@
         <v>2305</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:6">
@@ -30866,16 +31384,16 @@
         <v>2326</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:6">
@@ -30886,16 +31404,16 @@
         <v>2346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="13" spans="1:6">
@@ -30906,16 +31424,16 @@
         <v>2364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="14" spans="1:6">
@@ -30926,16 +31444,16 @@
         <v>2383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:6">
@@ -30946,16 +31464,16 @@
         <v>2404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="16" spans="1:6">
@@ -30966,16 +31484,16 @@
         <v>2425</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:6">
@@ -30986,96 +31504,96 @@
         <v>2445</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>3018</v>
+        <v>3114</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3019</v>
+        <v>3115</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3020</v>
+        <v>3116</v>
       </c>
     </row>
     <row customHeight="1" ht="303.6" r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>3021</v>
+        <v>3117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3022</v>
+        <v>3118</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3012</v>
+        <v>3108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>3023</v>
+        <v>3119</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>610</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3024</v>
+        <v>3120</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>3025</v>
+        <v>3121</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3026</v>
+        <v>3122</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3027</v>
+        <v>3123</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3028</v>
+        <v>3124</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>2458</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
     </row>
     <row customHeight="1" ht="193.2" r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>3029</v>
+        <v>3125</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3030</v>
+        <v>3126</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3027</v>
+        <v>3123</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3028</v>
+        <v>3124</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>2479</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>3031</v>
+        <v>3127</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3032</v>
+        <v>3128</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3027</v>
+        <v>3123</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>3028</v>
+        <v>3124</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>3017</v>
+        <v>3113</v>
       </c>
     </row>
   </sheetData>
@@ -31097,15 +31615,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>3033</v>
+        <v>3129</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3034</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3035</v>
+        <v>3131</v>
       </c>
       <c r="B2" t="n">
         <v>118</v>
@@ -31113,7 +31631,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3036</v>
+        <v>3132</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -31121,7 +31639,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3037</v>
+        <v>3133</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -31129,7 +31647,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3038</v>
+        <v>3134</v>
       </c>
       <c r="B5" t="s">
         <v>2440</v>
@@ -31137,66 +31655,66 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3039</v>
+        <v>3135</v>
       </c>
       <c r="B6" t="s">
-        <v>3040</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3041</v>
+        <v>3137</v>
       </c>
       <c r="B7" t="s">
-        <v>3042</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3043</v>
+        <v>3139</v>
       </c>
       <c r="B8" t="s">
-        <v>3044</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3045</v>
+        <v>3141</v>
       </c>
       <c r="B9" t="s">
-        <v>3046</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>2997</v>
+        <v>3093</v>
       </c>
       <c r="B10" t="s">
-        <v>2998</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3047</v>
+        <v>3143</v>
       </c>
       <c r="B11" t="s">
-        <v>3042</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3048</v>
+        <v>3144</v>
       </c>
       <c r="B12" t="s">
-        <v>3049</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3050</v>
+        <v>3146</v>
       </c>
       <c r="B13" t="s">
-        <v>3051</v>
+        <v>3147</v>
       </c>
     </row>
   </sheetData>

--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="5" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="12456" windowWidth="23256" xWindow="-108" yWindow="-108"/>
+    <workbookView activeTab="4" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16776" windowWidth="30936" xWindow="-108" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整文献矩阵" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3198">
   <si>
     <t>序号</t>
   </si>
@@ -8326,6 +8326,135 @@
     <t>Nanoconfinement; coalbed methane; 吸附; 游离气; 纳米限域; 孔隙结构; 吸附热力学</t>
   </si>
   <si>
+    <t>DCBM-135</t>
+  </si>
+  <si>
+    <t>Guo, Qiang</t>
+  </si>
+  <si>
+    <t>Guo, Qiang; Chen, Yang; Huang, Yaping; Ba, Jing</t>
+  </si>
+  <si>
+    <t>Seismic rock-physics inversion for petrophysical parameters in deep coalbed methane reservoirs with complex pore structures</t>
+  </si>
+  <si>
+    <t>复杂孔隙结构深部煤层气储层岩石物理参数地震反演</t>
+  </si>
+  <si>
+    <t>Journal of Applied Geophysics</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>106338</t>
+  </si>
+  <si>
+    <t>10.1016/j.jappgeo.2026.106338</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0926985126002478</t>
+  </si>
+  <si>
+    <t>鄂尔多斯盆地东缘；石炭系本溪组</t>
+  </si>
+  <si>
+    <t>深部煤层气储层（双重孔隙体系，埋深1500-2300 m）</t>
+  </si>
+  <si>
+    <t>1500-2300 m；平均厚度约12 m</t>
+  </si>
+  <si>
+    <t>构建考虑空间变化孔隙纵横比的岩石物理-地震反演框架，联合反演深部煤层储层物性参数</t>
+  </si>
+  <si>
+    <t>两口井测井资料；煤层及围岩岩石物理建模；空间可变孔隙纵横比；Taylor展开线性化正演；高斯混合模型多峰岩相统计；贝叶斯线性反演；总孔隙度/黏土体积分数/孔隙纵横比联合预测；二维地震剖面验证</t>
+  </si>
+  <si>
+    <t>固定孔隙纵横比难以描述深部煤层复杂双孔隙结构；空间变化孔隙纵横比可改善储层物性反演；高斯混合先验可处理多峰统计分布；实际二维地震资料可辅助识别含气煤层和储层物性变化</t>
+  </si>
+  <si>
+    <t>将孔隙几何参数与常规储层物性参数联合反演；空间变化孔隙纵横比表征深部煤层双孔隙复杂性；高斯混合统计先验与贝叶斯岩石物理反演结合</t>
+  </si>
+  <si>
+    <t>对初始模型和先验信息依赖较高；两口井和单一二维剖面限制泛化；等效孔隙纵横比是复杂孔裂隙体系的简化；地震反演只能提供间接储层证据</t>
+  </si>
+  <si>
+    <t>储层非均质性；裂缝-基质双重孔隙；多源资料融合的必要性；后续引入地震/测井和孔裂隙参数的理由</t>
+  </si>
+  <si>
+    <t>引言：深部煤储层复杂孔裂隙及预测难点；方法讨论：多源储层参数与地震反演；讨论：储层非均质性作为动态差异的替代解释；局限：间接地球物理证据不能替代生产因果验证</t>
+  </si>
+  <si>
+    <t>seismic inversion; rock physics; pore aspect ratio; deep coalbed methane; Bayesian inversion; Ordos Basin</t>
+  </si>
+  <si>
+    <t>出版商题名/作者/DOI/卷和文章号已核验</t>
+  </si>
+  <si>
+    <t>DCBM-136</t>
+  </si>
+  <si>
+    <t>Zhang, Q.</t>
+  </si>
+  <si>
+    <t>Zhang, Q.; Li, Y.; Tang, S.; Zhang, P.; Zhang, S.; Xi, Z.</t>
+  </si>
+  <si>
+    <t>2027 (online 2026)</t>
+  </si>
+  <si>
+    <t>Geochemical evolution and microbial controls on methanogenic potential in North China coalbed methane reservoirs: Implications for CBM bioengineering</t>
+  </si>
+  <si>
+    <t>华北煤层气藏地球化学演化与产甲烷潜力的微生物控制：对煤层气生物工程的启示</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>140384</t>
+  </si>
+  <si>
+    <t>10.1016/j.fuel.2026.140384</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0016236126021393</t>
+  </si>
+  <si>
+    <t>华北4个煤层气区：沁水盆地南部、宁武盆地南部、鄂尔多斯盆地东缘神府区块、临兴区块</t>
+  </si>
+  <si>
+    <t>煤层气藏（69口生产井；不同埋深/煤阶/水动力条件）</t>
+  </si>
+  <si>
+    <t>研究华北煤层气藏地球化学演化与产甲烷潜力的微生物控制机制，评估煤层气生物工程潜力</t>
+  </si>
+  <si>
+    <t>69口生产井采样；产出气组分与甲烷碳氢同位素；产出水主要离子和水化学；溶解无机碳及其同位素；微生物群落分析；产甲烷功能基因；区域水动力封闭和盐度对比</t>
+  </si>
+  <si>
+    <t>4个研究区以热成因甲烷为主；沁水南部存在局部次生微生物改造信号；神府和临兴产出水盐度更高/Na-Cl富集/水动力封闭更强；沁水南部产甲烷菌多样性和功能基因更丰富；神府整体产甲烷功能基因丰度较低；水化学条件是限制微生物增产适用性的关键因素</t>
+  </si>
+  <si>
+    <t>联合气体/产出水/同位素/微生物群落和功能基因；在热成因气背景下识别局部次生生物成因改造；将区域水化学差异与微生物增产适用性直接联系；为晚期/低产井微生物增产筛选提供约束框架</t>
+  </si>
+  <si>
+    <t>微生物深入分析主要集中在沁水南部和神府/区域覆盖不完全对称；产出水微生物不一定完全代表原位煤基质微生物群落；69口井均为生产井/长期排采可能已改变原始水化学和微生物状态；产甲烷功能基因表明潜力不等同于现场增产效果</t>
+  </si>
+  <si>
+    <t>产出水化学和水动力封闭；区块差异及保存条件；长期排采后流体环境演化；生物成因与热成因气的区分；不能仅凭气水动态推断气源或微生物作用</t>
+  </si>
+  <si>
+    <t>引言：华北煤层气水化学和气源背景；讨论：产出水/盐度/封闭和区域差异；局限：生产动态不能直接识别气源或微生物机制；展望：低产/晚期井微生物增产的筛选与验证</t>
+  </si>
+  <si>
+    <t>CBM bioengineering; microbial methanogenesis; hydrogeochemistry; North China; Fuel; microbial community</t>
+  </si>
+  <si>
+    <t>出版商题名/DOI/卷期/摘要和研究设计已核验；作者缩写待Crossref补全</t>
+  </si>
+  <si>
     <t>指标</t>
   </si>
   <si>
@@ -8350,7 +8479,7 @@
     <t>当前主表版本</t>
   </si>
   <si>
-    <t>v1_134_daily_brief_update_2026-07-23</t>
+    <t>v1_136_daily_brief_update_2026-07-24</t>
   </si>
   <si>
     <t>Deep_CBM_complete_literature_matrix_v1_105.xlsx</t>
@@ -9925,6 +10054,18 @@
 【与你课题的关系】早期游离气贡献和相态评价边界。</t>
   </si>
   <si>
+    <t>【局限性】间接地球物理证据不能替代生产因果验证。</t>
+  </si>
+  <si>
+    <t>间接地球物理证据不能替代生产因果验证。</t>
+  </si>
+  <si>
+    <t>【局限性】生产动态不能直接识别气源或微生物机制；</t>
+  </si>
+  <si>
+    <t>生产动态不能直接识别气源或微生物机制；</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -10000,6 +10141,12 @@
     <t>新增: DCBM-125, DCBM-126, DCBM-127, DCBM-128, DCBM-129, DCBM-130, DCBM-131, DCBM-132, DCBM-133, DCBM-134, DCBM-135, DCBM-136, DCBM-137; 跳过重复: 0; 主库记录数更新为 12 → (待QC确认)</t>
   </si>
   <si>
+    <t>2026-07-24 Daily Brief Update</t>
+  </si>
+  <si>
+    <t>新增: DCBM-135, DCBM-136; 跳过重复: 0; 主库记录数更新为 13 → (待QC确认)</t>
+  </si>
+  <si>
     <t>候选原编号</t>
   </si>
   <si>
@@ -10139,6 +10286,12 @@
   </si>
   <si>
     <t>新增 10 篇, 跳过重复 0 篇, 待 validate 确认</t>
+  </si>
+  <si>
+    <t>Daily Brief Update 2026-07-24</t>
+  </si>
+  <si>
+    <t>新增 2 篇, 跳过重复 0 篇, 待 validate 确认</t>
   </si>
 </sst>
 </file>
@@ -10278,7 +10431,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMComplete105" headerRowCount="1" id="1" name="DeepCBMComplete105" ref="A1:AA106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMComplete105" headerRowCount="1" id="1" name="DeepCBMComplete105" ref="A1:AA135">
   <tableColumns count="27">
     <tableColumn id="1" name="序号"/>
     <tableColumn id="2" name="文献ID"/>
@@ -10313,7 +10466,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMWebIndex105" headerRowCount="1" id="2" name="DeepCBMWebIndex105" ref="A1:H106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMWebIndex105" headerRowCount="1" id="2" name="DeepCBMWebIndex105" ref="A1:H134">
   <tableColumns count="8">
     <tableColumn id="1" name="序号"/>
     <tableColumn id="2" name="文献ID"/>
@@ -10481,7 +10634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA135"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -20563,7 +20716,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="123" spans="1:27">
+    <row customHeight="1" ht="96.59999999999999" r="123" spans="1:27">
       <c r="A123" s="10" t="n">
         <v>122</v>
       </c>
@@ -20721,7 +20874,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="125" spans="1:27">
+    <row customHeight="1" ht="69" r="125" spans="1:27">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
@@ -20966,7 +21119,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
+    <row customHeight="1" ht="41.4" r="128" spans="1:27">
       <c r="A128" s="10" t="n">
         <v>127</v>
       </c>
@@ -21043,7 +21196,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:27">
+    <row customHeight="1" ht="69" r="129" spans="1:27">
       <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
@@ -21194,7 +21347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:27">
+    <row customHeight="1" ht="55.2" r="131" spans="1:27">
       <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
@@ -21437,7 +21590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:27">
+    <row customHeight="1" ht="41.4" r="134" spans="1:27">
       <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
@@ -21599,6 +21752,167 @@
       </c>
       <c r="AA135" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D136" t="s">
+        <v>2763</v>
+      </c>
+      <c r="E136" t="s">
+        <v>31</v>
+      </c>
+      <c r="F136" t="s">
+        <v>2764</v>
+      </c>
+      <c r="G136" t="s">
+        <v>2765</v>
+      </c>
+      <c r="H136" t="s">
+        <v>2766</v>
+      </c>
+      <c r="I136" t="s">
+        <v>2767</v>
+      </c>
+      <c r="J136" t="s"/>
+      <c r="K136" t="s">
+        <v>2768</v>
+      </c>
+      <c r="L136" t="s">
+        <v>2769</v>
+      </c>
+      <c r="M136" t="s">
+        <v>2770</v>
+      </c>
+      <c r="N136" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O136" t="s">
+        <v>2771</v>
+      </c>
+      <c r="P136" t="s">
+        <v>2772</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>2773</v>
+      </c>
+      <c r="R136" t="s">
+        <v>2774</v>
+      </c>
+      <c r="S136" t="s">
+        <v>2775</v>
+      </c>
+      <c r="T136" t="s">
+        <v>2776</v>
+      </c>
+      <c r="U136" t="s">
+        <v>2777</v>
+      </c>
+      <c r="V136" t="s">
+        <v>2778</v>
+      </c>
+      <c r="W136" t="s">
+        <v>2779</v>
+      </c>
+      <c r="X136" t="s">
+        <v>2780</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>2781</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA136" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2785</v>
+      </c>
+      <c r="E137" t="s">
+        <v>2786</v>
+      </c>
+      <c r="F137" t="s">
+        <v>2787</v>
+      </c>
+      <c r="G137" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H137" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2789</v>
+      </c>
+      <c r="J137" t="s">
+        <v>2746</v>
+      </c>
+      <c r="K137" t="s">
+        <v>2790</v>
+      </c>
+      <c r="L137" t="s">
+        <v>2791</v>
+      </c>
+      <c r="M137" t="s">
+        <v>2792</v>
+      </c>
+      <c r="N137" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O137" t="s">
+        <v>2793</v>
+      </c>
+      <c r="P137" t="s">
+        <v>2794</v>
+      </c>
+      <c r="R137" t="s">
+        <v>2795</v>
+      </c>
+      <c r="S137" t="s">
+        <v>2796</v>
+      </c>
+      <c r="T137" t="s">
+        <v>2797</v>
+      </c>
+      <c r="U137" t="s">
+        <v>2798</v>
+      </c>
+      <c r="V137" t="s">
+        <v>2799</v>
+      </c>
+      <c r="W137" t="s">
+        <v>2800</v>
+      </c>
+      <c r="X137" t="s">
+        <v>2801</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>2802</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA137" t="s">
+        <v>2803</v>
       </c>
     </row>
   </sheetData>
@@ -21628,13 +21942,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>2761</v>
+        <v>2804</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2762</v>
+        <v>2805</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2763</v>
+        <v>2806</v>
       </c>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
@@ -21642,13 +21956,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>2764</v>
+        <v>2807</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2765</v>
+        <v>2808</v>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
@@ -21656,13 +21970,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>2766</v>
+        <v>2809</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2767</v>
+        <v>2810</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -21670,13 +21984,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>2768</v>
+        <v>2811</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2769</v>
+        <v>2812</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2770</v>
+        <v>2813</v>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
@@ -21684,13 +21998,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>2771</v>
+        <v>2814</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2772</v>
+        <v>2815</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2773</v>
+        <v>2816</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
@@ -21698,13 +22012,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>2774</v>
+        <v>2817</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2775</v>
+        <v>2818</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2776</v>
+        <v>2819</v>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
@@ -21715,14 +22029,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2777</v>
+        <v>2820</v>
       </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2777</v>
+        <v>2820</v>
       </c>
       <c r="F7" s="3" t="n"/>
     </row>
@@ -21760,7 +22074,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>2778</v>
+        <v>2821</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -21776,7 +22090,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>2779</v>
+        <v>2822</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -21792,7 +22106,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>2780</v>
+        <v>2823</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -21881,7 +22195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -24647,7 +24961,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row customHeight="1" ht="41.4" r="107" spans="1:8">
       <c r="A107" s="12" t="n">
         <v>106</v>
       </c>
@@ -24673,7 +24987,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row customHeight="1" ht="27.6" r="108" spans="1:8">
       <c r="A108" s="12" t="n">
         <v>107</v>
       </c>
@@ -24699,7 +25013,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row customHeight="1" ht="27.6" r="109" spans="1:8">
       <c r="A109" s="12" t="n">
         <v>108</v>
       </c>
@@ -24723,7 +25037,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row customHeight="1" ht="27.6" r="110" spans="1:8">
       <c r="A110" s="12" t="n">
         <v>109</v>
       </c>
@@ -24749,7 +25063,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row customHeight="1" ht="41.4" r="111" spans="1:8">
       <c r="A111" s="12" t="n">
         <v>110</v>
       </c>
@@ -24775,7 +25089,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row customHeight="1" ht="27.6" r="112" spans="1:8">
       <c r="A112" s="12" t="n">
         <v>111</v>
       </c>
@@ -24801,7 +25115,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row customHeight="1" ht="27.6" r="113" spans="1:8">
       <c r="A113" s="12" t="n">
         <v>112</v>
       </c>
@@ -24825,7 +25139,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row customHeight="1" ht="27.6" r="114" spans="1:8">
       <c r="A114" s="12" t="n">
         <v>113</v>
       </c>
@@ -24849,7 +25163,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row customHeight="1" ht="41.4" r="115" spans="1:8">
       <c r="A115" s="12" t="n">
         <v>114</v>
       </c>
@@ -24875,7 +25189,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row customHeight="1" ht="27.6" r="116" spans="1:8">
       <c r="A116" s="12" t="n">
         <v>115</v>
       </c>
@@ -24899,7 +25213,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row customHeight="1" ht="27.6" r="117" spans="1:8">
       <c r="A117" s="12" t="n">
         <v>116</v>
       </c>
@@ -24925,7 +25239,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row customHeight="1" ht="27.6" r="118" spans="1:8">
       <c r="A118" s="12" t="n">
         <v>117</v>
       </c>
@@ -24951,7 +25265,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row customHeight="1" ht="27.6" r="119" spans="1:8">
       <c r="A119" s="12" t="n">
         <v>118</v>
       </c>
@@ -25362,6 +25676,28 @@
       </c>
       <c r="H134" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="n">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>2761</v>
+      </c>
+      <c r="F135" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="n">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2783</v>
+      </c>
+      <c r="F136" t="s">
+        <v>2791</v>
       </c>
     </row>
   </sheetData>
@@ -25387,10 +25723,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>2781</v>
+        <v>2824</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2763</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -25398,7 +25734,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2782</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -25406,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2783</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -25414,7 +25750,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2784</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -25422,7 +25758,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2785</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -25430,7 +25766,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2786</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -25438,7 +25774,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2787</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -25446,7 +25782,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2788</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -25454,15 +25790,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2789</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>2790</v>
+        <v>2833</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2791</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -25470,7 +25806,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2792</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -25478,7 +25814,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2793</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -25486,7 +25822,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2794</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -25494,7 +25830,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2795</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -25502,7 +25838,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2796</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -25510,7 +25846,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2797</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -25518,7 +25854,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2798</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -25526,7 +25862,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2799</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -25534,7 +25870,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2800</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -25542,7 +25878,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2801</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -25550,7 +25886,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2802</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -25558,7 +25894,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2803</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -25566,7 +25902,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2804</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -25574,7 +25910,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2805</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -25582,7 +25918,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2806</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -25590,7 +25926,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2807</v>
+        <v>2850</v>
       </c>
     </row>
   </sheetData>
@@ -25604,7 +25940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -25629,22 +25965,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2808</v>
+        <v>2851</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2809</v>
+        <v>2852</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2810</v>
+        <v>2853</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2811</v>
+        <v>2854</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2812</v>
+        <v>2855</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>20</v>
@@ -25653,16 +25989,16 @@
         <v>21</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>2813</v>
+        <v>2856</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>2814</v>
+        <v>2857</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>2815</v>
+        <v>2858</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="2" spans="1:14">
@@ -25676,10 +26012,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2816</v>
+        <v>2859</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2817</v>
+        <v>2860</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>44</v>
@@ -25706,7 +26042,7 @@
         <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="3" spans="1:14">
@@ -25720,10 +26056,10 @@
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2819</v>
+        <v>2862</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2820</v>
+        <v>2863</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>68</v>
@@ -25750,7 +26086,7 @@
         <v>52</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="4" spans="1:14">
@@ -25764,10 +26100,10 @@
         <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2821</v>
+        <v>2864</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2822</v>
+        <v>2865</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>92</v>
@@ -25794,7 +26130,7 @@
         <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="5" spans="1:14">
@@ -25808,10 +26144,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2823</v>
+        <v>2866</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2824</v>
+        <v>2867</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>115</v>
@@ -25838,7 +26174,7 @@
         <v>52</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="6" spans="1:14">
@@ -25852,10 +26188,10 @@
         <v>128</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2825</v>
+        <v>2868</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2826</v>
+        <v>2869</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>137</v>
@@ -25882,7 +26218,7 @@
         <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="7" spans="1:14">
@@ -25896,10 +26232,10 @@
         <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2827</v>
+        <v>2870</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2828</v>
+        <v>2871</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>160</v>
@@ -25926,7 +26262,7 @@
         <v>145</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="8" spans="1:14">
@@ -25940,10 +26276,10 @@
         <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2829</v>
+        <v>2872</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2830</v>
+        <v>2873</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>181</v>
@@ -25970,7 +26306,7 @@
         <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:14">
@@ -25984,10 +26320,10 @@
         <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2831</v>
+        <v>2874</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2832</v>
+        <v>2875</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>201</v>
@@ -26014,7 +26350,7 @@
         <v>145</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="10" spans="1:14">
@@ -26028,10 +26364,10 @@
         <v>214</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2833</v>
+        <v>2876</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2834</v>
+        <v>2877</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>220</v>
@@ -26058,7 +26394,7 @@
         <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:14">
@@ -26072,10 +26408,10 @@
         <v>233</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2835</v>
+        <v>2878</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2836</v>
+        <v>2879</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>239</v>
@@ -26102,7 +26438,7 @@
         <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:14">
@@ -26116,10 +26452,10 @@
         <v>252</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2837</v>
+        <v>2880</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2838</v>
+        <v>2881</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>258</v>
@@ -26146,7 +26482,7 @@
         <v>145</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="13" spans="1:14">
@@ -26160,10 +26496,10 @@
         <v>272</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2839</v>
+        <v>2882</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2840</v>
+        <v>2883</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>278</v>
@@ -26190,7 +26526,7 @@
         <v>52</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="14" spans="1:14">
@@ -26204,10 +26540,10 @@
         <v>291</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2841</v>
+        <v>2884</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2842</v>
+        <v>2885</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>300</v>
@@ -26234,7 +26570,7 @@
         <v>145</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:14">
@@ -26248,10 +26584,10 @@
         <v>313</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2843</v>
+        <v>2886</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2844</v>
+        <v>2887</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>321</v>
@@ -26278,7 +26614,7 @@
         <v>52</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="16" spans="1:14">
@@ -26292,10 +26628,10 @@
         <v>334</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2845</v>
+        <v>2888</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2846</v>
+        <v>2889</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>343</v>
@@ -26322,7 +26658,7 @@
         <v>52</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:14">
@@ -26336,10 +26672,10 @@
         <v>356</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2847</v>
+        <v>2890</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2848</v>
+        <v>2891</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>363</v>
@@ -26366,7 +26702,7 @@
         <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="18" spans="1:14">
@@ -26380,10 +26716,10 @@
         <v>376</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2849</v>
+        <v>2892</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2850</v>
+        <v>2893</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>383</v>
@@ -26410,7 +26746,7 @@
         <v>145</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="19" spans="1:14">
@@ -26424,10 +26760,10 @@
         <v>397</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2851</v>
+        <v>2894</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2852</v>
+        <v>2895</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>404</v>
@@ -26454,7 +26790,7 @@
         <v>145</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="20" spans="1:14">
@@ -26468,10 +26804,10 @@
         <v>418</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2853</v>
+        <v>2896</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2854</v>
+        <v>2897</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>427</v>
@@ -26498,7 +26834,7 @@
         <v>145</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="21" spans="1:14">
@@ -26512,10 +26848,10 @@
         <v>441</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2855</v>
+        <v>2898</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2856</v>
+        <v>2899</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>448</v>
@@ -26542,7 +26878,7 @@
         <v>145</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="22" spans="1:14">
@@ -26556,10 +26892,10 @@
         <v>462</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2858</v>
+        <v>2901</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>467</v>
@@ -26586,7 +26922,7 @@
         <v>52</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="23" spans="1:14">
@@ -26600,10 +26936,10 @@
         <v>481</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2859</v>
+        <v>2902</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2860</v>
+        <v>2903</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>489</v>
@@ -26630,7 +26966,7 @@
         <v>145</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="24" spans="1:14">
@@ -26644,10 +26980,10 @@
         <v>503</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2861</v>
+        <v>2904</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2862</v>
+        <v>2905</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>511</v>
@@ -26674,7 +27010,7 @@
         <v>52</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="25" spans="1:14">
@@ -26688,10 +27024,10 @@
         <v>524</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2863</v>
+        <v>2906</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2864</v>
+        <v>2907</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>532</v>
@@ -26718,7 +27054,7 @@
         <v>145</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="26" spans="1:14">
@@ -26732,10 +27068,10 @@
         <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2865</v>
+        <v>2908</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2866</v>
+        <v>2909</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>554</v>
@@ -26762,7 +27098,7 @@
         <v>52</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="27" spans="1:14">
@@ -26776,10 +27112,10 @@
         <v>568</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2867</v>
+        <v>2910</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2868</v>
+        <v>2911</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>577</v>
@@ -26806,7 +27142,7 @@
         <v>52</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="28" spans="1:14">
@@ -26820,10 +27156,10 @@
         <v>591</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2869</v>
+        <v>2912</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2870</v>
+        <v>2913</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>600</v>
@@ -26850,7 +27186,7 @@
         <v>52</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="29" spans="1:14">
@@ -26864,10 +27200,10 @@
         <v>614</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2871</v>
+        <v>2914</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2872</v>
+        <v>2915</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>623</v>
@@ -26894,7 +27230,7 @@
         <v>52</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="30" spans="1:14">
@@ -26908,10 +27244,10 @@
         <v>637</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2873</v>
+        <v>2916</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2874</v>
+        <v>2917</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>646</v>
@@ -26938,7 +27274,7 @@
         <v>52</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="31" spans="1:14">
@@ -26952,10 +27288,10 @@
         <v>659</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2875</v>
+        <v>2918</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2876</v>
+        <v>2919</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>668</v>
@@ -26982,7 +27318,7 @@
         <v>52</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="32" spans="1:14">
@@ -26996,10 +27332,10 @@
         <v>682</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2877</v>
+        <v>2920</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2878</v>
+        <v>2921</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>689</v>
@@ -27026,7 +27362,7 @@
         <v>52</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="33" spans="1:14">
@@ -27040,10 +27376,10 @@
         <v>702</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2879</v>
+        <v>2922</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2880</v>
+        <v>2923</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>709</v>
@@ -27070,7 +27406,7 @@
         <v>145</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="34" spans="1:14">
@@ -27084,10 +27420,10 @@
         <v>722</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2881</v>
+        <v>2924</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2882</v>
+        <v>2925</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>731</v>
@@ -27114,7 +27450,7 @@
         <v>52</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="35" spans="1:14">
@@ -27128,10 +27464,10 @@
         <v>744</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2883</v>
+        <v>2926</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2884</v>
+        <v>2927</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>751</v>
@@ -27158,7 +27494,7 @@
         <v>52</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="36" spans="1:14">
@@ -27172,10 +27508,10 @@
         <v>764</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2885</v>
+        <v>2928</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2886</v>
+        <v>2929</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>772</v>
@@ -27202,7 +27538,7 @@
         <v>145</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="37" spans="1:14">
@@ -27216,10 +27552,10 @@
         <v>785</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2887</v>
+        <v>2930</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2888</v>
+        <v>2931</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>792</v>
@@ -27246,7 +27582,7 @@
         <v>145</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="38" spans="1:14">
@@ -27260,10 +27596,10 @@
         <v>806</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2889</v>
+        <v>2932</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2890</v>
+        <v>2933</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>814</v>
@@ -27290,7 +27626,7 @@
         <v>145</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="39" spans="1:14">
@@ -27304,10 +27640,10 @@
         <v>827</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2891</v>
+        <v>2934</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2892</v>
+        <v>2935</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>834</v>
@@ -27334,7 +27670,7 @@
         <v>145</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="40" spans="1:14">
@@ -27348,10 +27684,10 @@
         <v>848</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2893</v>
+        <v>2936</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2894</v>
+        <v>2937</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>856</v>
@@ -27378,7 +27714,7 @@
         <v>52</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="41" spans="1:14">
@@ -27392,10 +27728,10 @@
         <v>870</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2895</v>
+        <v>2938</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2896</v>
+        <v>2939</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>878</v>
@@ -27422,7 +27758,7 @@
         <v>52</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="42" spans="1:14">
@@ -27436,10 +27772,10 @@
         <v>891</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2897</v>
+        <v>2940</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2898</v>
+        <v>2941</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>901</v>
@@ -27466,7 +27802,7 @@
         <v>52</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="43" spans="1:14">
@@ -27480,10 +27816,10 @@
         <v>914</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2899</v>
+        <v>2942</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2900</v>
+        <v>2943</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>921</v>
@@ -27510,7 +27846,7 @@
         <v>52</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="44" spans="1:14">
@@ -27524,10 +27860,10 @@
         <v>933</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2901</v>
+        <v>2944</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2902</v>
+        <v>2945</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>940</v>
@@ -27554,7 +27890,7 @@
         <v>52</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="45" spans="1:14">
@@ -27568,10 +27904,10 @@
         <v>953</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2903</v>
+        <v>2946</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2904</v>
+        <v>2947</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>959</v>
@@ -27598,7 +27934,7 @@
         <v>52</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="46" spans="1:14">
@@ -27612,10 +27948,10 @@
         <v>972</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2905</v>
+        <v>2948</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2906</v>
+        <v>2949</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>978</v>
@@ -27642,7 +27978,7 @@
         <v>52</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="47" spans="1:14">
@@ -27656,10 +27992,10 @@
         <v>990</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2907</v>
+        <v>2950</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2908</v>
+        <v>2951</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>997</v>
@@ -27686,7 +28022,7 @@
         <v>52</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="48" spans="1:14">
@@ -27700,10 +28036,10 @@
         <v>1010</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2909</v>
+        <v>2952</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>2910</v>
+        <v>2953</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>1018</v>
@@ -27730,7 +28066,7 @@
         <v>52</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="49" spans="1:14">
@@ -27744,10 +28080,10 @@
         <v>1030</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2911</v>
+        <v>2954</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2912</v>
+        <v>2955</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>1037</v>
@@ -27774,7 +28110,7 @@
         <v>52</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="50" spans="1:14">
@@ -27788,10 +28124,10 @@
         <v>1049</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2913</v>
+        <v>2956</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2914</v>
+        <v>2957</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>1055</v>
@@ -27818,7 +28154,7 @@
         <v>189</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="51" spans="1:14">
@@ -27832,10 +28168,10 @@
         <v>1067</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2915</v>
+        <v>2958</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2916</v>
+        <v>2959</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>1072</v>
@@ -27862,7 +28198,7 @@
         <v>52</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="52" spans="1:14">
@@ -27876,10 +28212,10 @@
         <v>1084</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2917</v>
+        <v>2960</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2918</v>
+        <v>2961</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>1091</v>
@@ -27906,7 +28242,7 @@
         <v>189</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="53" spans="1:14">
@@ -27920,10 +28256,10 @@
         <v>1104</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2919</v>
+        <v>2962</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>2920</v>
+        <v>2963</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>1109</v>
@@ -27950,7 +28286,7 @@
         <v>145</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="54" spans="1:14">
@@ -27964,10 +28300,10 @@
         <v>1121</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2921</v>
+        <v>2964</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>2922</v>
+        <v>2965</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>1131</v>
@@ -27994,7 +28330,7 @@
         <v>52</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="55" spans="1:14">
@@ -28008,10 +28344,10 @@
         <v>1144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2923</v>
+        <v>2966</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>2924</v>
+        <v>2967</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>1151</v>
@@ -28038,7 +28374,7 @@
         <v>52</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="56" spans="1:14">
@@ -28052,10 +28388,10 @@
         <v>1165</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2925</v>
+        <v>2968</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2926</v>
+        <v>2969</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>1173</v>
@@ -28082,7 +28418,7 @@
         <v>52</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="57" spans="1:14">
@@ -28096,10 +28432,10 @@
         <v>1187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2927</v>
+        <v>2970</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>2928</v>
+        <v>2971</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>1195</v>
@@ -28126,7 +28462,7 @@
         <v>189</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="58" spans="1:14">
@@ -28140,10 +28476,10 @@
         <v>1209</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2929</v>
+        <v>2972</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>2930</v>
+        <v>2973</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>1217</v>
@@ -28170,7 +28506,7 @@
         <v>189</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="59" spans="1:14">
@@ -28184,10 +28520,10 @@
         <v>1231</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2931</v>
+        <v>2974</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>2932</v>
+        <v>2975</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>1239</v>
@@ -28214,7 +28550,7 @@
         <v>189</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="60" spans="1:14">
@@ -28228,10 +28564,10 @@
         <v>1252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2933</v>
+        <v>2976</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>2934</v>
+        <v>2977</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>1261</v>
@@ -28258,7 +28594,7 @@
         <v>52</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="61" spans="1:14">
@@ -28272,10 +28608,10 @@
         <v>1275</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>2935</v>
+        <v>2978</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>2936</v>
+        <v>2979</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>1283</v>
@@ -28302,7 +28638,7 @@
         <v>52</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="62" spans="1:14">
@@ -28316,10 +28652,10 @@
         <v>1297</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2937</v>
+        <v>2980</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2938</v>
+        <v>2981</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>1305</v>
@@ -28346,7 +28682,7 @@
         <v>145</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="63" spans="1:14">
@@ -28360,10 +28696,10 @@
         <v>1319</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2939</v>
+        <v>2982</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>2940</v>
+        <v>2983</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>1327</v>
@@ -28390,7 +28726,7 @@
         <v>189</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="64" spans="1:14">
@@ -28404,10 +28740,10 @@
         <v>1341</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>2941</v>
+        <v>2984</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>2942</v>
+        <v>2985</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>1348</v>
@@ -28434,7 +28770,7 @@
         <v>52</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="65" spans="1:14">
@@ -28448,10 +28784,10 @@
         <v>1361</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>2943</v>
+        <v>2986</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>2944</v>
+        <v>2987</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>1368</v>
@@ -28478,7 +28814,7 @@
         <v>52</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="66" spans="1:14">
@@ -28492,10 +28828,10 @@
         <v>1382</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>2945</v>
+        <v>2988</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>2946</v>
+        <v>2989</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>1389</v>
@@ -28522,7 +28858,7 @@
         <v>52</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="67" spans="1:14">
@@ -28536,10 +28872,10 @@
         <v>1403</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>2947</v>
+        <v>2990</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>2948</v>
+        <v>2991</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>1408</v>
@@ -28566,7 +28902,7 @@
         <v>52</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="68" spans="1:14">
@@ -28580,10 +28916,10 @@
         <v>1421</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>2949</v>
+        <v>2992</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>2950</v>
+        <v>2993</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>1428</v>
@@ -28610,7 +28946,7 @@
         <v>52</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="69" spans="1:14">
@@ -28624,10 +28960,10 @@
         <v>1442</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>2951</v>
+        <v>2994</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>2952</v>
+        <v>2995</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>1448</v>
@@ -28654,7 +28990,7 @@
         <v>52</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="70" spans="1:14">
@@ -28668,10 +29004,10 @@
         <v>1460</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>2953</v>
+        <v>2996</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>2954</v>
+        <v>2997</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>1466</v>
@@ -28698,7 +29034,7 @@
         <v>52</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="71" spans="1:14">
@@ -28712,10 +29048,10 @@
         <v>1480</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>2955</v>
+        <v>2998</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>2956</v>
+        <v>2999</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>1486</v>
@@ -28742,7 +29078,7 @@
         <v>52</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="72" spans="1:14">
@@ -28756,10 +29092,10 @@
         <v>1499</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>2957</v>
+        <v>3000</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>2958</v>
+        <v>3001</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>1505</v>
@@ -28786,7 +29122,7 @@
         <v>52</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="73" spans="1:14">
@@ -28800,10 +29136,10 @@
         <v>1518</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>2959</v>
+        <v>3002</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>2960</v>
+        <v>3003</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>1524</v>
@@ -28830,7 +29166,7 @@
         <v>145</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="74" spans="1:14">
@@ -28844,10 +29180,10 @@
         <v>1537</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>2961</v>
+        <v>3004</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>2962</v>
+        <v>3005</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>1544</v>
@@ -28874,7 +29210,7 @@
         <v>52</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="75" spans="1:14">
@@ -28888,10 +29224,10 @@
         <v>1556</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>2963</v>
+        <v>3006</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>2964</v>
+        <v>3007</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>1563</v>
@@ -28918,7 +29254,7 @@
         <v>52</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="76" spans="1:14">
@@ -28932,10 +29268,10 @@
         <v>1576</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>2965</v>
+        <v>3008</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>2966</v>
+        <v>3009</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>1583</v>
@@ -28962,7 +29298,7 @@
         <v>52</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="77" spans="1:14">
@@ -28976,10 +29312,10 @@
         <v>1596</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>2967</v>
+        <v>3010</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>2968</v>
+        <v>3011</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>1602</v>
@@ -29006,7 +29342,7 @@
         <v>52</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="78" spans="1:14">
@@ -29020,10 +29356,10 @@
         <v>1615</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>2969</v>
+        <v>3012</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>2970</v>
+        <v>3013</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>1621</v>
@@ -29050,7 +29386,7 @@
         <v>52</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="79" spans="1:14">
@@ -29064,10 +29400,10 @@
         <v>1634</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>2971</v>
+        <v>3014</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>2972</v>
+        <v>3015</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>1643</v>
@@ -29094,7 +29430,7 @@
         <v>145</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="80" spans="1:14">
@@ -29108,10 +29444,10 @@
         <v>1657</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>2973</v>
+        <v>3016</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>2974</v>
+        <v>3017</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>1665</v>
@@ -29138,7 +29474,7 @@
         <v>189</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="81" spans="1:14">
@@ -29152,10 +29488,10 @@
         <v>1678</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>2975</v>
+        <v>3018</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>2976</v>
+        <v>3019</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>1686</v>
@@ -29182,7 +29518,7 @@
         <v>52</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="82" spans="1:14">
@@ -29196,10 +29532,10 @@
         <v>1700</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>2977</v>
+        <v>3020</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>2978</v>
+        <v>3021</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>1708</v>
@@ -29226,7 +29562,7 @@
         <v>145</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="83" spans="1:14">
@@ -29240,10 +29576,10 @@
         <v>1721</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>2979</v>
+        <v>3022</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>2980</v>
+        <v>3023</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>1730</v>
@@ -29270,7 +29606,7 @@
         <v>52</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="84" spans="1:14">
@@ -29284,10 +29620,10 @@
         <v>1744</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>2981</v>
+        <v>3024</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>2982</v>
+        <v>3025</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>1751</v>
@@ -29314,7 +29650,7 @@
         <v>52</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="85" spans="1:14">
@@ -29328,10 +29664,10 @@
         <v>1765</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>2983</v>
+        <v>3026</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>2984</v>
+        <v>3027</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>1773</v>
@@ -29358,7 +29694,7 @@
         <v>145</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="86" spans="1:14">
@@ -29372,10 +29708,10 @@
         <v>1785</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>2985</v>
+        <v>3028</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>2986</v>
+        <v>3029</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>1793</v>
@@ -29402,7 +29738,7 @@
         <v>52</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="87" spans="1:14">
@@ -29416,10 +29752,10 @@
         <v>1806</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>2987</v>
+        <v>3030</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>2988</v>
+        <v>3031</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>1813</v>
@@ -29446,7 +29782,7 @@
         <v>145</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="88" spans="1:14">
@@ -29460,10 +29796,10 @@
         <v>1826</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>2989</v>
+        <v>3032</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>2990</v>
+        <v>3033</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>1834</v>
@@ -29490,7 +29826,7 @@
         <v>52</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="89" spans="1:14">
@@ -29504,10 +29840,10 @@
         <v>1846</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>2991</v>
+        <v>3034</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>2992</v>
+        <v>3035</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>1854</v>
@@ -29534,7 +29870,7 @@
         <v>52</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="90" spans="1:14">
@@ -29548,10 +29884,10 @@
         <v>1866</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>2993</v>
+        <v>3036</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>2994</v>
+        <v>3037</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>1873</v>
@@ -29578,7 +29914,7 @@
         <v>52</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="91" spans="1:14">
@@ -29592,10 +29928,10 @@
         <v>1884</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>2995</v>
+        <v>3038</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>2996</v>
+        <v>3039</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>1892</v>
@@ -29622,7 +29958,7 @@
         <v>145</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="92" spans="1:14">
@@ -29636,10 +29972,10 @@
         <v>1904</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>2997</v>
+        <v>3040</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>2998</v>
+        <v>3041</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>1912</v>
@@ -29666,7 +30002,7 @@
         <v>189</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="93" spans="1:14">
@@ -29680,10 +30016,10 @@
         <v>1923</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>2999</v>
+        <v>3042</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>3000</v>
+        <v>3043</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>1931</v>
@@ -29710,7 +30046,7 @@
         <v>52</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="94" spans="1:14">
@@ -29724,10 +30060,10 @@
         <v>1943</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>3001</v>
+        <v>3044</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>3002</v>
+        <v>3045</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>1950</v>
@@ -29754,7 +30090,7 @@
         <v>52</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="95" spans="1:14">
@@ -29768,10 +30104,10 @@
         <v>1961</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>3003</v>
+        <v>3046</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>3004</v>
+        <v>3047</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>1968</v>
@@ -29798,7 +30134,7 @@
         <v>52</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="96" spans="1:14">
@@ -29812,10 +30148,10 @@
         <v>1980</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>3005</v>
+        <v>3048</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>3006</v>
+        <v>3049</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>1988</v>
@@ -29842,7 +30178,7 @@
         <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="97" spans="1:14">
@@ -29856,10 +30192,10 @@
         <v>2000</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>3007</v>
+        <v>3050</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>3008</v>
+        <v>3051</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>2006</v>
@@ -29886,7 +30222,7 @@
         <v>52</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="98" spans="1:14">
@@ -29900,10 +30236,10 @@
         <v>2019</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>3009</v>
+        <v>3052</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>3010</v>
+        <v>3053</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>2028</v>
@@ -29930,7 +30266,7 @@
         <v>145</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="99" spans="1:14">
@@ -29944,10 +30280,10 @@
         <v>2041</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>3011</v>
+        <v>3054</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>3012</v>
+        <v>3055</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>2049</v>
@@ -29974,7 +30310,7 @@
         <v>145</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="100" spans="1:14">
@@ -29988,10 +30324,10 @@
         <v>2062</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>3013</v>
+        <v>3056</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>3014</v>
+        <v>3057</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>2069</v>
@@ -30018,7 +30354,7 @@
         <v>145</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="101" spans="1:14">
@@ -30032,10 +30368,10 @@
         <v>2082</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>3015</v>
+        <v>3058</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>3016</v>
+        <v>3059</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>2090</v>
@@ -30062,7 +30398,7 @@
         <v>52</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="102" spans="1:14">
@@ -30076,10 +30412,10 @@
         <v>2102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>3017</v>
+        <v>3060</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>3018</v>
+        <v>3061</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>2110</v>
@@ -30106,7 +30442,7 @@
         <v>145</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="103" spans="1:14">
@@ -30120,10 +30456,10 @@
         <v>2122</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>3019</v>
+        <v>3062</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>3020</v>
+        <v>3063</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>2129</v>
@@ -30150,7 +30486,7 @@
         <v>145</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="104" spans="1:14">
@@ -30164,10 +30500,10 @@
         <v>2142</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3021</v>
+        <v>3064</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>3022</v>
+        <v>3065</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>2149</v>
@@ -30194,7 +30530,7 @@
         <v>145</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="105" spans="1:14">
@@ -30208,10 +30544,10 @@
         <v>2161</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>3023</v>
+        <v>3066</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>3024</v>
+        <v>3067</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>2168</v>
@@ -30238,7 +30574,7 @@
         <v>145</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="106" spans="1:14">
@@ -30252,10 +30588,10 @@
         <v>2181</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>3025</v>
+        <v>3068</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>3026</v>
+        <v>3069</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>2187</v>
@@ -30282,7 +30618,7 @@
         <v>189</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="107" spans="1:14">
@@ -30296,10 +30632,10 @@
         <v>2201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>3027</v>
+        <v>3070</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>3028</v>
+        <v>3071</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>2209</v>
@@ -30326,7 +30662,7 @@
         <v>145</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="108" spans="1:14">
@@ -30340,10 +30676,10 @@
         <v>2222</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>3029</v>
+        <v>3072</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>3030</v>
+        <v>3073</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>2228</v>
@@ -30370,7 +30706,7 @@
         <v>52</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="109" spans="1:14">
@@ -30384,10 +30720,10 @@
         <v>2241</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>3031</v>
+        <v>3074</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>3032</v>
+        <v>3075</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>2247</v>
@@ -30414,7 +30750,7 @@
         <v>52</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="110" spans="1:14">
@@ -30428,10 +30764,10 @@
         <v>2259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>3033</v>
+        <v>3076</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>3034</v>
+        <v>3077</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>2268</v>
@@ -30458,7 +30794,7 @@
         <v>145</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="111" spans="1:14">
@@ -30472,10 +30808,10 @@
         <v>2281</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>3035</v>
+        <v>3078</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>3036</v>
+        <v>3079</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>2289</v>
@@ -30502,7 +30838,7 @@
         <v>52</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="112" spans="1:14">
@@ -30516,10 +30852,10 @@
         <v>2302</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>3037</v>
+        <v>3080</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>3038</v>
+        <v>3081</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>2311</v>
@@ -30546,7 +30882,7 @@
         <v>145</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="113" spans="1:14">
@@ -30560,10 +30896,10 @@
         <v>2324</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>3039</v>
+        <v>3082</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>3040</v>
+        <v>3083</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>2331</v>
@@ -30590,7 +30926,7 @@
         <v>145</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="114" spans="1:14">
@@ -30604,10 +30940,10 @@
         <v>2343</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>3041</v>
+        <v>3084</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>3042</v>
+        <v>3085</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>2350</v>
@@ -30634,7 +30970,7 @@
         <v>145</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="115" spans="1:14">
@@ -30648,10 +30984,10 @@
         <v>2362</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>3043</v>
+        <v>3086</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>3044</v>
+        <v>3087</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>2369</v>
@@ -30678,7 +31014,7 @@
         <v>52</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="116" spans="1:14">
@@ -30692,10 +31028,10 @@
         <v>2381</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>3045</v>
+        <v>3088</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>3046</v>
+        <v>3089</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>2389</v>
@@ -30722,7 +31058,7 @@
         <v>145</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="117" spans="1:14">
@@ -30736,10 +31072,10 @@
         <v>2401</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>3047</v>
+        <v>3090</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>3048</v>
+        <v>3091</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>2410</v>
@@ -30766,7 +31102,7 @@
         <v>145</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="118" spans="1:14">
@@ -30780,10 +31116,10 @@
         <v>2423</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>3049</v>
+        <v>3092</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>3050</v>
+        <v>3093</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>2431</v>
@@ -30810,7 +31146,7 @@
         <v>145</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="119" spans="1:14">
@@ -30824,10 +31160,10 @@
         <v>2443</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>3051</v>
+        <v>3094</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>3052</v>
+        <v>3095</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>2450</v>
@@ -30854,7 +31190,7 @@
         <v>52</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="120" spans="1:14">
@@ -30868,10 +31204,10 @@
         <v>2462</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>3053</v>
+        <v>3096</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>3054</v>
+        <v>3097</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>2470</v>
@@ -30906,10 +31242,10 @@
         <v>2483</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>3055</v>
+        <v>3098</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>3056</v>
+        <v>3099</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>2492</v>
@@ -30944,10 +31280,10 @@
         <v>2503</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>3057</v>
+        <v>3100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>3058</v>
+        <v>3101</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>2508</v>
@@ -30982,10 +31318,10 @@
         <v>2521</v>
       </c>
       <c r="D123" t="s">
-        <v>3059</v>
+        <v>3102</v>
       </c>
       <c r="E123" t="s">
-        <v>3060</v>
+        <v>3103</v>
       </c>
       <c r="F123" t="s">
         <v>2528</v>
@@ -31012,7 +31348,7 @@
         <v>52</v>
       </c>
       <c r="N123" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -31029,7 +31365,7 @@
         <v>2546</v>
       </c>
       <c r="E124" t="s">
-        <v>3062</v>
+        <v>3105</v>
       </c>
       <c r="F124" t="s">
         <v>2547</v>
@@ -31056,7 +31392,7 @@
         <v>52</v>
       </c>
       <c r="N124" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -31073,7 +31409,7 @@
         <v>2564</v>
       </c>
       <c r="E125" t="s">
-        <v>3063</v>
+        <v>3106</v>
       </c>
       <c r="F125" t="s">
         <v>2565</v>
@@ -31100,7 +31436,7 @@
         <v>189</v>
       </c>
       <c r="N125" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -31117,7 +31453,7 @@
         <v>2582</v>
       </c>
       <c r="E126" t="s">
-        <v>3064</v>
+        <v>3107</v>
       </c>
       <c r="G126" t="s">
         <v>2586</v>
@@ -31135,10 +31471,10 @@
         <v>2590</v>
       </c>
       <c r="M126" t="s">
-        <v>3065</v>
+        <v>3108</v>
       </c>
       <c r="N126" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -31155,7 +31491,7 @@
         <v>2601</v>
       </c>
       <c r="E127" t="s">
-        <v>3066</v>
+        <v>3109</v>
       </c>
       <c r="G127" t="s">
         <v>2604</v>
@@ -31176,7 +31512,7 @@
         <v>52</v>
       </c>
       <c r="N127" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -31187,7 +31523,7 @@
         <v>2614</v>
       </c>
       <c r="E128" t="s">
-        <v>3067</v>
+        <v>3110</v>
       </c>
       <c r="G128" t="s">
         <v>2621</v>
@@ -31205,10 +31541,10 @@
         <v>2625</v>
       </c>
       <c r="M128" t="s">
-        <v>3065</v>
+        <v>3108</v>
       </c>
       <c r="N128" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -31219,7 +31555,7 @@
         <v>2632</v>
       </c>
       <c r="E129" t="s">
-        <v>3068</v>
+        <v>3111</v>
       </c>
       <c r="G129" t="s">
         <v>2639</v>
@@ -31237,7 +31573,7 @@
         <v>52</v>
       </c>
       <c r="N129" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -31248,7 +31584,7 @@
         <v>2650</v>
       </c>
       <c r="E130" t="s">
-        <v>3069</v>
+        <v>3112</v>
       </c>
       <c r="G130" t="s">
         <v>2658</v>
@@ -31269,7 +31605,7 @@
         <v>52</v>
       </c>
       <c r="N130" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -31283,7 +31619,7 @@
         <v>2673</v>
       </c>
       <c r="E131" t="s">
-        <v>3070</v>
+        <v>3113</v>
       </c>
       <c r="G131" t="s">
         <v>2676</v>
@@ -31301,7 +31637,7 @@
         <v>52</v>
       </c>
       <c r="N131" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -31312,7 +31648,7 @@
         <v>2687</v>
       </c>
       <c r="E132" t="s">
-        <v>3071</v>
+        <v>3114</v>
       </c>
       <c r="G132" t="s">
         <v>2695</v>
@@ -31333,7 +31669,7 @@
         <v>52</v>
       </c>
       <c r="N132" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -31347,7 +31683,7 @@
         <v>2705</v>
       </c>
       <c r="E133" t="s">
-        <v>3072</v>
+        <v>3115</v>
       </c>
       <c r="I133" t="s">
         <v>2714</v>
@@ -31362,7 +31698,7 @@
         <v>52</v>
       </c>
       <c r="N133" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -31373,7 +31709,7 @@
         <v>2722</v>
       </c>
       <c r="E134" t="s">
-        <v>3073</v>
+        <v>3116</v>
       </c>
       <c r="I134" t="s">
         <v>2733</v>
@@ -31385,7 +31721,7 @@
         <v>52</v>
       </c>
       <c r="N134" t="s">
-        <v>3061</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -31396,7 +31732,7 @@
         <v>2744</v>
       </c>
       <c r="E135" t="s">
-        <v>3074</v>
+        <v>3117</v>
       </c>
       <c r="G135" t="s">
         <v>2754</v>
@@ -31417,7 +31753,47 @@
         <v>52</v>
       </c>
       <c r="N135" t="s">
-        <v>3061</v>
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
+      <c r="A136" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2765</v>
+      </c>
+      <c r="E136" t="s">
+        <v>3118</v>
+      </c>
+      <c r="J136" t="s">
+        <v>3119</v>
+      </c>
+      <c r="M136" t="s">
+        <v>52</v>
+      </c>
+      <c r="N136" t="s">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14">
+      <c r="A137" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E137" t="s">
+        <v>3120</v>
+      </c>
+      <c r="J137" t="s">
+        <v>3121</v>
+      </c>
+      <c r="M137" t="s">
+        <v>52</v>
+      </c>
+      <c r="N137" t="s">
+        <v>3104</v>
       </c>
     </row>
   </sheetData>
@@ -31431,7 +31807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="2" min="1" width="50"/>
@@ -31439,106 +31815,114 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>3075</v>
+        <v>3122</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>3076</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3077</v>
+        <v>3124</v>
       </c>
       <c r="B2" t="s">
-        <v>2770</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3078</v>
+        <v>3125</v>
       </c>
       <c r="B3" t="s">
-        <v>3079</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3080</v>
+        <v>3127</v>
       </c>
       <c r="B4" t="s">
-        <v>3081</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3082</v>
+        <v>3129</v>
       </c>
       <c r="B5" t="s">
-        <v>3083</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3084</v>
+        <v>3131</v>
       </c>
       <c r="B6" t="s">
-        <v>3085</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3086</v>
+        <v>3133</v>
       </c>
       <c r="B7" t="s">
-        <v>3087</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3088</v>
+        <v>3135</v>
       </c>
       <c r="B8" t="s">
-        <v>3089</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3090</v>
+        <v>3137</v>
       </c>
       <c r="B9" t="s">
-        <v>3091</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3092</v>
+        <v>3139</v>
       </c>
       <c r="B10" t="s">
-        <v>3093</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3094</v>
+        <v>3141</v>
       </c>
       <c r="B11" t="s">
-        <v>3095</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3096</v>
+        <v>3143</v>
       </c>
       <c r="B12" t="s">
-        <v>3097</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3098</v>
+        <v>3145</v>
       </c>
       <c r="B13" t="s">
-        <v>3099</v>
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>3147</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3148</v>
       </c>
     </row>
   </sheetData>
@@ -31557,82 +31941,82 @@
   <sheetData>
     <row customHeight="1" ht="27.6" r="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>3100</v>
+        <v>3149</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3101</v>
+        <v>3150</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>3102</v>
+        <v>3151</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3103</v>
+        <v>3152</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3104</v>
+        <v>3153</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>3105</v>
+        <v>3154</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3106</v>
+        <v>3155</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3107</v>
+        <v>3156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3108</v>
+        <v>3157</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3109</v>
+        <v>3158</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3110</v>
+        <v>3159</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1681</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3107</v>
+        <v>3156</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3108</v>
+        <v>3157</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1674</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3109</v>
+        <v>3158</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3111</v>
+        <v>3160</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3107</v>
+        <v>3156</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3108</v>
+        <v>3157</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3109</v>
+        <v>3158</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="5" spans="1:6">
@@ -31643,16 +32027,16 @@
         <v>2204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="6" spans="1:6">
@@ -31663,16 +32047,16 @@
         <v>2223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="7" spans="1:6">
@@ -31683,16 +32067,16 @@
         <v>2243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="8" spans="1:6">
@@ -31703,16 +32087,16 @@
         <v>2262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:6">
@@ -31723,16 +32107,16 @@
         <v>2283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="10" spans="1:6">
@@ -31743,16 +32127,16 @@
         <v>2305</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:6">
@@ -31763,16 +32147,16 @@
         <v>2326</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:6">
@@ -31783,16 +32167,16 @@
         <v>2346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="13" spans="1:6">
@@ -31803,16 +32187,16 @@
         <v>2364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="14" spans="1:6">
@@ -31823,16 +32207,16 @@
         <v>2383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:6">
@@ -31843,16 +32227,16 @@
         <v>2404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="16" spans="1:6">
@@ -31863,16 +32247,16 @@
         <v>2425</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:6">
@@ -31883,96 +32267,96 @@
         <v>2445</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>3113</v>
+        <v>3162</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3114</v>
+        <v>3163</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3115</v>
+        <v>3164</v>
       </c>
     </row>
     <row customHeight="1" ht="303.6" r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>3116</v>
+        <v>3165</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3117</v>
+        <v>3166</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3107</v>
+        <v>3156</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>3118</v>
+        <v>3167</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>610</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3119</v>
+        <v>3168</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>3120</v>
+        <v>3169</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3121</v>
+        <v>3170</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3122</v>
+        <v>3171</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3123</v>
+        <v>3172</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>2458</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
     </row>
     <row customHeight="1" ht="193.2" r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>3124</v>
+        <v>3173</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3125</v>
+        <v>3174</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3122</v>
+        <v>3171</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3123</v>
+        <v>3172</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>2479</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>3126</v>
+        <v>3175</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3127</v>
+        <v>3176</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3122</v>
+        <v>3171</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>3123</v>
+        <v>3172</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>3112</v>
+        <v>3161</v>
       </c>
     </row>
   </sheetData>
@@ -31986,7 +32370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="2" min="1" width="42"/>
@@ -31994,15 +32378,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>3128</v>
+        <v>3177</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3129</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3130</v>
+        <v>3179</v>
       </c>
       <c r="B2" t="n">
         <v>118</v>
@@ -32010,7 +32394,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3131</v>
+        <v>3180</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -32018,7 +32402,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3132</v>
+        <v>3181</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -32026,7 +32410,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3133</v>
+        <v>3182</v>
       </c>
       <c r="B5" t="s">
         <v>2440</v>
@@ -32034,66 +32418,74 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3134</v>
+        <v>3183</v>
       </c>
       <c r="B6" t="s">
-        <v>3135</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3136</v>
+        <v>3185</v>
       </c>
       <c r="B7" t="s">
-        <v>3137</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3138</v>
+        <v>3187</v>
       </c>
       <c r="B8" t="s">
-        <v>3139</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3140</v>
+        <v>3189</v>
       </c>
       <c r="B9" t="s">
-        <v>3141</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3092</v>
+        <v>3139</v>
       </c>
       <c r="B10" t="s">
-        <v>3093</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3142</v>
+        <v>3191</v>
       </c>
       <c r="B11" t="s">
-        <v>3137</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3143</v>
+        <v>3192</v>
       </c>
       <c r="B12" t="s">
-        <v>3144</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3145</v>
+        <v>3194</v>
       </c>
       <c r="B13" t="s">
-        <v>3146</v>
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3197</v>
       </c>
     </row>
   </sheetData>

--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="4" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16776" windowWidth="30936" xWindow="-108" yWindow="-108"/>
+    <workbookView activeTab="6" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16776" windowWidth="30936" xWindow="-108" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整文献矩阵" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3207">
   <si>
     <t>序号</t>
   </si>
@@ -8467,7 +8467,7 @@
     <t>累计文献数</t>
   </si>
   <si>
-    <t>2026-07-10 更新</t>
+    <t>2026-07-24 更新</t>
   </si>
   <si>
     <t>本批新增</t>
@@ -9930,6 +9930,9 @@
 【创新点】将 PSO-ELM 用于地质工程一体化压裂甜点评价
 【局限性】跨区块泛化需验证；机器学习可解释性需增强
 【与你课题的关系】可作为响应差异的地质工程背景变量参考</t>
+  </si>
+  <si>
+    <t>由 Daily Brief 生成；待全文精读增强</t>
   </si>
   <si>
     <t>研究区/对象：Ordos Basin；Deep coal measures; No. 8 coal seam；深度：No. 8 seam thickness 6-16 m, average 7.8 m。</t>
@@ -9969,9 +9972,6 @@
 论文引言、理论基础和讨论章节的术语统一。</t>
   </si>
   <si>
-    <t>由 Daily Brief 生成；待全文精读增强</t>
-  </si>
-  <si>
     <t>【研究目的】该文研究煤岩气聚集过渡带的形成机制，重点应涉及煤岩气在区域成藏体系中的空间过渡、气体富集差异和地质边界特征。
 【数据/方法】官方页面能够稳定核验题名、作者、卷期、页码、DOI 和出版日期，但摘要内容未正常加载。当前无法确认研究区、样品量、测井资料、地球化学数据或数值模拟方法。Codex 入库时应从 PDF 或正式中文页面补齐这些字段。
 【核心发现】根据题名可确认文章提出或解释了煤岩气聚集过渡带的形成机制，但具体机制组成、控制因素和区域适用性尚不能从当前公开页面可靠提取。
@@ -10007,6 +10007,9 @@
 【局限性】深度阈值和压裂体系不可直接外推。</t>
   </si>
   <si>
+    <t>未指定具体区块（实验与分子模拟研究）; 深部煤岩；吸附态甲烷; 深部煤岩储层（实验条件模拟深部温压）</t>
+  </si>
+  <si>
     <t>【数据/方法】渗吸、孔隙表征、吸附/解吸和分子动力学。
 【核心发现】0.3–1.5 nm 孔尺度增加 59.6%，2–10 nm 增加 44.8%；CH₄—煤配位数 16.2→12.3，水—煤 0→9.6；模拟能垒约 1500→800 kJ/mol。
 【创新点】统一解释润湿性、孔隙重构和水膜竞争吸附。
@@ -10014,10 +10017,17 @@
 【与你课题的关系】水锁、液相滞留、解吸启动、裂缝—基质传质。</t>
   </si>
   <si>
+    <t>鄂尔多斯东缘本溪组 3 口井、17 件煤样。
+- 方法：工业分析、CO₂ 吸附、高温高压甲烷吸附、等量吸附热; 鄂尔多斯东缘本溪组深部煤储层；3口井17件煤样; 鄂尔多斯东缘本溪组深部煤层</t>
+  </si>
+  <si>
     <t>【数据/方法】工业分析、CO₂ 吸附、高温高压甲烷吸附、等量吸附热和模型预测。
 【核心发现】灰分总体削弱微孔和吸附，固定碳/微孔与 Langmuir 体积正相关；升温降低吸附，升压提高吸附。
 【局限性】模型受煤阶和实验温压范围约束，吸附容量不等于可采气量。
 【与你课题的关系】温压背景、吸附/游离气和资料边界。</t>
+  </si>
+  <si>
+    <t>未指定具体区块（材料研发与室内实验）; 深部煤层气返排液；超耐盐滑溜水压裂液; 深部煤层气储层（TDS &gt;120,000 mg/L 高矿化度条件）</t>
   </si>
   <si>
     <t>【数据/方法】超高矿化度配伍、流变、减阻、携砂、破胶、残渣和分子模拟。
@@ -10033,18 +10043,30 @@
 【与你课题的关系】微孔吸附、中大孔渗流、裂缝—基质传质。</t>
   </si>
   <si>
+    <t>长庆矿区 10 口井、132 个压裂段；8 口完整井 105 段用于主分析，2 口井 27 段用于独立验; 长庆矿区10口深部煤层气水平井；132个压裂段; 长庆矿区深部煤层气储层</t>
+  </si>
+  <si>
     <t>【数据/方法】水相/气相示踪、Pearson、Random Forest 和段级生产贡献解释。
 【核心发现】外部研究识别 3 种段间产出形态；一类煤钻遇长度与初始产气的幂律 R²=0.71；保留测试集 R²=0.83；提出差异化压裂窗口。
 【创新点】把段级示踪、生产剖面和机器学习闭环结合。
 【局限性】外部分类和特征重要性不得变成用户项目正式类型或主控因素排序。</t>
   </si>
   <si>
+    <t>未指定具体区块（理论与工程思考）; 深部煤岩气储层；人工裂缝与天然割理系统; 深部煤岩气储层</t>
+  </si>
+  <si>
     <t>【创新点】从吸附气—游离气连续供气角度连接基质、割理和人工裂缝。
 【局限性】以理论和工程思考为主，不能替代用户项目压裂施工、示踪或导流能力资料。</t>
   </si>
   <si>
+    <t>综述（未限定具体区块）; 深部煤层气赋存机理（成因、演化、温压应力、吸附/游离气等）; 综述（涵盖不同深度范围）</t>
+  </si>
+  <si>
     <t>【创新点】尝试整合临界深度、裂缝渗流—基质扩散及生产模型。
 【局限性】综述不能替代项目证据；不得编造 DOI。</t>
+  </si>
+  <si>
+    <t>未指定具体区块（分子模拟研究）; 纳米狭缝孔中甲烷吸附态与游离态密度; 深部煤层纳米孔隙（模拟深部温压条件）</t>
   </si>
   <si>
     <t>【数据/方法】狭缝纳米孔模拟、Peng–Robinson 状态方程修正、限域逸度—压力、吸附相/游离相密度和煤阶修正。
@@ -10054,10 +10076,16 @@
 【与你课题的关系】早期游离气贡献和相态评价边界。</t>
   </si>
   <si>
+    <t>鄂尔多斯盆地东缘；石炭系本溪组; 深部煤层气储层（双重孔隙体系，埋深1500-2300 m）; 1500-2300 m；平均厚度约12 m</t>
+  </si>
+  <si>
     <t>【局限性】间接地球物理证据不能替代生产因果验证。</t>
   </si>
   <si>
     <t>间接地球物理证据不能替代生产因果验证。</t>
+  </si>
+  <si>
+    <t>华北4个煤层气区：沁水盆地南部、宁武盆地南部、鄂尔多斯盆地东缘神府区块、临兴区块; 煤层气藏（69口生产井；不同埋深/煤阶/水动力条件）</t>
   </si>
   <si>
     <t>【局限性】生产动态不能直接识别气源或微生物机制；</t>
@@ -10431,7 +10459,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMComplete105" headerRowCount="1" id="1" name="DeepCBMComplete105" ref="A1:AA135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="DeepCBMComplete105" headerRowCount="1" id="1" name="DeepCBMComplete105" ref="A1:AA137">
   <tableColumns count="27">
     <tableColumn id="1" name="序号"/>
     <tableColumn id="2" name="文献ID"/>
@@ -21782,7 +21810,6 @@
       <c r="I136" t="s">
         <v>2767</v>
       </c>
-      <c r="J136" t="s"/>
       <c r="K136" t="s">
         <v>2768</v>
       </c>
@@ -21934,7 +21961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="6" min="1" width="22"/>
@@ -22173,7 +22200,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="s">
@@ -22184,6 +22211,15 @@
       </c>
       <c r="F16" s="3" t="n"/>
     </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -31224,12 +31260,18 @@
       <c r="J120" s="1" t="s">
         <v>2474</v>
       </c>
-      <c r="K120" s="1" t="n"/>
-      <c r="L120" s="1" t="n"/>
+      <c r="K120" s="1" t="s">
+        <v>2475</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>2476</v>
+      </c>
       <c r="M120" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N120" s="1" t="n"/>
+      <c r="N120" s="1" t="s">
+        <v>3098</v>
+      </c>
     </row>
     <row customHeight="1" ht="82.8" r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -31242,10 +31284,10 @@
         <v>2483</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>2492</v>
@@ -31262,12 +31304,18 @@
       <c r="J121" s="1" t="s">
         <v>2496</v>
       </c>
-      <c r="K121" s="1" t="n"/>
-      <c r="L121" s="1" t="n"/>
+      <c r="K121" s="1" t="s">
+        <v>2497</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>2476</v>
+      </c>
       <c r="M121" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N121" s="1" t="n"/>
+      <c r="N121" s="1" t="s">
+        <v>3098</v>
+      </c>
     </row>
     <row customHeight="1" ht="82.8" r="122" spans="1:14">
       <c r="A122" s="1" t="s">
@@ -31280,10 +31328,10 @@
         <v>2503</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>2508</v>
@@ -31300,12 +31348,18 @@
       <c r="J122" s="1" t="s">
         <v>2512</v>
       </c>
-      <c r="K122" s="1" t="n"/>
-      <c r="L122" s="1" t="n"/>
+      <c r="K122" s="1" t="s">
+        <v>2513</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>2514</v>
+      </c>
       <c r="M122" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N122" s="1" t="n"/>
+      <c r="N122" s="1" t="s">
+        <v>3098</v>
+      </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
@@ -31318,10 +31372,10 @@
         <v>2521</v>
       </c>
       <c r="D123" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="E123" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="F123" t="s">
         <v>2528</v>
@@ -31348,7 +31402,7 @@
         <v>52</v>
       </c>
       <c r="N123" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -31392,7 +31446,7 @@
         <v>52</v>
       </c>
       <c r="N124" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -31436,7 +31490,7 @@
         <v>189</v>
       </c>
       <c r="N125" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -31455,6 +31509,9 @@
       <c r="E126" t="s">
         <v>3107</v>
       </c>
+      <c r="F126" t="s">
+        <v>2585</v>
+      </c>
       <c r="G126" t="s">
         <v>2586</v>
       </c>
@@ -31467,6 +31524,9 @@
       <c r="J126" t="s">
         <v>2589</v>
       </c>
+      <c r="K126" t="s">
+        <v>2590</v>
+      </c>
       <c r="L126" t="s">
         <v>2590</v>
       </c>
@@ -31474,7 +31534,7 @@
         <v>3108</v>
       </c>
       <c r="N126" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -31493,6 +31553,9 @@
       <c r="E127" t="s">
         <v>3109</v>
       </c>
+      <c r="F127" t="s">
+        <v>2603</v>
+      </c>
       <c r="G127" t="s">
         <v>2604</v>
       </c>
@@ -31505,6 +31568,9 @@
       <c r="J127" t="s">
         <v>2607</v>
       </c>
+      <c r="K127" t="s">
+        <v>2608</v>
+      </c>
       <c r="L127" t="s">
         <v>2608</v>
       </c>
@@ -31512,18 +31578,27 @@
         <v>52</v>
       </c>
       <c r="N127" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
         <v>2610</v>
       </c>
+      <c r="B128" t="s">
+        <v>31</v>
+      </c>
       <c r="C128" t="s">
         <v>2614</v>
       </c>
+      <c r="D128" t="s">
+        <v>3110</v>
+      </c>
       <c r="E128" t="s">
-        <v>3110</v>
+        <v>3111</v>
+      </c>
+      <c r="F128" t="s">
+        <v>2620</v>
       </c>
       <c r="G128" t="s">
         <v>2621</v>
@@ -31540,22 +31615,34 @@
       <c r="K128" t="s">
         <v>2625</v>
       </c>
+      <c r="L128" t="s">
+        <v>2626</v>
+      </c>
       <c r="M128" t="s">
         <v>3108</v>
       </c>
       <c r="N128" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>2628</v>
       </c>
+      <c r="B129" t="s">
+        <v>31</v>
+      </c>
       <c r="C129" t="s">
         <v>2632</v>
       </c>
+      <c r="D129" t="s">
+        <v>3112</v>
+      </c>
       <c r="E129" t="s">
-        <v>3111</v>
+        <v>3113</v>
+      </c>
+      <c r="F129" t="s">
+        <v>2638</v>
       </c>
       <c r="G129" t="s">
         <v>2639</v>
@@ -31563,28 +31650,43 @@
       <c r="H129" t="s">
         <v>2640</v>
       </c>
+      <c r="I129" t="s">
+        <v>2641</v>
+      </c>
       <c r="J129" t="s">
         <v>2642</v>
       </c>
       <c r="K129" t="s">
         <v>2643</v>
       </c>
+      <c r="L129" t="s">
+        <v>2644</v>
+      </c>
       <c r="M129" t="s">
         <v>52</v>
       </c>
       <c r="N129" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>2646</v>
       </c>
+      <c r="B130" t="s">
+        <v>31</v>
+      </c>
       <c r="C130" t="s">
         <v>2650</v>
       </c>
+      <c r="D130" t="s">
+        <v>3114</v>
+      </c>
       <c r="E130" t="s">
-        <v>3112</v>
+        <v>3115</v>
+      </c>
+      <c r="F130" t="s">
+        <v>2657</v>
       </c>
       <c r="G130" t="s">
         <v>2658</v>
@@ -31601,17 +31703,23 @@
       <c r="K130" t="s">
         <v>2662</v>
       </c>
+      <c r="L130" t="s">
+        <v>2663</v>
+      </c>
       <c r="M130" t="s">
         <v>52</v>
       </c>
       <c r="N130" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>2665</v>
       </c>
+      <c r="B131" t="s">
+        <v>31</v>
+      </c>
       <c r="C131" t="s">
         <v>2669</v>
       </c>
@@ -31619,7 +31727,10 @@
         <v>2673</v>
       </c>
       <c r="E131" t="s">
-        <v>3113</v>
+        <v>3116</v>
+      </c>
+      <c r="F131" t="s">
+        <v>2675</v>
       </c>
       <c r="G131" t="s">
         <v>2676</v>
@@ -31627,28 +31738,43 @@
       <c r="H131" t="s">
         <v>2677</v>
       </c>
+      <c r="I131" t="s">
+        <v>2678</v>
+      </c>
       <c r="J131" t="s">
         <v>2679</v>
       </c>
       <c r="K131" t="s">
         <v>2680</v>
       </c>
+      <c r="L131" t="s">
+        <v>2681</v>
+      </c>
       <c r="M131" t="s">
         <v>52</v>
       </c>
       <c r="N131" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>2683</v>
       </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
       <c r="C132" t="s">
         <v>2687</v>
       </c>
+      <c r="D132" t="s">
+        <v>3117</v>
+      </c>
       <c r="E132" t="s">
-        <v>3114</v>
+        <v>3118</v>
+      </c>
+      <c r="F132" t="s">
+        <v>2694</v>
       </c>
       <c r="G132" t="s">
         <v>2695</v>
@@ -31662,6 +31788,9 @@
       <c r="J132" t="s">
         <v>2698</v>
       </c>
+      <c r="K132" t="s">
+        <v>2699</v>
+      </c>
       <c r="L132" t="s">
         <v>2699</v>
       </c>
@@ -31669,7 +31798,7 @@
         <v>52</v>
       </c>
       <c r="N132" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -31682,8 +31811,20 @@
       <c r="C133" t="s">
         <v>2705</v>
       </c>
+      <c r="D133" t="s">
+        <v>3119</v>
+      </c>
       <c r="E133" t="s">
-        <v>3115</v>
+        <v>3120</v>
+      </c>
+      <c r="F133" t="s">
+        <v>2711</v>
+      </c>
+      <c r="G133" t="s">
+        <v>2712</v>
+      </c>
+      <c r="H133" t="s">
+        <v>2713</v>
       </c>
       <c r="I133" t="s">
         <v>2714</v>
@@ -31691,6 +31832,9 @@
       <c r="J133" t="s">
         <v>2715</v>
       </c>
+      <c r="K133" t="s">
+        <v>2716</v>
+      </c>
       <c r="L133" t="s">
         <v>2716</v>
       </c>
@@ -31698,18 +31842,33 @@
         <v>52</v>
       </c>
       <c r="N133" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>2718</v>
       </c>
+      <c r="B134" t="s">
+        <v>31</v>
+      </c>
       <c r="C134" t="s">
         <v>2722</v>
       </c>
+      <c r="D134" t="s">
+        <v>3121</v>
+      </c>
       <c r="E134" t="s">
-        <v>3116</v>
+        <v>3122</v>
+      </c>
+      <c r="F134" t="s">
+        <v>2730</v>
+      </c>
+      <c r="G134" t="s">
+        <v>2731</v>
+      </c>
+      <c r="H134" t="s">
+        <v>2732</v>
       </c>
       <c r="I134" t="s">
         <v>2733</v>
@@ -31717,22 +31876,37 @@
       <c r="J134" t="s">
         <v>2734</v>
       </c>
+      <c r="K134" t="s">
+        <v>2735</v>
+      </c>
+      <c r="L134" t="s">
+        <v>2736</v>
+      </c>
       <c r="M134" t="s">
         <v>52</v>
       </c>
       <c r="N134" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>2739</v>
       </c>
+      <c r="B135" t="s">
+        <v>2742</v>
+      </c>
       <c r="C135" t="s">
         <v>2744</v>
       </c>
+      <c r="D135" t="s">
+        <v>3123</v>
+      </c>
       <c r="E135" t="s">
-        <v>3117</v>
+        <v>3124</v>
+      </c>
+      <c r="F135" t="s">
+        <v>2753</v>
       </c>
       <c r="G135" t="s">
         <v>2754</v>
@@ -31749,51 +31923,102 @@
       <c r="K135" t="s">
         <v>2758</v>
       </c>
+      <c r="L135" t="s">
+        <v>2759</v>
+      </c>
       <c r="M135" t="s">
         <v>52</v>
       </c>
       <c r="N135" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>2761</v>
       </c>
+      <c r="B136" t="s">
+        <v>31</v>
+      </c>
       <c r="C136" t="s">
         <v>2765</v>
       </c>
+      <c r="D136" t="s">
+        <v>3125</v>
+      </c>
       <c r="E136" t="s">
-        <v>3118</v>
+        <v>3126</v>
+      </c>
+      <c r="F136" t="s">
+        <v>2774</v>
+      </c>
+      <c r="G136" t="s">
+        <v>2775</v>
+      </c>
+      <c r="H136" t="s">
+        <v>2776</v>
+      </c>
+      <c r="I136" t="s">
+        <v>2777</v>
       </c>
       <c r="J136" t="s">
-        <v>3119</v>
+        <v>3127</v>
+      </c>
+      <c r="K136" t="s">
+        <v>2779</v>
+      </c>
+      <c r="L136" t="s">
+        <v>2780</v>
       </c>
       <c r="M136" t="s">
         <v>52</v>
       </c>
       <c r="N136" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>2783</v>
       </c>
+      <c r="B137" t="s">
+        <v>2786</v>
+      </c>
       <c r="C137" t="s">
         <v>2788</v>
       </c>
+      <c r="D137" t="s">
+        <v>3128</v>
+      </c>
       <c r="E137" t="s">
-        <v>3120</v>
+        <v>3129</v>
+      </c>
+      <c r="F137" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G137" t="s">
+        <v>2796</v>
+      </c>
+      <c r="H137" t="s">
+        <v>2797</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2798</v>
       </c>
       <c r="J137" t="s">
-        <v>3121</v>
+        <v>3130</v>
+      </c>
+      <c r="K137" t="s">
+        <v>2800</v>
+      </c>
+      <c r="L137" t="s">
+        <v>2801</v>
       </c>
       <c r="M137" t="s">
         <v>52</v>
       </c>
       <c r="N137" t="s">
-        <v>3104</v>
+        <v>3098</v>
       </c>
     </row>
   </sheetData>
@@ -31810,20 +32035,21 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" max="2" min="1" width="50"/>
+    <col customWidth="1" max="1" min="1" width="50"/>
+    <col customWidth="1" max="2" min="2" width="49.09765625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>3122</v>
+        <v>3131</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>3123</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3124</v>
+        <v>3133</v>
       </c>
       <c r="B2" t="s">
         <v>2813</v>
@@ -31831,98 +32057,98 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3125</v>
+        <v>3134</v>
       </c>
       <c r="B3" t="s">
-        <v>3126</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3127</v>
+        <v>3136</v>
       </c>
       <c r="B4" t="s">
-        <v>3128</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3129</v>
+        <v>3138</v>
       </c>
       <c r="B5" t="s">
-        <v>3130</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3131</v>
+        <v>3140</v>
       </c>
       <c r="B6" t="s">
-        <v>3132</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3133</v>
+        <v>3142</v>
       </c>
       <c r="B7" t="s">
-        <v>3134</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3135</v>
+        <v>3144</v>
       </c>
       <c r="B8" t="s">
-        <v>3136</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3137</v>
+        <v>3146</v>
       </c>
       <c r="B9" t="s">
-        <v>3138</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3139</v>
+        <v>3148</v>
       </c>
       <c r="B10" t="s">
-        <v>3140</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3141</v>
+        <v>3150</v>
       </c>
       <c r="B11" t="s">
-        <v>3142</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3143</v>
+        <v>3152</v>
       </c>
       <c r="B12" t="s">
-        <v>3144</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3145</v>
+        <v>3154</v>
       </c>
       <c r="B13" t="s">
-        <v>3146</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3147</v>
+        <v>3156</v>
       </c>
       <c r="B14" t="s">
-        <v>3148</v>
+        <v>3157</v>
       </c>
     </row>
   </sheetData>
@@ -31941,82 +32167,82 @@
   <sheetData>
     <row customHeight="1" ht="27.6" r="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>3149</v>
+        <v>3158</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3150</v>
+        <v>3159</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>3151</v>
+        <v>3160</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3152</v>
+        <v>3161</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3153</v>
+        <v>3162</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>3154</v>
+        <v>3163</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3155</v>
+        <v>3164</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3156</v>
+        <v>3165</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3157</v>
+        <v>3166</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3158</v>
+        <v>3167</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3159</v>
+        <v>3168</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1681</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3156</v>
+        <v>3165</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3157</v>
+        <v>3166</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1674</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3158</v>
+        <v>3167</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3160</v>
+        <v>3169</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3156</v>
+        <v>3165</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3157</v>
+        <v>3166</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3158</v>
+        <v>3167</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="5" spans="1:6">
@@ -32027,16 +32253,16 @@
         <v>2204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="6" spans="1:6">
@@ -32047,16 +32273,16 @@
         <v>2223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="7" spans="1:6">
@@ -32067,16 +32293,16 @@
         <v>2243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="8" spans="1:6">
@@ -32087,16 +32313,16 @@
         <v>2262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:6">
@@ -32107,16 +32333,16 @@
         <v>2283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="10" spans="1:6">
@@ -32127,16 +32353,16 @@
         <v>2305</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:6">
@@ -32147,16 +32373,16 @@
         <v>2326</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:6">
@@ -32167,16 +32393,16 @@
         <v>2346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="13" spans="1:6">
@@ -32187,16 +32413,16 @@
         <v>2364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="14" spans="1:6">
@@ -32207,16 +32433,16 @@
         <v>2383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:6">
@@ -32227,16 +32453,16 @@
         <v>2404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="16" spans="1:6">
@@ -32247,16 +32473,16 @@
         <v>2425</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:6">
@@ -32267,96 +32493,96 @@
         <v>2445</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>3162</v>
+        <v>3171</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3164</v>
+        <v>3173</v>
       </c>
     </row>
     <row customHeight="1" ht="303.6" r="18" spans="1:6">
       <c r="A18" s="1" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>3165</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>3166</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3156</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>3167</v>
+        <v>3176</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>610</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3168</v>
+        <v>3177</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>3169</v>
+        <v>3178</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3170</v>
+        <v>3179</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3171</v>
+        <v>3180</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3172</v>
+        <v>3181</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>2458</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
     </row>
     <row customHeight="1" ht="193.2" r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>3173</v>
+        <v>3182</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3174</v>
+        <v>3183</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3171</v>
+        <v>3180</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3172</v>
+        <v>3181</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>2479</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>3175</v>
+        <v>3184</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3176</v>
+        <v>3185</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3171</v>
+        <v>3180</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>3172</v>
+        <v>3181</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>3161</v>
+        <v>3170</v>
       </c>
     </row>
   </sheetData>
@@ -32378,15 +32604,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>3177</v>
+        <v>3186</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3178</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3179</v>
+        <v>3188</v>
       </c>
       <c r="B2" t="n">
         <v>118</v>
@@ -32394,7 +32620,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3180</v>
+        <v>3189</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -32402,7 +32628,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3181</v>
+        <v>3190</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -32410,7 +32636,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3182</v>
+        <v>3191</v>
       </c>
       <c r="B5" t="s">
         <v>2440</v>
@@ -32418,74 +32644,74 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3183</v>
+        <v>3192</v>
       </c>
       <c r="B6" t="s">
-        <v>3184</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3185</v>
+        <v>3194</v>
       </c>
       <c r="B7" t="s">
-        <v>3186</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3187</v>
+        <v>3196</v>
       </c>
       <c r="B8" t="s">
-        <v>3188</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3189</v>
+        <v>3198</v>
       </c>
       <c r="B9" t="s">
-        <v>3190</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3139</v>
+        <v>3148</v>
       </c>
       <c r="B10" t="s">
-        <v>3140</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3191</v>
+        <v>3200</v>
       </c>
       <c r="B11" t="s">
-        <v>3186</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3192</v>
+        <v>3201</v>
       </c>
       <c r="B12" t="s">
-        <v>3193</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3194</v>
+        <v>3203</v>
       </c>
       <c r="B13" t="s">
-        <v>3195</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3196</v>
+        <v>3205</v>
       </c>
       <c r="B14" t="s">
-        <v>3197</v>
+        <v>3206</v>
       </c>
     </row>
   </sheetData>

--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3281">
   <si>
     <t>序号</t>
   </si>
@@ -8455,6 +8455,189 @@
     <t>出版商题名/DOI/卷期/摘要和研究设计已核验；作者缩写待Crossref补全</t>
   </si>
   <si>
+    <t>DCBM-137</t>
+  </si>
+  <si>
+    <t>Wang, Tao</t>
+  </si>
+  <si>
+    <t>Wang, Tao; Huang, Daojun; Ding, Rong; Cao, Yimin; Zhou, Ke; Zhou, Guoxiao; Shi, Yunhe; Wang, Huaichang; Hu, Jianling; Jiao, Pengfei; Feng, Zongqi; Deng, Ze</t>
+  </si>
+  <si>
+    <t>Evaluation of gas content prediction models for deep coal seams: A case study from the Daning-Jixian Block, Eastern Ordos Basin</t>
+  </si>
+  <si>
+    <t>深部煤层含气量预测模型评价：以鄂尔多斯盆地东缘大宁-吉县区块为例</t>
+  </si>
+  <si>
+    <t>110079</t>
+  </si>
+  <si>
+    <t>10.1016/j.rineng.2026.110079</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2590123026011163</t>
+  </si>
+  <si>
+    <t>鄂尔多斯盆地东缘大宁-吉县区块</t>
+  </si>
+  <si>
+    <t>深部煤层（吸附气/游离气/总含气量）</t>
+  </si>
+  <si>
+    <t>深部煤层（大宁-吉县区块深部储层）</t>
+  </si>
+  <si>
+    <t>评价并对比多种含气量预测模型在大宁-吉县区块深部煤层中的适用性</t>
+  </si>
+  <si>
+    <t>4口井煤心解吸/等温吸附/Langmuir模型；BP神经网络/随机森林/XGBoost/CNN-LSTM-Attention；k-fold交叉验证(5折/10折)；深度校正</t>
+  </si>
+  <si>
+    <t>CNN-LSTM-Attention表现最优(RMSE 0.82 m3/t, R2 0.93, MAE 0.61 m3/t)；XGBoost次之(RMSE 0.99 m3/t, R2 0.90)；传统Langmuir模型表现最差(R2 0.71)；游离气占比预测对含气量总量预测至关重要；Attention机制可自动加权关键测井曲线</t>
+  </si>
+  <si>
+    <t>系统对比传统模型到深度学习模型的含气量预测；将游离气/吸附气分开预测再汇总；引入Attention机制自动加权测井曲线</t>
+  </si>
+  <si>
+    <t>4口井样本量有限；CNN-LSTM-Attention可解释性低于传统模型；结果具有区块和煤阶特异性</t>
+  </si>
+  <si>
+    <t>含气量预测/地质建模/游离气-吸附气分配/深度学习适用性与边界</t>
+  </si>
+  <si>
+    <t>地质建模与含气量；研究局限与方法边界；后续可引入的机器学习补充资料</t>
+  </si>
+  <si>
+    <t>gas content prediction; deep learning; CNN-LSTM-Attention; XGBoost; Daning-Jixian; Langmuir</t>
+  </si>
+  <si>
+    <t>出版商题名/DOI/卷和文章号/摘要已核验</t>
+  </si>
+  <si>
+    <t>DCBM-138</t>
+  </si>
+  <si>
+    <t>Guo, Chen</t>
+  </si>
+  <si>
+    <t>Guo, Chen; Jiang, Lingling; Lu, Lingling; Gao, Junzhe; Cheng, Xi</t>
+  </si>
+  <si>
+    <t>Adsorption behavior and prediction model of coalbed methane under the influence of temperature and pressure: a case study of the Zhijin Block, Western Guizhou, South China</t>
+  </si>
+  <si>
+    <t>温压影响下煤层气吸附行为与预测模型：以黔西织金区块为例</t>
+  </si>
+  <si>
+    <t>21736</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-026-52704-3</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-026-52704-3</t>
+  </si>
+  <si>
+    <t>黔西织金区块上二叠统龙潭组（4个向斜6个煤矿）</t>
+  </si>
+  <si>
+    <t>煤层气吸附行为（6件煤样）</t>
+  </si>
+  <si>
+    <t>温度-压力-埋深耦合（织金区块深部条件）</t>
+  </si>
+  <si>
+    <t>研究温压耦合条件下煤层气吸附行为变化规律，建立温度-压力-埋深耦合预测模型</t>
+  </si>
+  <si>
+    <t>6件煤样工业分析和镜质组反射率；高压等温吸附(N2/CO2)；4种吸附模型对比(Langmuir/DR/DA/L-F)；温度-压力-埋深耦合预测</t>
+  </si>
+  <si>
+    <t>吸附气含量随埋深先增后降；最大吸附量对应埋深受温度梯度和煤阶共同控制；超临界条件下过剩吸附量需进行密度校正；L-F模型在超临界条件下拟合效果最佳</t>
+  </si>
+  <si>
+    <t>明确吸附气含量先增后降的临界深度窗口；整合温度-压力-埋深三维耦合预测；系统对比4种吸附模型在超临界条件下的适用性</t>
+  </si>
+  <si>
+    <t>6件煤样覆盖范围有限；织金区块结果不可直接外推至其他盆地；未与生产动态数据交叉验证</t>
+  </si>
+  <si>
+    <t>吸附/游离气比例/临界深度/超临界吸附校正/区域差异</t>
+  </si>
+  <si>
+    <t>赋存机理与吸附行为；温压-深度耦合；区域差异与模型选择；局限</t>
+  </si>
+  <si>
+    <t>adsorption; temperature-pressure coupling; supercritical; Langmuir; Zhijin block; coal rank</t>
+  </si>
+  <si>
+    <t>Nature官方页和全文已核验</t>
+  </si>
+  <si>
+    <t>DCBM-139</t>
+  </si>
+  <si>
+    <t>Ji, Yusong</t>
+  </si>
+  <si>
+    <t>Ji, Yusong; Li, Song; Hou, Wei; Li, Yongzhou; Feng, Peng; Yang, Shizhuang; Zhou, Hanmiao</t>
+  </si>
+  <si>
+    <t>Quantitative Evaluation of Deep Coalbed Methane Content: A Logging Data-Driven Approach</t>
+  </si>
+  <si>
+    <t>测井数据驱动的深部煤层气含量定量评价</t>
+  </si>
+  <si>
+    <t>Geological Journal</t>
+  </si>
+  <si>
+    <t>2072-2086</t>
+  </si>
+  <si>
+    <t>10.1002/gj.70077</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/doi/10.1002/gj.70077</t>
+  </si>
+  <si>
+    <t>大宁-吉县区块本溪组8号煤</t>
+  </si>
+  <si>
+    <t>深部煤层气含量（10口井）</t>
+  </si>
+  <si>
+    <t>大宁-吉县区块深部段(&gt;1500 m)</t>
+  </si>
+  <si>
+    <t>构建测井数据驱动的深部煤层气含量多模型定量评价方法</t>
+  </si>
+  <si>
+    <t>10口井常规测井(GR/DEN/CNL/RD/RS/AC)；煤心解吸含气量标定；多元线性回归/RBF神经网络/随机森林/CNN；数据增广(CTGAN)</t>
+  </si>
+  <si>
+    <t>CNN预测精度最高(+20%~35%)；CTGAN数据增广后小样本模型性能显著提升；深部段(&gt;1500 m)含气量变化更复杂需要更深的网络结构</t>
+  </si>
+  <si>
+    <t>系统对比4种模型(MLR到CNN)在同一区块的性能；引入CTGAN数据增广解决小样本深度学习问题；为测井含气量评价提供可迁移框架</t>
+  </si>
+  <si>
+    <t>10口井样本仍属小样本；深部&gt;1500 m段模型不确定性升高；结果具有区块和煤阶依赖性</t>
+  </si>
+  <si>
+    <t>含气量评价/测井-地质-工程一体化/深度学习适用性/小样本增广策略</t>
+  </si>
+  <si>
+    <t>地质建模与含气量；方法讨论：多源数据与模型选择；局限；后续可引入的机器学习补充方向</t>
+  </si>
+  <si>
+    <t>logging data; deep learning; CNN; CTGAN data augmentation; gas content; Daning-Jixian</t>
+  </si>
+  <si>
+    <t>Wiley官方题名/作者/DOI/卷期/摘要已核验；页码待最终确认</t>
+  </si>
+  <si>
     <t>指标</t>
   </si>
   <si>
@@ -8479,7 +8662,7 @@
     <t>当前主表版本</t>
   </si>
   <si>
-    <t>v1_136_daily_brief_update_2026-07-24</t>
+    <t>v1_139_daily_brief_update_2026-07-26</t>
   </si>
   <si>
     <t>Deep_CBM_complete_literature_matrix_v1_105.xlsx</t>
@@ -10094,6 +10277,46 @@
     <t>生产动态不能直接识别气源或微生物机制；</t>
   </si>
   <si>
+    <t>深部煤层含气量预测模型评价：以鄂尔多斯盆地东缘大宁—吉县区块为例</t>
+  </si>
+  <si>
+    <t>鄂尔多斯盆地东缘大宁-吉县区块; 深部煤层（吸附气/游离气/总含气量）; 深部煤层（大宁-吉县区块深部储层）</t>
+  </si>
+  <si>
+    <t>【局限性】动态曲线与储层测试之间的边界；</t>
+  </si>
+  <si>
+    <t>动态曲线与储层测试之间的边界；</t>
+  </si>
+  <si>
+    <t>黔西织金区块上二叠统龙潭组（4个向斜6个煤矿）; 煤层气吸附行为（6件煤样）; 温度-压力-埋深耦合（织金区块深部条件）</t>
+  </si>
+  <si>
+    <t>【研究目的】研究温压耦合条件下煤层气吸附行为变化规律，建立温度-压力-埋深耦合预测模型
+【数据/方法】6件煤样工业分析和镜质组反射率；高压等温吸附(N2/CO2)；4种吸附模型对比(Langmuir/DR/DA/L-F)；温度-压力-埋深耦合预测
+【核心发现】吸附气含量随埋深先增后降；最大吸附量对应埋深受温度梯度和煤阶共同控制；超临界条件下过剩吸附量需进行密度校正；L-F模型在超临界条件下拟合效果最佳
+【创新点】明确吸附气含量先增后降的临界深度窗口；整合温度-压力-埋深三维耦合预测；系统对比4种吸附模型在超临界条件下的适用性
+【局限性】6件煤样覆盖范围有限；织金区块结果不可直接外推至其他盆地；未与生产动态数据交叉验证
+【与你课题的关系】吸附/游离气比例/临界深度/超临界吸附校正/区域差异</t>
+  </si>
+  <si>
+    <t>临界深度和深部定义的区域性。</t>
+  </si>
+  <si>
+    <t>大宁-吉县区块本溪组8号煤; 深部煤层气含量（10口井）; 大宁-吉县区块深部段(&gt;1500 m)</t>
+  </si>
+  <si>
+    <t>【研究目的】构建测井数据驱动的深部煤层气含量多模型定量评价方法
+【数据/方法】10口井常规测井(GR/DEN/CNL/RD/RS/AC)；煤心解吸含气量标定；多元线性回归/RBF神经网络/随机森林/CNN；数据增广(CTGAN)
+【核心发现】CNN预测精度最高(+20%~35%)；CTGAN数据增广后小样本模型性能显著提升；深部段(&gt;1500 m)含气量变化更复杂需要更深的网络结构
+【创新点】系统对比4种模型(MLR到CNN)在同一区块的性能；引入CTGAN数据增广解决小样本深度学习问题；为测井含气量评价提供可迁移框架
+【局限性】10口井样本仍属小样本；深部&gt;1500 m段模型不确定性升高；结果具有区块和煤阶依赖性
+【与你课题的关系】含气量评价/测井-地质-工程一体化/深度学习适用性/小样本增广策略</t>
+  </si>
+  <si>
+    <t>模型可迁移性和资料完整性。</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -10175,6 +10398,12 @@
     <t>新增: DCBM-135, DCBM-136; 跳过重复: 0; 主库记录数更新为 13 → (待QC确认)</t>
   </si>
   <si>
+    <t>2026-07-26 Daily Brief Update</t>
+  </si>
+  <si>
+    <t>新增: DCBM-137, DCBM-138, DCBM-139; 跳过重复: 0; 主库记录数更新为 14 → (待QC确认)</t>
+  </si>
+  <si>
     <t>候选原编号</t>
   </si>
   <si>
@@ -10320,6 +10549,9 @@
   </si>
   <si>
     <t>新增 2 篇, 跳过重复 0 篇, 待 validate 确认</t>
+  </si>
+  <si>
+    <t>Daily Brief Update 2026-07-26</t>
   </si>
 </sst>
 </file>
@@ -10662,7 +10894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -21942,6 +22174,249 @@
         <v>2803</v>
       </c>
     </row>
+    <row r="138" spans="1:27">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C138" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D138" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E138" t="s">
+        <v>31</v>
+      </c>
+      <c r="F138" t="s">
+        <v>2807</v>
+      </c>
+      <c r="G138" t="s">
+        <v>2808</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I138" t="s">
+        <v>655</v>
+      </c>
+      <c r="K138" t="s">
+        <v>2809</v>
+      </c>
+      <c r="L138" t="s">
+        <v>2810</v>
+      </c>
+      <c r="M138" t="s">
+        <v>2811</v>
+      </c>
+      <c r="N138" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O138" t="s">
+        <v>2812</v>
+      </c>
+      <c r="P138" t="s">
+        <v>2813</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>2814</v>
+      </c>
+      <c r="R138" t="s">
+        <v>2815</v>
+      </c>
+      <c r="S138" t="s">
+        <v>2816</v>
+      </c>
+      <c r="T138" t="s">
+        <v>2817</v>
+      </c>
+      <c r="U138" t="s">
+        <v>2818</v>
+      </c>
+      <c r="V138" t="s">
+        <v>2819</v>
+      </c>
+      <c r="W138" t="s">
+        <v>2820</v>
+      </c>
+      <c r="X138" t="s">
+        <v>2821</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>2822</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA138" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D139" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E139" t="s">
+        <v>31</v>
+      </c>
+      <c r="F139" t="s">
+        <v>2827</v>
+      </c>
+      <c r="G139" t="s">
+        <v>2828</v>
+      </c>
+      <c r="H139" t="s">
+        <v>638</v>
+      </c>
+      <c r="I139" t="s">
+        <v>351</v>
+      </c>
+      <c r="K139" t="s">
+        <v>2829</v>
+      </c>
+      <c r="L139" t="s">
+        <v>2830</v>
+      </c>
+      <c r="M139" t="s">
+        <v>2831</v>
+      </c>
+      <c r="N139" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O139" t="s">
+        <v>2832</v>
+      </c>
+      <c r="P139" t="s">
+        <v>2833</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>2834</v>
+      </c>
+      <c r="R139" t="s">
+        <v>2835</v>
+      </c>
+      <c r="S139" t="s">
+        <v>2836</v>
+      </c>
+      <c r="T139" t="s">
+        <v>2837</v>
+      </c>
+      <c r="U139" t="s">
+        <v>2838</v>
+      </c>
+      <c r="V139" t="s">
+        <v>2839</v>
+      </c>
+      <c r="W139" t="s">
+        <v>2840</v>
+      </c>
+      <c r="X139" t="s">
+        <v>2841</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>2842</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA139" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C140" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E140" t="s">
+        <v>31</v>
+      </c>
+      <c r="F140" t="s">
+        <v>2847</v>
+      </c>
+      <c r="G140" t="s">
+        <v>2848</v>
+      </c>
+      <c r="H140" t="s">
+        <v>2849</v>
+      </c>
+      <c r="I140" t="s">
+        <v>1292</v>
+      </c>
+      <c r="J140" t="s">
+        <v>169</v>
+      </c>
+      <c r="K140" t="s">
+        <v>2850</v>
+      </c>
+      <c r="L140" t="s">
+        <v>2851</v>
+      </c>
+      <c r="M140" t="s">
+        <v>2852</v>
+      </c>
+      <c r="N140" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O140" t="s">
+        <v>2853</v>
+      </c>
+      <c r="P140" t="s">
+        <v>2854</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>2855</v>
+      </c>
+      <c r="R140" t="s">
+        <v>2856</v>
+      </c>
+      <c r="S140" t="s">
+        <v>2857</v>
+      </c>
+      <c r="T140" t="s">
+        <v>2858</v>
+      </c>
+      <c r="U140" t="s">
+        <v>2859</v>
+      </c>
+      <c r="V140" t="s">
+        <v>2860</v>
+      </c>
+      <c r="W140" t="s">
+        <v>2861</v>
+      </c>
+      <c r="X140" t="s">
+        <v>2862</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>2863</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>2864</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId1"/>
@@ -21961,7 +22436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="6" min="1" width="22"/>
@@ -21969,13 +22444,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>2804</v>
+        <v>2865</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2805</v>
+        <v>2866</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2806</v>
+        <v>2867</v>
       </c>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
@@ -21983,13 +22458,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>2807</v>
+        <v>2868</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2808</v>
+        <v>2869</v>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
@@ -21997,13 +22472,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>2809</v>
+        <v>2870</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2810</v>
+        <v>2871</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -22011,13 +22486,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>2811</v>
+        <v>2872</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2812</v>
+        <v>2873</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2813</v>
+        <v>2874</v>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
@@ -22025,13 +22500,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>2814</v>
+        <v>2875</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2815</v>
+        <v>2876</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2816</v>
+        <v>2877</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
@@ -22039,13 +22514,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>2817</v>
+        <v>2878</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2818</v>
+        <v>2879</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2819</v>
+        <v>2880</v>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
@@ -22056,14 +22531,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2820</v>
+        <v>2881</v>
       </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2820</v>
+        <v>2881</v>
       </c>
       <c r="F7" s="3" t="n"/>
     </row>
@@ -22101,7 +22576,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>2821</v>
+        <v>2882</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -22117,7 +22592,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>2822</v>
+        <v>2883</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -22133,7 +22608,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>2823</v>
+        <v>2884</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -22200,7 +22675,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="s">
@@ -22219,7 +22694,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -22231,7 +22705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -25734,6 +26208,39 @@
       </c>
       <c r="F136" t="s">
         <v>2791</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="n">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>2804</v>
+      </c>
+      <c r="F137" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="n">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F138" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="n">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2844</v>
+      </c>
+      <c r="F139" t="s">
+        <v>2851</v>
       </c>
     </row>
   </sheetData>
@@ -25759,10 +26266,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>2824</v>
+        <v>2885</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2806</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -25770,7 +26277,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2825</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -25778,7 +26285,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2826</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -25786,7 +26293,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2827</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -25794,7 +26301,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2828</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -25802,7 +26309,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2829</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -25810,7 +26317,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2830</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -25818,7 +26325,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2831</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -25826,15 +26333,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2832</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>2833</v>
+        <v>2894</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2834</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -25842,7 +26349,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2835</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -25850,7 +26357,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2836</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -25858,7 +26365,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2837</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -25866,7 +26373,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2838</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -25874,7 +26381,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2839</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -25882,7 +26389,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2840</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -25890,7 +26397,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2841</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -25898,7 +26405,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2842</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -25906,7 +26413,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2843</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -25914,7 +26421,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2844</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -25922,7 +26429,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2845</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -25930,7 +26437,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2846</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -25938,7 +26445,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2847</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -25946,7 +26453,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2848</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -25954,7 +26461,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2849</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -25962,7 +26469,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2850</v>
+        <v>2911</v>
       </c>
     </row>
   </sheetData>
@@ -25976,7 +26483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -26001,22 +26508,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2851</v>
+        <v>2912</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2852</v>
+        <v>2913</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2853</v>
+        <v>2914</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2854</v>
+        <v>2915</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2855</v>
+        <v>2916</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>20</v>
@@ -26025,16 +26532,16 @@
         <v>21</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>2856</v>
+        <v>2917</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>2857</v>
+        <v>2918</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>2858</v>
+        <v>2919</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="2" spans="1:14">
@@ -26048,10 +26555,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2859</v>
+        <v>2920</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2860</v>
+        <v>2921</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>44</v>
@@ -26078,7 +26585,7 @@
         <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="3" spans="1:14">
@@ -26092,10 +26599,10 @@
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2862</v>
+        <v>2923</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2863</v>
+        <v>2924</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>68</v>
@@ -26122,7 +26629,7 @@
         <v>52</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="4" spans="1:14">
@@ -26136,10 +26643,10 @@
         <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2864</v>
+        <v>2925</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2865</v>
+        <v>2926</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>92</v>
@@ -26166,7 +26673,7 @@
         <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="5" spans="1:14">
@@ -26180,10 +26687,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2866</v>
+        <v>2927</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2867</v>
+        <v>2928</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>115</v>
@@ -26210,7 +26717,7 @@
         <v>52</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="6" spans="1:14">
@@ -26224,10 +26731,10 @@
         <v>128</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2868</v>
+        <v>2929</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2869</v>
+        <v>2930</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>137</v>
@@ -26254,7 +26761,7 @@
         <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="7" spans="1:14">
@@ -26268,10 +26775,10 @@
         <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2870</v>
+        <v>2931</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2871</v>
+        <v>2932</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>160</v>
@@ -26298,7 +26805,7 @@
         <v>145</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="8" spans="1:14">
@@ -26312,10 +26819,10 @@
         <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2872</v>
+        <v>2933</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2873</v>
+        <v>2934</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>181</v>
@@ -26342,7 +26849,7 @@
         <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:14">
@@ -26356,10 +26863,10 @@
         <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2874</v>
+        <v>2935</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2875</v>
+        <v>2936</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>201</v>
@@ -26386,7 +26893,7 @@
         <v>145</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="10" spans="1:14">
@@ -26400,10 +26907,10 @@
         <v>214</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2876</v>
+        <v>2937</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2877</v>
+        <v>2938</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>220</v>
@@ -26430,7 +26937,7 @@
         <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:14">
@@ -26444,10 +26951,10 @@
         <v>233</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2878</v>
+        <v>2939</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2879</v>
+        <v>2940</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>239</v>
@@ -26474,7 +26981,7 @@
         <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:14">
@@ -26488,10 +26995,10 @@
         <v>252</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2880</v>
+        <v>2941</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2881</v>
+        <v>2942</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>258</v>
@@ -26518,7 +27025,7 @@
         <v>145</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="13" spans="1:14">
@@ -26532,10 +27039,10 @@
         <v>272</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2882</v>
+        <v>2943</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2883</v>
+        <v>2944</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>278</v>
@@ -26562,7 +27069,7 @@
         <v>52</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="14" spans="1:14">
@@ -26576,10 +27083,10 @@
         <v>291</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2884</v>
+        <v>2945</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2885</v>
+        <v>2946</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>300</v>
@@ -26606,7 +27113,7 @@
         <v>145</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:14">
@@ -26620,10 +27127,10 @@
         <v>313</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2886</v>
+        <v>2947</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2887</v>
+        <v>2948</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>321</v>
@@ -26650,7 +27157,7 @@
         <v>52</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="16" spans="1:14">
@@ -26664,10 +27171,10 @@
         <v>334</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2888</v>
+        <v>2949</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2889</v>
+        <v>2950</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>343</v>
@@ -26694,7 +27201,7 @@
         <v>52</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:14">
@@ -26708,10 +27215,10 @@
         <v>356</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2890</v>
+        <v>2951</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2891</v>
+        <v>2952</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>363</v>
@@ -26738,7 +27245,7 @@
         <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="18" spans="1:14">
@@ -26752,10 +27259,10 @@
         <v>376</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2892</v>
+        <v>2953</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2893</v>
+        <v>2954</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>383</v>
@@ -26782,7 +27289,7 @@
         <v>145</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="19" spans="1:14">
@@ -26796,10 +27303,10 @@
         <v>397</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2894</v>
+        <v>2955</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2895</v>
+        <v>2956</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>404</v>
@@ -26826,7 +27333,7 @@
         <v>145</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="20" spans="1:14">
@@ -26840,10 +27347,10 @@
         <v>418</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2896</v>
+        <v>2957</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2897</v>
+        <v>2958</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>427</v>
@@ -26870,7 +27377,7 @@
         <v>145</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="21" spans="1:14">
@@ -26884,10 +27391,10 @@
         <v>441</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2898</v>
+        <v>2959</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2899</v>
+        <v>2960</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>448</v>
@@ -26914,7 +27421,7 @@
         <v>145</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="22" spans="1:14">
@@ -26928,10 +27435,10 @@
         <v>462</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2900</v>
+        <v>2961</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2901</v>
+        <v>2962</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>467</v>
@@ -26958,7 +27465,7 @@
         <v>52</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="23" spans="1:14">
@@ -26972,10 +27479,10 @@
         <v>481</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2902</v>
+        <v>2963</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2903</v>
+        <v>2964</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>489</v>
@@ -27002,7 +27509,7 @@
         <v>145</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="24" spans="1:14">
@@ -27016,10 +27523,10 @@
         <v>503</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2904</v>
+        <v>2965</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2905</v>
+        <v>2966</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>511</v>
@@ -27046,7 +27553,7 @@
         <v>52</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="25" spans="1:14">
@@ -27060,10 +27567,10 @@
         <v>524</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2906</v>
+        <v>2967</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2907</v>
+        <v>2968</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>532</v>
@@ -27090,7 +27597,7 @@
         <v>145</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="26" spans="1:14">
@@ -27104,10 +27611,10 @@
         <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2908</v>
+        <v>2969</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2909</v>
+        <v>2970</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>554</v>
@@ -27134,7 +27641,7 @@
         <v>52</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="27" spans="1:14">
@@ -27148,10 +27655,10 @@
         <v>568</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2910</v>
+        <v>2971</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2911</v>
+        <v>2972</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>577</v>
@@ -27178,7 +27685,7 @@
         <v>52</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="28" spans="1:14">
@@ -27192,10 +27699,10 @@
         <v>591</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2912</v>
+        <v>2973</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2913</v>
+        <v>2974</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>600</v>
@@ -27222,7 +27729,7 @@
         <v>52</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="29" spans="1:14">
@@ -27236,10 +27743,10 @@
         <v>614</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2914</v>
+        <v>2975</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2915</v>
+        <v>2976</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>623</v>
@@ -27266,7 +27773,7 @@
         <v>52</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="30" spans="1:14">
@@ -27280,10 +27787,10 @@
         <v>637</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2916</v>
+        <v>2977</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2917</v>
+        <v>2978</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>646</v>
@@ -27310,7 +27817,7 @@
         <v>52</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="31" spans="1:14">
@@ -27324,10 +27831,10 @@
         <v>659</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2918</v>
+        <v>2979</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2919</v>
+        <v>2980</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>668</v>
@@ -27354,7 +27861,7 @@
         <v>52</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="32" spans="1:14">
@@ -27368,10 +27875,10 @@
         <v>682</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2920</v>
+        <v>2981</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2921</v>
+        <v>2982</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>689</v>
@@ -27398,7 +27905,7 @@
         <v>52</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="33" spans="1:14">
@@ -27412,10 +27919,10 @@
         <v>702</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2922</v>
+        <v>2983</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2923</v>
+        <v>2984</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>709</v>
@@ -27442,7 +27949,7 @@
         <v>145</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="34" spans="1:14">
@@ -27456,10 +27963,10 @@
         <v>722</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2924</v>
+        <v>2985</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2925</v>
+        <v>2986</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>731</v>
@@ -27486,7 +27993,7 @@
         <v>52</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="35" spans="1:14">
@@ -27500,10 +28007,10 @@
         <v>744</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2926</v>
+        <v>2987</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2927</v>
+        <v>2988</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>751</v>
@@ -27530,7 +28037,7 @@
         <v>52</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="36" spans="1:14">
@@ -27544,10 +28051,10 @@
         <v>764</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2928</v>
+        <v>2989</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2929</v>
+        <v>2990</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>772</v>
@@ -27574,7 +28081,7 @@
         <v>145</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="37" spans="1:14">
@@ -27588,10 +28095,10 @@
         <v>785</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2930</v>
+        <v>2991</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2931</v>
+        <v>2992</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>792</v>
@@ -27618,7 +28125,7 @@
         <v>145</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="38" spans="1:14">
@@ -27632,10 +28139,10 @@
         <v>806</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2932</v>
+        <v>2993</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2933</v>
+        <v>2994</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>814</v>
@@ -27662,7 +28169,7 @@
         <v>145</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="39" spans="1:14">
@@ -27676,10 +28183,10 @@
         <v>827</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2934</v>
+        <v>2995</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2935</v>
+        <v>2996</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>834</v>
@@ -27706,7 +28213,7 @@
         <v>145</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="40" spans="1:14">
@@ -27720,10 +28227,10 @@
         <v>848</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2936</v>
+        <v>2997</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2937</v>
+        <v>2998</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>856</v>
@@ -27750,7 +28257,7 @@
         <v>52</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="41" spans="1:14">
@@ -27764,10 +28271,10 @@
         <v>870</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2938</v>
+        <v>2999</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2939</v>
+        <v>3000</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>878</v>
@@ -27794,7 +28301,7 @@
         <v>52</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="42" spans="1:14">
@@ -27808,10 +28315,10 @@
         <v>891</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2940</v>
+        <v>3001</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2941</v>
+        <v>3002</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>901</v>
@@ -27838,7 +28345,7 @@
         <v>52</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="43" spans="1:14">
@@ -27852,10 +28359,10 @@
         <v>914</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2942</v>
+        <v>3003</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2943</v>
+        <v>3004</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>921</v>
@@ -27882,7 +28389,7 @@
         <v>52</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="44" spans="1:14">
@@ -27896,10 +28403,10 @@
         <v>933</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2944</v>
+        <v>3005</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2945</v>
+        <v>3006</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>940</v>
@@ -27926,7 +28433,7 @@
         <v>52</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="45" spans="1:14">
@@ -27940,10 +28447,10 @@
         <v>953</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2946</v>
+        <v>3007</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2947</v>
+        <v>3008</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>959</v>
@@ -27970,7 +28477,7 @@
         <v>52</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="46" spans="1:14">
@@ -27984,10 +28491,10 @@
         <v>972</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2948</v>
+        <v>3009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2949</v>
+        <v>3010</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>978</v>
@@ -28014,7 +28521,7 @@
         <v>52</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="47" spans="1:14">
@@ -28028,10 +28535,10 @@
         <v>990</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2950</v>
+        <v>3011</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2951</v>
+        <v>3012</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>997</v>
@@ -28058,7 +28565,7 @@
         <v>52</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="48" spans="1:14">
@@ -28072,10 +28579,10 @@
         <v>1010</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2952</v>
+        <v>3013</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>2953</v>
+        <v>3014</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>1018</v>
@@ -28102,7 +28609,7 @@
         <v>52</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="49" spans="1:14">
@@ -28116,10 +28623,10 @@
         <v>1030</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2954</v>
+        <v>3015</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2955</v>
+        <v>3016</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>1037</v>
@@ -28146,7 +28653,7 @@
         <v>52</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="50" spans="1:14">
@@ -28160,10 +28667,10 @@
         <v>1049</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2956</v>
+        <v>3017</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2957</v>
+        <v>3018</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>1055</v>
@@ -28190,7 +28697,7 @@
         <v>189</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="51" spans="1:14">
@@ -28204,10 +28711,10 @@
         <v>1067</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2958</v>
+        <v>3019</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2959</v>
+        <v>3020</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>1072</v>
@@ -28234,7 +28741,7 @@
         <v>52</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="52" spans="1:14">
@@ -28248,10 +28755,10 @@
         <v>1084</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2960</v>
+        <v>3021</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2961</v>
+        <v>3022</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>1091</v>
@@ -28278,7 +28785,7 @@
         <v>189</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="53" spans="1:14">
@@ -28292,10 +28799,10 @@
         <v>1104</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2962</v>
+        <v>3023</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>2963</v>
+        <v>3024</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>1109</v>
@@ -28322,7 +28829,7 @@
         <v>145</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="54" spans="1:14">
@@ -28336,10 +28843,10 @@
         <v>1121</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2964</v>
+        <v>3025</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>2965</v>
+        <v>3026</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>1131</v>
@@ -28366,7 +28873,7 @@
         <v>52</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="55" spans="1:14">
@@ -28380,10 +28887,10 @@
         <v>1144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2966</v>
+        <v>3027</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>2967</v>
+        <v>3028</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>1151</v>
@@ -28410,7 +28917,7 @@
         <v>52</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="56" spans="1:14">
@@ -28424,10 +28931,10 @@
         <v>1165</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2968</v>
+        <v>3029</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2969</v>
+        <v>3030</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>1173</v>
@@ -28454,7 +28961,7 @@
         <v>52</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="57" spans="1:14">
@@ -28468,10 +28975,10 @@
         <v>1187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2970</v>
+        <v>3031</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>2971</v>
+        <v>3032</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>1195</v>
@@ -28498,7 +29005,7 @@
         <v>189</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="58" spans="1:14">
@@ -28512,10 +29019,10 @@
         <v>1209</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2972</v>
+        <v>3033</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>2973</v>
+        <v>3034</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>1217</v>
@@ -28542,7 +29049,7 @@
         <v>189</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="59" spans="1:14">
@@ -28556,10 +29063,10 @@
         <v>1231</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2974</v>
+        <v>3035</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>2975</v>
+        <v>3036</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>1239</v>
@@ -28586,7 +29093,7 @@
         <v>189</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="60" spans="1:14">
@@ -28600,10 +29107,10 @@
         <v>1252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2976</v>
+        <v>3037</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>2977</v>
+        <v>3038</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>1261</v>
@@ -28630,7 +29137,7 @@
         <v>52</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="61" spans="1:14">
@@ -28644,10 +29151,10 @@
         <v>1275</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>2978</v>
+        <v>3039</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>2979</v>
+        <v>3040</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>1283</v>
@@ -28674,7 +29181,7 @@
         <v>52</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="62" spans="1:14">
@@ -28688,10 +29195,10 @@
         <v>1297</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2980</v>
+        <v>3041</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2981</v>
+        <v>3042</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>1305</v>
@@ -28718,7 +29225,7 @@
         <v>145</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="63" spans="1:14">
@@ -28732,10 +29239,10 @@
         <v>1319</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2982</v>
+        <v>3043</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>2983</v>
+        <v>3044</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>1327</v>
@@ -28762,7 +29269,7 @@
         <v>189</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="64" spans="1:14">
@@ -28776,10 +29283,10 @@
         <v>1341</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>2984</v>
+        <v>3045</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>2985</v>
+        <v>3046</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>1348</v>
@@ -28806,7 +29313,7 @@
         <v>52</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="65" spans="1:14">
@@ -28820,10 +29327,10 @@
         <v>1361</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>2986</v>
+        <v>3047</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>2987</v>
+        <v>3048</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>1368</v>
@@ -28850,7 +29357,7 @@
         <v>52</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="66" spans="1:14">
@@ -28864,10 +29371,10 @@
         <v>1382</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>2988</v>
+        <v>3049</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>2989</v>
+        <v>3050</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>1389</v>
@@ -28894,7 +29401,7 @@
         <v>52</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="67" spans="1:14">
@@ -28908,10 +29415,10 @@
         <v>1403</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>2990</v>
+        <v>3051</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>2991</v>
+        <v>3052</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>1408</v>
@@ -28938,7 +29445,7 @@
         <v>52</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="68" spans="1:14">
@@ -28952,10 +29459,10 @@
         <v>1421</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>2992</v>
+        <v>3053</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>2993</v>
+        <v>3054</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>1428</v>
@@ -28982,7 +29489,7 @@
         <v>52</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="69" spans="1:14">
@@ -28996,10 +29503,10 @@
         <v>1442</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>2994</v>
+        <v>3055</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>2995</v>
+        <v>3056</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>1448</v>
@@ -29026,7 +29533,7 @@
         <v>52</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="70" spans="1:14">
@@ -29040,10 +29547,10 @@
         <v>1460</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>2996</v>
+        <v>3057</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>2997</v>
+        <v>3058</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>1466</v>
@@ -29070,7 +29577,7 @@
         <v>52</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="71" spans="1:14">
@@ -29084,10 +29591,10 @@
         <v>1480</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>2998</v>
+        <v>3059</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>2999</v>
+        <v>3060</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>1486</v>
@@ -29114,7 +29621,7 @@
         <v>52</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="72" spans="1:14">
@@ -29128,10 +29635,10 @@
         <v>1499</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>3000</v>
+        <v>3061</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>3001</v>
+        <v>3062</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>1505</v>
@@ -29158,7 +29665,7 @@
         <v>52</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="73" spans="1:14">
@@ -29172,10 +29679,10 @@
         <v>1518</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>3002</v>
+        <v>3063</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>3003</v>
+        <v>3064</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>1524</v>
@@ -29202,7 +29709,7 @@
         <v>145</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="74" spans="1:14">
@@ -29216,10 +29723,10 @@
         <v>1537</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>3004</v>
+        <v>3065</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>3005</v>
+        <v>3066</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>1544</v>
@@ -29246,7 +29753,7 @@
         <v>52</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="75" spans="1:14">
@@ -29260,10 +29767,10 @@
         <v>1556</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>3006</v>
+        <v>3067</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>3007</v>
+        <v>3068</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>1563</v>
@@ -29290,7 +29797,7 @@
         <v>52</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="76" spans="1:14">
@@ -29304,10 +29811,10 @@
         <v>1576</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>3008</v>
+        <v>3069</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>3009</v>
+        <v>3070</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>1583</v>
@@ -29334,7 +29841,7 @@
         <v>52</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="77" spans="1:14">
@@ -29348,10 +29855,10 @@
         <v>1596</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>3010</v>
+        <v>3071</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>3011</v>
+        <v>3072</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>1602</v>
@@ -29378,7 +29885,7 @@
         <v>52</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="78" spans="1:14">
@@ -29392,10 +29899,10 @@
         <v>1615</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>3012</v>
+        <v>3073</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>3013</v>
+        <v>3074</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>1621</v>
@@ -29422,7 +29929,7 @@
         <v>52</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="79" spans="1:14">
@@ -29436,10 +29943,10 @@
         <v>1634</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>3014</v>
+        <v>3075</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>3015</v>
+        <v>3076</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>1643</v>
@@ -29466,7 +29973,7 @@
         <v>145</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="80" spans="1:14">
@@ -29480,10 +29987,10 @@
         <v>1657</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>3016</v>
+        <v>3077</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>3017</v>
+        <v>3078</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>1665</v>
@@ -29510,7 +30017,7 @@
         <v>189</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="81" spans="1:14">
@@ -29524,10 +30031,10 @@
         <v>1678</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>3018</v>
+        <v>3079</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>3019</v>
+        <v>3080</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>1686</v>
@@ -29554,7 +30061,7 @@
         <v>52</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="82" spans="1:14">
@@ -29568,10 +30075,10 @@
         <v>1700</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>3020</v>
+        <v>3081</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>3021</v>
+        <v>3082</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>1708</v>
@@ -29598,7 +30105,7 @@
         <v>145</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="83" spans="1:14">
@@ -29612,10 +30119,10 @@
         <v>1721</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>3022</v>
+        <v>3083</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>3023</v>
+        <v>3084</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>1730</v>
@@ -29642,7 +30149,7 @@
         <v>52</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="84" spans="1:14">
@@ -29656,10 +30163,10 @@
         <v>1744</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>3024</v>
+        <v>3085</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>3025</v>
+        <v>3086</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>1751</v>
@@ -29686,7 +30193,7 @@
         <v>52</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="85" spans="1:14">
@@ -29700,10 +30207,10 @@
         <v>1765</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>3026</v>
+        <v>3087</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>3027</v>
+        <v>3088</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>1773</v>
@@ -29730,7 +30237,7 @@
         <v>145</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="86" spans="1:14">
@@ -29744,10 +30251,10 @@
         <v>1785</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>3028</v>
+        <v>3089</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>3029</v>
+        <v>3090</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>1793</v>
@@ -29774,7 +30281,7 @@
         <v>52</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="87" spans="1:14">
@@ -29788,10 +30295,10 @@
         <v>1806</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>3030</v>
+        <v>3091</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>3031</v>
+        <v>3092</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>1813</v>
@@ -29818,7 +30325,7 @@
         <v>145</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="88" spans="1:14">
@@ -29832,10 +30339,10 @@
         <v>1826</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>3032</v>
+        <v>3093</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>3033</v>
+        <v>3094</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>1834</v>
@@ -29862,7 +30369,7 @@
         <v>52</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="89" spans="1:14">
@@ -29876,10 +30383,10 @@
         <v>1846</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>3034</v>
+        <v>3095</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>3035</v>
+        <v>3096</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>1854</v>
@@ -29906,7 +30413,7 @@
         <v>52</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="90" spans="1:14">
@@ -29920,10 +30427,10 @@
         <v>1866</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>3036</v>
+        <v>3097</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>3037</v>
+        <v>3098</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>1873</v>
@@ -29950,7 +30457,7 @@
         <v>52</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="91" spans="1:14">
@@ -29964,10 +30471,10 @@
         <v>1884</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>3038</v>
+        <v>3099</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>3039</v>
+        <v>3100</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>1892</v>
@@ -29994,7 +30501,7 @@
         <v>145</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="92" spans="1:14">
@@ -30008,10 +30515,10 @@
         <v>1904</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>3040</v>
+        <v>3101</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>3041</v>
+        <v>3102</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>1912</v>
@@ -30038,7 +30545,7 @@
         <v>189</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="93" spans="1:14">
@@ -30052,10 +30559,10 @@
         <v>1923</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>3042</v>
+        <v>3103</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>3043</v>
+        <v>3104</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>1931</v>
@@ -30082,7 +30589,7 @@
         <v>52</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="94" spans="1:14">
@@ -30096,10 +30603,10 @@
         <v>1943</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>3044</v>
+        <v>3105</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>3045</v>
+        <v>3106</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>1950</v>
@@ -30126,7 +30633,7 @@
         <v>52</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="95" spans="1:14">
@@ -30140,10 +30647,10 @@
         <v>1961</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>3046</v>
+        <v>3107</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>3047</v>
+        <v>3108</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>1968</v>
@@ -30170,7 +30677,7 @@
         <v>52</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="96" spans="1:14">
@@ -30184,10 +30691,10 @@
         <v>1980</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>3048</v>
+        <v>3109</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>3049</v>
+        <v>3110</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>1988</v>
@@ -30214,7 +30721,7 @@
         <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="97" spans="1:14">
@@ -30228,10 +30735,10 @@
         <v>2000</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>3050</v>
+        <v>3111</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>3051</v>
+        <v>3112</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>2006</v>
@@ -30258,7 +30765,7 @@
         <v>52</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="98" spans="1:14">
@@ -30272,10 +30779,10 @@
         <v>2019</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>3052</v>
+        <v>3113</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>3053</v>
+        <v>3114</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>2028</v>
@@ -30302,7 +30809,7 @@
         <v>145</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="99" spans="1:14">
@@ -30316,10 +30823,10 @@
         <v>2041</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>3054</v>
+        <v>3115</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>3055</v>
+        <v>3116</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>2049</v>
@@ -30346,7 +30853,7 @@
         <v>145</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="100" spans="1:14">
@@ -30360,10 +30867,10 @@
         <v>2062</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>3056</v>
+        <v>3117</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>3057</v>
+        <v>3118</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>2069</v>
@@ -30390,7 +30897,7 @@
         <v>145</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="101" spans="1:14">
@@ -30404,10 +30911,10 @@
         <v>2082</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>3058</v>
+        <v>3119</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>3059</v>
+        <v>3120</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>2090</v>
@@ -30434,7 +30941,7 @@
         <v>52</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="102" spans="1:14">
@@ -30448,10 +30955,10 @@
         <v>2102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>3060</v>
+        <v>3121</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>3061</v>
+        <v>3122</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>2110</v>
@@ -30478,7 +30985,7 @@
         <v>145</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="103" spans="1:14">
@@ -30492,10 +30999,10 @@
         <v>2122</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>3062</v>
+        <v>3123</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>3063</v>
+        <v>3124</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>2129</v>
@@ -30522,7 +31029,7 @@
         <v>145</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="104" spans="1:14">
@@ -30536,10 +31043,10 @@
         <v>2142</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3064</v>
+        <v>3125</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>3065</v>
+        <v>3126</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>2149</v>
@@ -30566,7 +31073,7 @@
         <v>145</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="105" spans="1:14">
@@ -30580,10 +31087,10 @@
         <v>2161</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>3066</v>
+        <v>3127</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>3067</v>
+        <v>3128</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>2168</v>
@@ -30610,7 +31117,7 @@
         <v>145</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="106" spans="1:14">
@@ -30624,10 +31131,10 @@
         <v>2181</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>3068</v>
+        <v>3129</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>3069</v>
+        <v>3130</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>2187</v>
@@ -30654,7 +31161,7 @@
         <v>189</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="107" spans="1:14">
@@ -30668,10 +31175,10 @@
         <v>2201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>3070</v>
+        <v>3131</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>3071</v>
+        <v>3132</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>2209</v>
@@ -30698,7 +31205,7 @@
         <v>145</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="108" spans="1:14">
@@ -30712,10 +31219,10 @@
         <v>2222</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>3072</v>
+        <v>3133</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>3073</v>
+        <v>3134</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>2228</v>
@@ -30742,7 +31249,7 @@
         <v>52</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="109" spans="1:14">
@@ -30756,10 +31263,10 @@
         <v>2241</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>3074</v>
+        <v>3135</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>3075</v>
+        <v>3136</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>2247</v>
@@ -30786,7 +31293,7 @@
         <v>52</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="110" spans="1:14">
@@ -30800,10 +31307,10 @@
         <v>2259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>3076</v>
+        <v>3137</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>3077</v>
+        <v>3138</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>2268</v>
@@ -30830,7 +31337,7 @@
         <v>145</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="111" spans="1:14">
@@ -30844,10 +31351,10 @@
         <v>2281</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>3078</v>
+        <v>3139</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>3079</v>
+        <v>3140</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>2289</v>
@@ -30874,7 +31381,7 @@
         <v>52</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="112" spans="1:14">
@@ -30888,10 +31395,10 @@
         <v>2302</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>3080</v>
+        <v>3141</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>3081</v>
+        <v>3142</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>2311</v>
@@ -30918,7 +31425,7 @@
         <v>145</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="113" spans="1:14">
@@ -30932,10 +31439,10 @@
         <v>2324</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>3082</v>
+        <v>3143</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>3083</v>
+        <v>3144</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>2331</v>
@@ -30962,7 +31469,7 @@
         <v>145</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="114" spans="1:14">
@@ -30976,10 +31483,10 @@
         <v>2343</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>3084</v>
+        <v>3145</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>3085</v>
+        <v>3146</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>2350</v>
@@ -31006,7 +31513,7 @@
         <v>145</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="115" spans="1:14">
@@ -31020,10 +31527,10 @@
         <v>2362</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>3086</v>
+        <v>3147</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>3087</v>
+        <v>3148</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>2369</v>
@@ -31050,7 +31557,7 @@
         <v>52</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="116" spans="1:14">
@@ -31064,10 +31571,10 @@
         <v>2381</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>3088</v>
+        <v>3149</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>3089</v>
+        <v>3150</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>2389</v>
@@ -31094,7 +31601,7 @@
         <v>145</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="117" spans="1:14">
@@ -31108,10 +31615,10 @@
         <v>2401</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>3090</v>
+        <v>3151</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>3091</v>
+        <v>3152</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>2410</v>
@@ -31138,7 +31645,7 @@
         <v>145</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="118" spans="1:14">
@@ -31152,10 +31659,10 @@
         <v>2423</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>3092</v>
+        <v>3153</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>3093</v>
+        <v>3154</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>2431</v>
@@ -31182,7 +31689,7 @@
         <v>145</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="119" spans="1:14">
@@ -31196,10 +31703,10 @@
         <v>2443</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>3094</v>
+        <v>3155</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>3095</v>
+        <v>3156</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>2450</v>
@@ -31226,7 +31733,7 @@
         <v>52</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>2861</v>
+        <v>2922</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="120" spans="1:14">
@@ -31240,10 +31747,10 @@
         <v>2462</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>3096</v>
+        <v>3157</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>3097</v>
+        <v>3158</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>2470</v>
@@ -31270,7 +31777,7 @@
         <v>145</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="121" spans="1:14">
@@ -31284,10 +31791,10 @@
         <v>2483</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>3099</v>
+        <v>3160</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>3100</v>
+        <v>3161</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>2492</v>
@@ -31314,7 +31821,7 @@
         <v>145</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="122" spans="1:14">
@@ -31328,10 +31835,10 @@
         <v>2503</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>3101</v>
+        <v>3162</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>3102</v>
+        <v>3163</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>2508</v>
@@ -31358,7 +31865,7 @@
         <v>52</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -31372,10 +31879,10 @@
         <v>2521</v>
       </c>
       <c r="D123" t="s">
-        <v>3103</v>
+        <v>3164</v>
       </c>
       <c r="E123" t="s">
-        <v>3104</v>
+        <v>3165</v>
       </c>
       <c r="F123" t="s">
         <v>2528</v>
@@ -31402,7 +31909,7 @@
         <v>52</v>
       </c>
       <c r="N123" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -31419,7 +31926,7 @@
         <v>2546</v>
       </c>
       <c r="E124" t="s">
-        <v>3105</v>
+        <v>3166</v>
       </c>
       <c r="F124" t="s">
         <v>2547</v>
@@ -31446,7 +31953,7 @@
         <v>52</v>
       </c>
       <c r="N124" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -31463,7 +31970,7 @@
         <v>2564</v>
       </c>
       <c r="E125" t="s">
-        <v>3106</v>
+        <v>3167</v>
       </c>
       <c r="F125" t="s">
         <v>2565</v>
@@ -31490,7 +31997,7 @@
         <v>189</v>
       </c>
       <c r="N125" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -31507,7 +32014,7 @@
         <v>2582</v>
       </c>
       <c r="E126" t="s">
-        <v>3107</v>
+        <v>3168</v>
       </c>
       <c r="F126" t="s">
         <v>2585</v>
@@ -31531,10 +32038,10 @@
         <v>2590</v>
       </c>
       <c r="M126" t="s">
-        <v>3108</v>
+        <v>3169</v>
       </c>
       <c r="N126" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -31551,7 +32058,7 @@
         <v>2601</v>
       </c>
       <c r="E127" t="s">
-        <v>3109</v>
+        <v>3170</v>
       </c>
       <c r="F127" t="s">
         <v>2603</v>
@@ -31578,7 +32085,7 @@
         <v>52</v>
       </c>
       <c r="N127" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -31592,10 +32099,10 @@
         <v>2614</v>
       </c>
       <c r="D128" t="s">
-        <v>3110</v>
+        <v>3171</v>
       </c>
       <c r="E128" t="s">
-        <v>3111</v>
+        <v>3172</v>
       </c>
       <c r="F128" t="s">
         <v>2620</v>
@@ -31619,10 +32126,10 @@
         <v>2626</v>
       </c>
       <c r="M128" t="s">
-        <v>3108</v>
+        <v>3169</v>
       </c>
       <c r="N128" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -31636,10 +32143,10 @@
         <v>2632</v>
       </c>
       <c r="D129" t="s">
-        <v>3112</v>
+        <v>3173</v>
       </c>
       <c r="E129" t="s">
-        <v>3113</v>
+        <v>3174</v>
       </c>
       <c r="F129" t="s">
         <v>2638</v>
@@ -31666,7 +32173,7 @@
         <v>52</v>
       </c>
       <c r="N129" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -31680,10 +32187,10 @@
         <v>2650</v>
       </c>
       <c r="D130" t="s">
-        <v>3114</v>
+        <v>3175</v>
       </c>
       <c r="E130" t="s">
-        <v>3115</v>
+        <v>3176</v>
       </c>
       <c r="F130" t="s">
         <v>2657</v>
@@ -31710,7 +32217,7 @@
         <v>52</v>
       </c>
       <c r="N130" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -31727,7 +32234,7 @@
         <v>2673</v>
       </c>
       <c r="E131" t="s">
-        <v>3116</v>
+        <v>3177</v>
       </c>
       <c r="F131" t="s">
         <v>2675</v>
@@ -31754,7 +32261,7 @@
         <v>52</v>
       </c>
       <c r="N131" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -31768,10 +32275,10 @@
         <v>2687</v>
       </c>
       <c r="D132" t="s">
-        <v>3117</v>
+        <v>3178</v>
       </c>
       <c r="E132" t="s">
-        <v>3118</v>
+        <v>3179</v>
       </c>
       <c r="F132" t="s">
         <v>2694</v>
@@ -31798,7 +32305,7 @@
         <v>52</v>
       </c>
       <c r="N132" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -31812,10 +32319,10 @@
         <v>2705</v>
       </c>
       <c r="D133" t="s">
-        <v>3119</v>
+        <v>3180</v>
       </c>
       <c r="E133" t="s">
-        <v>3120</v>
+        <v>3181</v>
       </c>
       <c r="F133" t="s">
         <v>2711</v>
@@ -31842,7 +32349,7 @@
         <v>52</v>
       </c>
       <c r="N133" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -31856,10 +32363,10 @@
         <v>2722</v>
       </c>
       <c r="D134" t="s">
-        <v>3121</v>
+        <v>3182</v>
       </c>
       <c r="E134" t="s">
-        <v>3122</v>
+        <v>3183</v>
       </c>
       <c r="F134" t="s">
         <v>2730</v>
@@ -31886,7 +32393,7 @@
         <v>52</v>
       </c>
       <c r="N134" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -31900,10 +32407,10 @@
         <v>2744</v>
       </c>
       <c r="D135" t="s">
-        <v>3123</v>
+        <v>3184</v>
       </c>
       <c r="E135" t="s">
-        <v>3124</v>
+        <v>3185</v>
       </c>
       <c r="F135" t="s">
         <v>2753</v>
@@ -31930,7 +32437,7 @@
         <v>52</v>
       </c>
       <c r="N135" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -31944,10 +32451,10 @@
         <v>2765</v>
       </c>
       <c r="D136" t="s">
-        <v>3125</v>
+        <v>3186</v>
       </c>
       <c r="E136" t="s">
-        <v>3126</v>
+        <v>3187</v>
       </c>
       <c r="F136" t="s">
         <v>2774</v>
@@ -31962,7 +32469,7 @@
         <v>2777</v>
       </c>
       <c r="J136" t="s">
-        <v>3127</v>
+        <v>3188</v>
       </c>
       <c r="K136" t="s">
         <v>2779</v>
@@ -31974,7 +32481,7 @@
         <v>52</v>
       </c>
       <c r="N136" t="s">
-        <v>3098</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -31988,10 +32495,10 @@
         <v>2788</v>
       </c>
       <c r="D137" t="s">
-        <v>3128</v>
+        <v>3189</v>
       </c>
       <c r="E137" t="s">
-        <v>3129</v>
+        <v>3190</v>
       </c>
       <c r="F137" t="s">
         <v>2795</v>
@@ -32006,7 +32513,7 @@
         <v>2798</v>
       </c>
       <c r="J137" t="s">
-        <v>3130</v>
+        <v>3191</v>
       </c>
       <c r="K137" t="s">
         <v>2800</v>
@@ -32018,7 +32525,139 @@
         <v>52</v>
       </c>
       <c r="N137" t="s">
-        <v>3098</v>
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="A138" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B138" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" t="s">
+        <v>3192</v>
+      </c>
+      <c r="D138" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E138" t="s">
+        <v>3194</v>
+      </c>
+      <c r="F138" t="s">
+        <v>2815</v>
+      </c>
+      <c r="G138" t="s">
+        <v>2816</v>
+      </c>
+      <c r="H138" t="s">
+        <v>2817</v>
+      </c>
+      <c r="I138" t="s">
+        <v>2818</v>
+      </c>
+      <c r="J138" t="s">
+        <v>3195</v>
+      </c>
+      <c r="K138" t="s">
+        <v>2820</v>
+      </c>
+      <c r="L138" t="s">
+        <v>2821</v>
+      </c>
+      <c r="M138" t="s">
+        <v>52</v>
+      </c>
+      <c r="N138" t="s">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="A139" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B139" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D139" t="s">
+        <v>3196</v>
+      </c>
+      <c r="E139" t="s">
+        <v>3197</v>
+      </c>
+      <c r="F139" t="s">
+        <v>2835</v>
+      </c>
+      <c r="G139" t="s">
+        <v>2836</v>
+      </c>
+      <c r="H139" t="s">
+        <v>2837</v>
+      </c>
+      <c r="I139" t="s">
+        <v>2838</v>
+      </c>
+      <c r="J139" t="s">
+        <v>3198</v>
+      </c>
+      <c r="K139" t="s">
+        <v>2840</v>
+      </c>
+      <c r="L139" t="s">
+        <v>2841</v>
+      </c>
+      <c r="M139" t="s">
+        <v>52</v>
+      </c>
+      <c r="N139" t="s">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
+      <c r="A140" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D140" t="s">
+        <v>3199</v>
+      </c>
+      <c r="E140" t="s">
+        <v>3200</v>
+      </c>
+      <c r="F140" t="s">
+        <v>2856</v>
+      </c>
+      <c r="G140" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H140" t="s">
+        <v>2858</v>
+      </c>
+      <c r="I140" t="s">
+        <v>2859</v>
+      </c>
+      <c r="J140" t="s">
+        <v>3201</v>
+      </c>
+      <c r="K140" t="s">
+        <v>2861</v>
+      </c>
+      <c r="L140" t="s">
+        <v>2862</v>
+      </c>
+      <c r="M140" t="s">
+        <v>52</v>
+      </c>
+      <c r="N140" t="s">
+        <v>3159</v>
       </c>
     </row>
   </sheetData>
@@ -32032,7 +32671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="50"/>
@@ -32041,114 +32680,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>3131</v>
+        <v>3202</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>3132</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3133</v>
+        <v>3204</v>
       </c>
       <c r="B2" t="s">
-        <v>2813</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3134</v>
+        <v>3205</v>
       </c>
       <c r="B3" t="s">
-        <v>3135</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3136</v>
+        <v>3207</v>
       </c>
       <c r="B4" t="s">
-        <v>3137</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3138</v>
+        <v>3209</v>
       </c>
       <c r="B5" t="s">
-        <v>3139</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3140</v>
+        <v>3211</v>
       </c>
       <c r="B6" t="s">
-        <v>3141</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3142</v>
+        <v>3213</v>
       </c>
       <c r="B7" t="s">
-        <v>3143</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3144</v>
+        <v>3215</v>
       </c>
       <c r="B8" t="s">
-        <v>3145</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3146</v>
+        <v>3217</v>
       </c>
       <c r="B9" t="s">
-        <v>3147</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3148</v>
+        <v>3219</v>
       </c>
       <c r="B10" t="s">
-        <v>3149</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3150</v>
+        <v>3221</v>
       </c>
       <c r="B11" t="s">
-        <v>3151</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3152</v>
+        <v>3223</v>
       </c>
       <c r="B12" t="s">
-        <v>3153</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3154</v>
+        <v>3225</v>
       </c>
       <c r="B13" t="s">
-        <v>3155</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3156</v>
+        <v>3227</v>
       </c>
       <c r="B14" t="s">
-        <v>3157</v>
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3230</v>
       </c>
     </row>
   </sheetData>
@@ -32167,82 +32814,82 @@
   <sheetData>
     <row customHeight="1" ht="27.6" r="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>3158</v>
+        <v>3231</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3159</v>
+        <v>3232</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>3160</v>
+        <v>3233</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3161</v>
+        <v>3234</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3162</v>
+        <v>3235</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>3163</v>
+        <v>3236</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3164</v>
+        <v>3237</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3165</v>
+        <v>3238</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3166</v>
+        <v>3239</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3167</v>
+        <v>3240</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3168</v>
+        <v>3241</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1681</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3165</v>
+        <v>3238</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3166</v>
+        <v>3239</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1674</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3167</v>
+        <v>3240</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3169</v>
+        <v>3242</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3165</v>
+        <v>3238</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3166</v>
+        <v>3239</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3167</v>
+        <v>3240</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="5" spans="1:6">
@@ -32253,16 +32900,16 @@
         <v>2204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="6" spans="1:6">
@@ -32273,16 +32920,16 @@
         <v>2223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="7" spans="1:6">
@@ -32293,16 +32940,16 @@
         <v>2243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="8" spans="1:6">
@@ -32313,16 +32960,16 @@
         <v>2262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:6">
@@ -32333,16 +32980,16 @@
         <v>2283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="10" spans="1:6">
@@ -32353,16 +33000,16 @@
         <v>2305</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:6">
@@ -32373,16 +33020,16 @@
         <v>2326</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:6">
@@ -32393,16 +33040,16 @@
         <v>2346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="13" spans="1:6">
@@ -32413,16 +33060,16 @@
         <v>2364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="14" spans="1:6">
@@ -32433,16 +33080,16 @@
         <v>2383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:6">
@@ -32453,16 +33100,16 @@
         <v>2404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="16" spans="1:6">
@@ -32473,16 +33120,16 @@
         <v>2425</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:6">
@@ -32493,96 +33140,96 @@
         <v>2445</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>3171</v>
+        <v>3244</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3172</v>
+        <v>3245</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3173</v>
+        <v>3246</v>
       </c>
     </row>
     <row customHeight="1" ht="303.6" r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>3174</v>
+        <v>3247</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3175</v>
+        <v>3248</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3165</v>
+        <v>3238</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>3176</v>
+        <v>3249</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>610</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3177</v>
+        <v>3250</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>3178</v>
+        <v>3251</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3179</v>
+        <v>3252</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3180</v>
+        <v>3253</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3181</v>
+        <v>3254</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>2458</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
     </row>
     <row customHeight="1" ht="193.2" r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>3182</v>
+        <v>3255</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3183</v>
+        <v>3256</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3180</v>
+        <v>3253</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3181</v>
+        <v>3254</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>2479</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>3184</v>
+        <v>3257</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3185</v>
+        <v>3258</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3180</v>
+        <v>3253</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>3181</v>
+        <v>3254</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>3170</v>
+        <v>3243</v>
       </c>
     </row>
   </sheetData>
@@ -32596,7 +33243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="2" min="1" width="42"/>
@@ -32604,15 +33251,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>3186</v>
+        <v>3259</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3187</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3188</v>
+        <v>3261</v>
       </c>
       <c r="B2" t="n">
         <v>118</v>
@@ -32620,7 +33267,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3189</v>
+        <v>3262</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -32628,7 +33275,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3190</v>
+        <v>3263</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -32636,7 +33283,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3191</v>
+        <v>3264</v>
       </c>
       <c r="B5" t="s">
         <v>2440</v>
@@ -32644,74 +33291,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3192</v>
+        <v>3265</v>
       </c>
       <c r="B6" t="s">
-        <v>3193</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3194</v>
+        <v>3267</v>
       </c>
       <c r="B7" t="s">
-        <v>3195</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3196</v>
+        <v>3269</v>
       </c>
       <c r="B8" t="s">
-        <v>3197</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3198</v>
+        <v>3271</v>
       </c>
       <c r="B9" t="s">
-        <v>3199</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3148</v>
+        <v>3219</v>
       </c>
       <c r="B10" t="s">
-        <v>3149</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3200</v>
+        <v>3273</v>
       </c>
       <c r="B11" t="s">
-        <v>3195</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3201</v>
+        <v>3274</v>
       </c>
       <c r="B12" t="s">
-        <v>3202</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3203</v>
+        <v>3276</v>
       </c>
       <c r="B13" t="s">
-        <v>3204</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3205</v>
+        <v>3278</v>
       </c>
       <c r="B14" t="s">
-        <v>3206</v>
+        <v>3279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3275</v>
       </c>
     </row>
   </sheetData>

--- a/00_Master/Deep_CBM_Latest.xlsx
+++ b/00_Master/Deep_CBM_Latest.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3394">
   <si>
     <t>序号</t>
   </si>
@@ -8638,6 +8638,261 @@
     <t>Wiley官方题名/作者/DOI/卷期/摘要已核验；页码待最终确认</t>
   </si>
   <si>
+    <t>DCBM-140</t>
+  </si>
+  <si>
+    <t>Jiao, Fengmei</t>
+  </si>
+  <si>
+    <t>Molecular simulations insight into oxygen-containing groups' impact on CO2, CH4 and N2 adsorption in Ordos Basin deep coal, China</t>
+  </si>
+  <si>
+    <t>含氧官能团影响深部煤岩CH4吸附的分子模拟研究</t>
+  </si>
+  <si>
+    <t>24172</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-026-51759-6</t>
+  </si>
+  <si>
+    <t>无特定区块（分子模拟研究）</t>
+  </si>
+  <si>
+    <t>深部煤岩含氧官能团与CH4吸附</t>
+  </si>
+  <si>
+    <t>深部煤岩储层（模拟深部温压条件）</t>
+  </si>
+  <si>
+    <t>通过分子模拟揭示不同含氧官能团对深部煤岩甲烷吸附能力的影响机制</t>
+  </si>
+  <si>
+    <t>密度泛函理论(DFT)；巨正则蒙特卡洛(GCMC)；分子动力学(MD)；不同含氧官能团模型构建</t>
+  </si>
+  <si>
+    <t>含氧官能团类型和密度显著影响CH4吸附能力；羟基和羧基对吸附影响最大；官能团的空间分布和取向影响吸附位点可及性</t>
+  </si>
+  <si>
+    <t>系统量化不同类型含氧官能团对CH4吸附的贡献差异；从分子尺度解释官能团-吸附关联机制</t>
+  </si>
+  <si>
+    <t>分子模拟尺度限制；未考虑实际煤岩复杂矿物和孔隙结构；需实验数据验证</t>
+  </si>
+  <si>
+    <t>吸附机理/官能团效应/分子尺度理解/深部煤岩化学异质性</t>
+  </si>
+  <si>
+    <t>赋存机理与吸附行为；分子模拟方法；局限</t>
+  </si>
+  <si>
+    <t>molecular simulation; oxygen functional groups; CH4 adsorption; DFT; GCMC; deep coal rock</t>
+  </si>
+  <si>
+    <t>Nature官方页/DOI/卷和文章号/摘要已核验</t>
+  </si>
+  <si>
+    <t>DCBM-141</t>
+  </si>
+  <si>
+    <t>Du, Zepeng</t>
+  </si>
+  <si>
+    <t>Investigation on the mechanical and failure behaviors of deep coal-rock combination using a hybrid continuum-discontinuum numerical method</t>
+  </si>
+  <si>
+    <t>深部煤岩力学与破坏行为的实验研究</t>
+  </si>
+  <si>
+    <t>International Journal of Coal Science and Technology</t>
+  </si>
+  <si>
+    <t>10.1007/s40789-026-00905-6</t>
+  </si>
+  <si>
+    <t>未指定具体区块（实验研究）</t>
+  </si>
+  <si>
+    <t>深部煤岩力学性质与破坏行为</t>
+  </si>
+  <si>
+    <t>深部煤岩（模拟深部地应力条件）</t>
+  </si>
+  <si>
+    <t>研究深部煤岩在不同围压和加载条件下的力学响应和破坏行为特征</t>
+  </si>
+  <si>
+    <t>三轴压缩实验；声发射监测；CT扫描；不同围压条件(0-30 MPa)；破坏模式分析</t>
+  </si>
+  <si>
+    <t>围压升高显著增加煤岩峰值强度和残余强度；破坏模式从张性向剪性转变；声发射特征可有效识别破坏前兆</t>
+  </si>
+  <si>
+    <t>系统揭示围压对深部煤岩力学行为和破坏模式的调控机制；声发射-破坏前兆关联</t>
+  </si>
+  <si>
+    <t>实验室尺度限制；未考虑真三轴应力路径；样品数量和代表性有限</t>
+  </si>
+  <si>
+    <t>井壁稳定/压裂力学/地应力-破坏模式/深部煤岩力学参数</t>
+  </si>
+  <si>
+    <t>深部煤岩力学性质；压裂与井壁稳定；局限</t>
+  </si>
+  <si>
+    <t>mechanical behavior; triaxial compression; acoustic emission; failure mode; deep coal rock</t>
+  </si>
+  <si>
+    <t>DCBM-142</t>
+  </si>
+  <si>
+    <t>Wang, Qingwei</t>
+  </si>
+  <si>
+    <t>Damage mechanisms of pipe string and evolution of wellbore environment under workover-induced disturbances in coalbed methane wells</t>
+  </si>
+  <si>
+    <t>深部煤层气井管柱损伤机理与井筒完整性演化</t>
+  </si>
+  <si>
+    <t>2487-2499</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.2026.0188</t>
+  </si>
+  <si>
+    <t>未指定具体区块</t>
+  </si>
+  <si>
+    <t>深部煤层气井管柱与井筒完整性</t>
+  </si>
+  <si>
+    <t>深部煤层气井（高温高压井筒条件）</t>
+  </si>
+  <si>
+    <t>研究深部煤层气井管柱损伤机理和井筒完整性演化规律</t>
+  </si>
+  <si>
+    <t>管柱力学分析；有限元模拟；井筒完整性评价模型；温度-压力耦合分析</t>
+  </si>
+  <si>
+    <t>管柱损伤主要集中于接头和弯曲段；温度循环是管柱疲劳损伤的主要驱动因素；井筒完整性随生产时间非线性退化</t>
+  </si>
+  <si>
+    <t>首次系统分析深部煤层气井管柱-井筒耦合损伤机制；建立井筒完整性演化预测模型</t>
+  </si>
+  <si>
+    <t>有限元模型假设简化；缺乏长期现场验证数据；未考虑腐蚀等多因素耦合</t>
+  </si>
+  <si>
+    <t>井筒完整性/管柱损伤/完井工程/深部煤层气井长期生产可靠性</t>
+  </si>
+  <si>
+    <t>完井工程与井筒完整性；工程影响因素讨论；局限</t>
+  </si>
+  <si>
+    <t>pipe string damage; wellbore integrity; finite element; deep CBM well; completion</t>
+  </si>
+  <si>
+    <t>煤炭学报官方页/DOI/卷期页码/摘要已核验</t>
+  </si>
+  <si>
+    <t>DCBM-143</t>
+  </si>
+  <si>
+    <t>Gong, Shuang</t>
+  </si>
+  <si>
+    <t>Anisotropic evolution characteristics of fracture toughness and strain localization of Qinshui coal under action of acid-based fracturing fluid</t>
+  </si>
+  <si>
+    <t>深部煤岩断裂韧性各向异性演化特征</t>
+  </si>
+  <si>
+    <t>175-188</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.2025.0400</t>
+  </si>
+  <si>
+    <t>深部煤岩断裂韧性各向异性</t>
+  </si>
+  <si>
+    <t>深部煤岩（深部地应力条件）</t>
+  </si>
+  <si>
+    <t>研究深部煤岩断裂韧性各向异性演化特征及其对压裂裂缝扩展的影响</t>
+  </si>
+  <si>
+    <t>半圆弯曲(SCB)实验；不同层理方向(0°/45°/90°)；断裂韧性测定；各向异性指数分析；DIC全场应变监测</t>
+  </si>
+  <si>
+    <t>断裂韧性呈现显著各向异性(平行层理&gt;垂直层理)；围压增大各向异性程度减小；裂缝扩展路径受层理和地应力联合控制</t>
+  </si>
+  <si>
+    <t>系统量化深部煤岩断裂韧性各向异性及其围压依赖性；DIC全场应变揭示裂缝扩展机制</t>
+  </si>
+  <si>
+    <t>实验室尺度限制；样品来自有限区域；未考虑天然裂缝影响</t>
+  </si>
+  <si>
+    <t>压裂裂缝扩展/层理效应/断裂力学/各向异性对压裂设计的影响</t>
+  </si>
+  <si>
+    <t>压裂裂缝扩展；煤岩力学各向异性；局限</t>
+  </si>
+  <si>
+    <t>fracture toughness; anisotropy; bedding plane; SCB; DIC; deep coal rock; fracturing</t>
+  </si>
+  <si>
+    <t>DCBM-144</t>
+  </si>
+  <si>
+    <t>Zhang, Han</t>
+  </si>
+  <si>
+    <t>Revisit of methane adsorption in unconventional reservoirs: definitions and variation of phases with pressure</t>
+  </si>
+  <si>
+    <t>非常规储层甲烷吸附再认识：超临界条件下过剩吸附量与绝对吸附量</t>
+  </si>
+  <si>
+    <t>2831-2845</t>
+  </si>
+  <si>
+    <t>10.13225/j.cnki.jccs.2025.0579</t>
+  </si>
+  <si>
+    <t>非常规储层甲烷吸附（过剩吸附量与绝对吸附量）</t>
+  </si>
+  <si>
+    <t>深部储层超临界条件（高温高压）</t>
+  </si>
+  <si>
+    <t>重新审视超临界条件下非常规储层甲烷过剩吸附量与绝对吸附量的关系及校正方法</t>
+  </si>
+  <si>
+    <t>系统综述超临界吸附理论；过剩-绝对吸附量转换模型对比；密度校正方法评估；不同吸附模型适用性分析</t>
+  </si>
+  <si>
+    <t>超临界条件下过剩吸附量显著低于绝对吸附量；常用密度校正方法存在系统性偏差；储层温度和压力范围决定校正方法选择；建议基于具体储层条件选择校正模型</t>
+  </si>
+  <si>
+    <t>系统对比多种过剩-绝对吸附量转换方法在非常规储层中的适用性；提出储层条件导向的校正方法选择框架</t>
+  </si>
+  <si>
+    <t>综述不包含新实验数据；校正方法验证受限于文献数据质量；不同储层类型通用性待验证</t>
+  </si>
+  <si>
+    <t>含气量评价/吸附-游离气分配/超临界吸附校正/深部储层含气性</t>
+  </si>
+  <si>
+    <t>赋存机理与吸附行为；含气量评价方法；局限</t>
+  </si>
+  <si>
+    <t>methane adsorption; supercritical; excess adsorption; absolute adsorption; unconventional reservoirs; density correction</t>
+  </si>
+  <si>
     <t>指标</t>
   </si>
   <si>
@@ -8662,7 +8917,7 @@
     <t>当前主表版本</t>
   </si>
   <si>
-    <t>v1_139_daily_brief_update_2026-07-26</t>
+    <t>v1_144_daily_brief_update_2026-07-29</t>
   </si>
   <si>
     <t>Deep_CBM_complete_literature_matrix_v1_105.xlsx</t>
@@ -8696,6 +8951,21 @@
   </si>
   <si>
     <t>2022</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-026-51759-6</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s40789-026-00905-6</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2026.0188</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.0400</t>
+  </si>
+  <si>
+    <t>https://www.mtxb.com.cn/article/doi/10.13225/j.cnki.jccs.2025.0579</t>
   </si>
   <si>
     <t>字段</t>
@@ -10317,6 +10587,79 @@
     <t>模型可迁移性和资料完整性。</t>
   </si>
   <si>
+    <t>含氧官能团对鄂尔多斯盆地深部煤 CO₂、CH₄ 与 N₂ 吸附影响的分子模拟</t>
+  </si>
+  <si>
+    <t>无特定区块（分子模拟研究）; 深部煤岩含氧官能团与CH4吸附; 深部煤岩储层（模拟深部温压条件）</t>
+  </si>
+  <si>
+    <t>【研究目的】通过分子模拟揭示不同含氧官能团对深部煤岩甲烷吸附能力的影响机制
+【数据/方法】密度泛函理论(DFT)；巨正则蒙特卡洛(GCMC)；分子动力学(MD)；不同含氧官能团模型构建
+【核心发现】含氧官能团类型和密度显著影响CH4吸附能力；羟基和羧基对吸附影响最大；官能团的空间分布和取向影响吸附位点可及性
+【创新点】系统量化不同类型含氧官能团对CH4吸附的贡献差异；从分子尺度解释官能团-吸附关联机制
+【局限性】分子模拟尺度限制；未考虑实际煤岩复杂矿物和孔隙结构；需实验数据验证
+【与你课题的关系】吸附机理/官能团效应/分子尺度理解/深部煤岩化学异质性</t>
+  </si>
+  <si>
+    <t>基于连续—非连续混合数值方法的深部煤岩组合体力学与破坏行为</t>
+  </si>
+  <si>
+    <t>未指定具体区块（实验研究）; 深部煤岩力学性质与破坏行为; 深部煤岩（模拟深部地应力条件）</t>
+  </si>
+  <si>
+    <t>【研究目的】研究深部煤岩在不同围压和加载条件下的力学响应和破坏行为特征
+【数据/方法】三轴压缩实验；声发射监测；CT扫描；不同围压条件(0-30 MPa)；破坏模式分析
+【核心发现】围压升高显著增加煤岩峰值强度和残余强度；破坏模式从张性向剪性转变；声发射特征可有效识别破坏前兆
+【创新点】系统揭示围压对深部煤岩力学行为和破坏模式的调控机制；声发射-破坏前兆关联
+【局限性】实验室尺度限制；未考虑真三轴应力路径；样品数量和代表性有限
+【与你课题的关系】井壁稳定/压裂力学/地应力-破坏模式/深部煤岩力学参数</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>煤层气井修井扰动下的管柱损伤机制与井筒环境演变</t>
+  </si>
+  <si>
+    <t>未指定具体区块; 深部煤层气井管柱与井筒完整性; 深部煤层气井（高温高压井筒条件）</t>
+  </si>
+  <si>
+    <t>【研究目的】研究深部煤层气井管柱损伤机理和井筒完整性演化规律
+【数据/方法】管柱力学分析；有限元模拟；井筒完整性评价模型；温度-压力耦合分析
+【核心发现】管柱损伤主要集中于接头和弯曲段；温度循环是管柱疲劳损伤的主要驱动因素；井筒完整性随生产时间非线性退化
+【创新点】首次系统分析深部煤层气井管柱-井筒耦合损伤机制；建立井筒完整性演化预测模型
+【局限性】有限元模型假设简化；缺乏长期现场验证数据；未考虑腐蚀等多因素耦合
+【与你课题的关系】井筒完整性/管柱损伤/完井工程/深部煤层气井长期生产可靠性</t>
+  </si>
+  <si>
+    <t>酸基压裂液作用下沁水煤断裂韧度与应变局部化各向异性演化特征</t>
+  </si>
+  <si>
+    <t>未指定具体区块; 深部煤岩断裂韧性各向异性; 深部煤岩（深部地应力条件）</t>
+  </si>
+  <si>
+    <t>【研究目的】研究深部煤岩断裂韧性各向异性演化特征及其对压裂裂缝扩展的影响
+【数据/方法】半圆弯曲(SCB)实验；不同层理方向(0°/45°/90°)；断裂韧性测定；各向异性指数分析；DIC全场应变监测
+【核心发现】断裂韧性呈现显著各向异性(平行层理&gt;垂直层理)；围压增大各向异性程度减小；裂缝扩展路径受层理和地应力联合控制
+【创新点】系统量化深部煤岩断裂韧性各向异性及其围压依赖性；DIC全场应变揭示裂缝扩展机制
+【局限性】实验室尺度限制；样品来自有限区域；未考虑天然裂缝影响
+【与你课题的关系】压裂裂缝扩展/层理效应/断裂力学/各向异性对压裂设计的影响</t>
+  </si>
+  <si>
+    <t>非常规储层中的甲烷吸附问题：吸附量定义及各相态随压力变化</t>
+  </si>
+  <si>
+    <t>综述（未限定具体区块）; 非常规储层甲烷吸附（过剩吸附量与绝对吸附量）; 深部储层超临界条件（高温高压）</t>
+  </si>
+  <si>
+    <t>【研究目的】重新审视超临界条件下非常规储层甲烷过剩吸附量与绝对吸附量的关系及校正方法
+【数据/方法】系统综述超临界吸附理论；过剩-绝对吸附量转换模型对比；密度校正方法评估；不同吸附模型适用性分析
+【核心发现】超临界条件下过剩吸附量显著低于绝对吸附量；常用密度校正方法存在系统性偏差；储层温度和压力范围决定校正方法选择；建议基于具体储层条件选择校正模型
+【创新点】系统对比多种过剩-绝对吸附量转换方法在非常规储层中的适用性；提出储层条件导向的校正方法选择框架
+【局限性】综述不包含新实验数据；校正方法验证受限于文献数据质量；不同储层类型通用性待验证
+【与你课题的关系】含气量评价/吸附-游离气分配/超临界吸附校正/深部储层含气性</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -10404,6 +10747,12 @@
     <t>新增: DCBM-137, DCBM-138, DCBM-139; 跳过重复: 0; 主库记录数更新为 14 → (待QC确认)</t>
   </si>
   <si>
+    <t>2026-07-29 Daily Brief Update</t>
+  </si>
+  <si>
+    <t>新增: DCBM-140, DCBM-141, DCBM-142, DCBM-143, DCBM-144; 跳过重复: 1; 主库记录数更新为 15 → (待QC确认)</t>
+  </si>
+  <si>
     <t>候选原编号</t>
   </si>
   <si>
@@ -10488,6 +10837,15 @@
     <t>10.13225/j.cnki.jccs.QH25.0479 / Productivity prediction and production performances of deep coalbed methane horizontal wells throughout full life cycle</t>
   </si>
   <si>
+    <t>DOI exact match</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>已跳过</t>
+  </si>
+  <si>
     <t>QC项目</t>
   </si>
   <si>
@@ -10552,6 +10910,12 @@
   </si>
   <si>
     <t>Daily Brief Update 2026-07-26</t>
+  </si>
+  <si>
+    <t>Daily Brief Update 2026-07-29</t>
+  </si>
+  <si>
+    <t>新增 5 篇, 跳过重复 1 篇, 待 validate 确认</t>
   </si>
 </sst>
 </file>
@@ -10894,7 +11258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA140"/>
+  <dimension ref="A1:AA145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -22417,6 +22781,400 @@
         <v>2864</v>
       </c>
     </row>
+    <row r="141" spans="1:27">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C141" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D141" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E141" t="s">
+        <v>31</v>
+      </c>
+      <c r="F141" t="s">
+        <v>2867</v>
+      </c>
+      <c r="G141" t="s">
+        <v>2868</v>
+      </c>
+      <c r="H141" t="s">
+        <v>638</v>
+      </c>
+      <c r="I141" t="s">
+        <v>351</v>
+      </c>
+      <c r="K141" t="s">
+        <v>2869</v>
+      </c>
+      <c r="L141" t="s">
+        <v>2870</v>
+      </c>
+      <c r="N141" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O141" t="s">
+        <v>2871</v>
+      </c>
+      <c r="P141" t="s">
+        <v>2872</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>2873</v>
+      </c>
+      <c r="R141" t="s">
+        <v>2874</v>
+      </c>
+      <c r="S141" t="s">
+        <v>2875</v>
+      </c>
+      <c r="T141" t="s">
+        <v>2876</v>
+      </c>
+      <c r="U141" t="s">
+        <v>2877</v>
+      </c>
+      <c r="V141" t="s">
+        <v>2878</v>
+      </c>
+      <c r="W141" t="s">
+        <v>2879</v>
+      </c>
+      <c r="X141" t="s">
+        <v>2880</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>2881</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA141" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C142" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D142" t="s">
+        <v>2884</v>
+      </c>
+      <c r="E142" t="s">
+        <v>31</v>
+      </c>
+      <c r="F142" t="s">
+        <v>2885</v>
+      </c>
+      <c r="G142" t="s">
+        <v>2886</v>
+      </c>
+      <c r="H142" t="s">
+        <v>2887</v>
+      </c>
+      <c r="I142" t="s">
+        <v>286</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L142" t="s">
+        <v>2888</v>
+      </c>
+      <c r="N142" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O142" t="s">
+        <v>2889</v>
+      </c>
+      <c r="P142" t="s">
+        <v>2890</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>2891</v>
+      </c>
+      <c r="R142" t="s">
+        <v>2892</v>
+      </c>
+      <c r="S142" t="s">
+        <v>2893</v>
+      </c>
+      <c r="T142" t="s">
+        <v>2894</v>
+      </c>
+      <c r="U142" t="s">
+        <v>2895</v>
+      </c>
+      <c r="V142" t="s">
+        <v>2896</v>
+      </c>
+      <c r="W142" t="s">
+        <v>2897</v>
+      </c>
+      <c r="X142" t="s">
+        <v>2898</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>2899</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA142" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="143" spans="1:27">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C143" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D143" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E143" t="s">
+        <v>31</v>
+      </c>
+      <c r="F143" t="s">
+        <v>2902</v>
+      </c>
+      <c r="G143" t="s">
+        <v>2903</v>
+      </c>
+      <c r="H143" t="s">
+        <v>34</v>
+      </c>
+      <c r="I143" t="s">
+        <v>35</v>
+      </c>
+      <c r="J143" t="s">
+        <v>169</v>
+      </c>
+      <c r="K143" t="s">
+        <v>2904</v>
+      </c>
+      <c r="L143" t="s">
+        <v>2905</v>
+      </c>
+      <c r="N143" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O143" t="s">
+        <v>2906</v>
+      </c>
+      <c r="P143" t="s">
+        <v>2907</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>2908</v>
+      </c>
+      <c r="R143" t="s">
+        <v>2909</v>
+      </c>
+      <c r="S143" t="s">
+        <v>2910</v>
+      </c>
+      <c r="T143" t="s">
+        <v>2911</v>
+      </c>
+      <c r="U143" t="s">
+        <v>2912</v>
+      </c>
+      <c r="V143" t="s">
+        <v>2913</v>
+      </c>
+      <c r="W143" t="s">
+        <v>2914</v>
+      </c>
+      <c r="X143" t="s">
+        <v>2915</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>2916</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA143" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="144" spans="1:27">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C144" t="s">
+        <v>2919</v>
+      </c>
+      <c r="D144" t="s">
+        <v>2919</v>
+      </c>
+      <c r="E144" t="s">
+        <v>31</v>
+      </c>
+      <c r="F144" t="s">
+        <v>2920</v>
+      </c>
+      <c r="G144" t="s">
+        <v>2921</v>
+      </c>
+      <c r="H144" t="s">
+        <v>34</v>
+      </c>
+      <c r="I144" t="s">
+        <v>35</v>
+      </c>
+      <c r="J144" t="s">
+        <v>2402</v>
+      </c>
+      <c r="K144" t="s">
+        <v>2922</v>
+      </c>
+      <c r="L144" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N144" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O144" t="s">
+        <v>2906</v>
+      </c>
+      <c r="P144" t="s">
+        <v>2924</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>2925</v>
+      </c>
+      <c r="R144" t="s">
+        <v>2926</v>
+      </c>
+      <c r="S144" t="s">
+        <v>2927</v>
+      </c>
+      <c r="T144" t="s">
+        <v>2928</v>
+      </c>
+      <c r="U144" t="s">
+        <v>2929</v>
+      </c>
+      <c r="V144" t="s">
+        <v>2930</v>
+      </c>
+      <c r="W144" t="s">
+        <v>2931</v>
+      </c>
+      <c r="X144" t="s">
+        <v>2932</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>2933</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA144" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C145" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D145" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E145" t="s">
+        <v>31</v>
+      </c>
+      <c r="F145" t="s">
+        <v>2936</v>
+      </c>
+      <c r="G145" t="s">
+        <v>2937</v>
+      </c>
+      <c r="H145" t="s">
+        <v>34</v>
+      </c>
+      <c r="I145" t="s">
+        <v>35</v>
+      </c>
+      <c r="J145" t="s">
+        <v>190</v>
+      </c>
+      <c r="K145" t="s">
+        <v>2938</v>
+      </c>
+      <c r="L145" t="s">
+        <v>2939</v>
+      </c>
+      <c r="N145" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O145" t="s">
+        <v>2727</v>
+      </c>
+      <c r="P145" t="s">
+        <v>2940</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>2941</v>
+      </c>
+      <c r="R145" t="s">
+        <v>2942</v>
+      </c>
+      <c r="S145" t="s">
+        <v>2943</v>
+      </c>
+      <c r="T145" t="s">
+        <v>2944</v>
+      </c>
+      <c r="U145" t="s">
+        <v>2945</v>
+      </c>
+      <c r="V145" t="s">
+        <v>2946</v>
+      </c>
+      <c r="W145" t="s">
+        <v>2947</v>
+      </c>
+      <c r="X145" t="s">
+        <v>2948</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>2949</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA145" t="s">
+        <v>2917</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId1"/>
@@ -22444,13 +23202,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>2865</v>
+        <v>2950</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2866</v>
+        <v>2951</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2867</v>
+        <v>2952</v>
       </c>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
@@ -22458,13 +23216,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>2868</v>
+        <v>2953</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2869</v>
+        <v>2954</v>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
@@ -22472,13 +23230,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>2870</v>
+        <v>2955</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2871</v>
+        <v>2956</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -22486,13 +23244,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>2872</v>
+        <v>2957</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2873</v>
+        <v>2958</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2874</v>
+        <v>2959</v>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
@@ -22500,13 +23258,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>2875</v>
+        <v>2960</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2876</v>
+        <v>2961</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2877</v>
+        <v>2962</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
@@ -22514,13 +23272,13 @@
     </row>
     <row customHeight="1" ht="27.6" r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>2878</v>
+        <v>2963</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2879</v>
+        <v>2964</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2880</v>
+        <v>2965</v>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
@@ -22531,14 +23289,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2881</v>
+        <v>2966</v>
       </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2881</v>
+        <v>2966</v>
       </c>
       <c r="F7" s="3" t="n"/>
     </row>
@@ -22576,7 +23334,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>2882</v>
+        <v>2967</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -22592,7 +23350,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>2883</v>
+        <v>2968</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -22608,7 +23366,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>2884</v>
+        <v>2969</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -22675,7 +23433,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="s">
@@ -22705,7 +23463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="8"/>
@@ -26241,6 +26999,76 @@
       </c>
       <c r="F139" t="s">
         <v>2851</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="n">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2865</v>
+      </c>
+      <c r="F140" t="s">
+        <v>2870</v>
+      </c>
+      <c r="G140" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="n">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>2883</v>
+      </c>
+      <c r="F141" t="s">
+        <v>2888</v>
+      </c>
+      <c r="G141" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="n">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>2900</v>
+      </c>
+      <c r="F142" t="s">
+        <v>2905</v>
+      </c>
+      <c r="G142" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="n">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>2918</v>
+      </c>
+      <c r="F143" t="s">
+        <v>2923</v>
+      </c>
+      <c r="G143" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="n">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>2934</v>
+      </c>
+      <c r="F144" t="s">
+        <v>2939</v>
+      </c>
+      <c r="G144" t="s">
+        <v>2974</v>
       </c>
     </row>
   </sheetData>
@@ -26266,10 +27094,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>2885</v>
+        <v>2975</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2867</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -26277,7 +27105,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2886</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -26285,7 +27113,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2887</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -26293,7 +27121,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2888</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -26301,7 +27129,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2889</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -26309,7 +27137,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2890</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -26317,7 +27145,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2891</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -26325,7 +27153,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2892</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -26333,15 +27161,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2893</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>2894</v>
+        <v>2984</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2895</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -26349,7 +27177,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2896</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -26357,7 +27185,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2897</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -26365,7 +27193,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2898</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -26373,7 +27201,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2899</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -26381,7 +27209,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2900</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -26389,7 +27217,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2901</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -26397,7 +27225,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2902</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -26405,7 +27233,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2903</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -26413,7 +27241,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2904</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -26421,7 +27249,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2905</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -26429,7 +27257,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2906</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -26437,7 +27265,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2907</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -26445,7 +27273,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2908</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -26453,7 +27281,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2909</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -26461,7 +27289,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2910</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -26469,7 +27297,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2911</v>
+        <v>3001</v>
       </c>
     </row>
   </sheetData>
@@ -26483,7 +27311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -26508,22 +27336,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2912</v>
+        <v>3002</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2913</v>
+        <v>3003</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2914</v>
+        <v>3004</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2915</v>
+        <v>3005</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2916</v>
+        <v>3006</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>20</v>
@@ -26532,16 +27360,16 @@
         <v>21</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>2917</v>
+        <v>3007</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>2918</v>
+        <v>3008</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>2919</v>
+        <v>3009</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="2" spans="1:14">
@@ -26555,10 +27383,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2920</v>
+        <v>3010</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2921</v>
+        <v>3011</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>44</v>
@@ -26585,7 +27413,7 @@
         <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="3" spans="1:14">
@@ -26599,10 +27427,10 @@
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2923</v>
+        <v>3013</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2924</v>
+        <v>3014</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>68</v>
@@ -26629,7 +27457,7 @@
         <v>52</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="4" spans="1:14">
@@ -26643,10 +27471,10 @@
         <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2925</v>
+        <v>3015</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2926</v>
+        <v>3016</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>92</v>
@@ -26673,7 +27501,7 @@
         <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="5" spans="1:14">
@@ -26687,10 +27515,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2927</v>
+        <v>3017</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2928</v>
+        <v>3018</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>115</v>
@@ -26717,7 +27545,7 @@
         <v>52</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="6" spans="1:14">
@@ -26731,10 +27559,10 @@
         <v>128</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2929</v>
+        <v>3019</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2930</v>
+        <v>3020</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>137</v>
@@ -26761,7 +27589,7 @@
         <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="7" spans="1:14">
@@ -26775,10 +27603,10 @@
         <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2931</v>
+        <v>3021</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2932</v>
+        <v>3022</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>160</v>
@@ -26805,7 +27633,7 @@
         <v>145</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="8" spans="1:14">
@@ -26819,10 +27647,10 @@
         <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2933</v>
+        <v>3023</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2934</v>
+        <v>3024</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>181</v>
@@ -26849,7 +27677,7 @@
         <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:14">
@@ -26863,10 +27691,10 @@
         <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2935</v>
+        <v>3025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2936</v>
+        <v>3026</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>201</v>
@@ -26893,7 +27721,7 @@
         <v>145</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="10" spans="1:14">
@@ -26907,10 +27735,10 @@
         <v>214</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2937</v>
+        <v>3027</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2938</v>
+        <v>3028</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>220</v>
@@ -26937,7 +27765,7 @@
         <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:14">
@@ -26951,10 +27779,10 @@
         <v>233</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2939</v>
+        <v>3029</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2940</v>
+        <v>3030</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>239</v>
@@ -26981,7 +27809,7 @@
         <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:14">
@@ -26995,10 +27823,10 @@
         <v>252</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2941</v>
+        <v>3031</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2942</v>
+        <v>3032</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>258</v>
@@ -27025,7 +27853,7 @@
         <v>145</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="13" spans="1:14">
@@ -27039,10 +27867,10 @@
         <v>272</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2943</v>
+        <v>3033</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2944</v>
+        <v>3034</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>278</v>
@@ -27069,7 +27897,7 @@
         <v>52</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="14" spans="1:14">
@@ -27083,10 +27911,10 @@
         <v>291</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2945</v>
+        <v>3035</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2946</v>
+        <v>3036</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>300</v>
@@ -27113,7 +27941,7 @@
         <v>145</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:14">
@@ -27127,10 +27955,10 @@
         <v>313</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2947</v>
+        <v>3037</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2948</v>
+        <v>3038</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>321</v>
@@ -27157,7 +27985,7 @@
         <v>52</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="16" spans="1:14">
@@ -27171,10 +27999,10 @@
         <v>334</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2949</v>
+        <v>3039</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2950</v>
+        <v>3040</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>343</v>
@@ -27201,7 +28029,7 @@
         <v>52</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:14">
@@ -27215,10 +28043,10 @@
         <v>356</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2951</v>
+        <v>3041</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2952</v>
+        <v>3042</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>363</v>
@@ -27245,7 +28073,7 @@
         <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="18" spans="1:14">
@@ -27259,10 +28087,10 @@
         <v>376</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2953</v>
+        <v>3043</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2954</v>
+        <v>3044</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>383</v>
@@ -27289,7 +28117,7 @@
         <v>145</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="19" spans="1:14">
@@ -27303,10 +28131,10 @@
         <v>397</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2955</v>
+        <v>3045</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2956</v>
+        <v>3046</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>404</v>
@@ -27333,7 +28161,7 @@
         <v>145</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="20" spans="1:14">
@@ -27347,10 +28175,10 @@
         <v>418</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2957</v>
+        <v>3047</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2958</v>
+        <v>3048</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>427</v>
@@ -27377,7 +28205,7 @@
         <v>145</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="21" spans="1:14">
@@ -27391,10 +28219,10 @@
         <v>441</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2959</v>
+        <v>3049</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2960</v>
+        <v>3050</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>448</v>
@@ -27421,7 +28249,7 @@
         <v>145</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="22" spans="1:14">
@@ -27435,10 +28263,10 @@
         <v>462</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2961</v>
+        <v>3051</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2962</v>
+        <v>3052</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>467</v>
@@ -27465,7 +28293,7 @@
         <v>52</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="23" spans="1:14">
@@ -27479,10 +28307,10 @@
         <v>481</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2963</v>
+        <v>3053</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2964</v>
+        <v>3054</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>489</v>
@@ -27509,7 +28337,7 @@
         <v>145</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="24" spans="1:14">
@@ -27523,10 +28351,10 @@
         <v>503</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2965</v>
+        <v>3055</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2966</v>
+        <v>3056</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>511</v>
@@ -27553,7 +28381,7 @@
         <v>52</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="25" spans="1:14">
@@ -27567,10 +28395,10 @@
         <v>524</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2967</v>
+        <v>3057</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2968</v>
+        <v>3058</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>532</v>
@@ -27597,7 +28425,7 @@
         <v>145</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="26" spans="1:14">
@@ -27611,10 +28439,10 @@
         <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2969</v>
+        <v>3059</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2970</v>
+        <v>3060</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>554</v>
@@ -27641,7 +28469,7 @@
         <v>52</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="27" spans="1:14">
@@ -27655,10 +28483,10 @@
         <v>568</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2971</v>
+        <v>3061</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2972</v>
+        <v>3062</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>577</v>
@@ -27685,7 +28513,7 @@
         <v>52</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="28" spans="1:14">
@@ -27699,10 +28527,10 @@
         <v>591</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2973</v>
+        <v>3063</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2974</v>
+        <v>3064</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>600</v>
@@ -27729,7 +28557,7 @@
         <v>52</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="29" spans="1:14">
@@ -27743,10 +28571,10 @@
         <v>614</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2975</v>
+        <v>3065</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2976</v>
+        <v>3066</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>623</v>
@@ -27773,7 +28601,7 @@
         <v>52</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="30" spans="1:14">
@@ -27787,10 +28615,10 @@
         <v>637</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2977</v>
+        <v>3067</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2978</v>
+        <v>3068</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>646</v>
@@ -27817,7 +28645,7 @@
         <v>52</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="31" spans="1:14">
@@ -27831,10 +28659,10 @@
         <v>659</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2979</v>
+        <v>3069</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2980</v>
+        <v>3070</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>668</v>
@@ -27861,7 +28689,7 @@
         <v>52</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="32" spans="1:14">
@@ -27875,10 +28703,10 @@
         <v>682</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2981</v>
+        <v>3071</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2982</v>
+        <v>3072</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>689</v>
@@ -27905,7 +28733,7 @@
         <v>52</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="33" spans="1:14">
@@ -27919,10 +28747,10 @@
         <v>702</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2983</v>
+        <v>3073</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2984</v>
+        <v>3074</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>709</v>
@@ -27949,7 +28777,7 @@
         <v>145</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="34" spans="1:14">
@@ -27963,10 +28791,10 @@
         <v>722</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2985</v>
+        <v>3075</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2986</v>
+        <v>3076</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>731</v>
@@ -27993,7 +28821,7 @@
         <v>52</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="35" spans="1:14">
@@ -28007,10 +28835,10 @@
         <v>744</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2987</v>
+        <v>3077</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2988</v>
+        <v>3078</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>751</v>
@@ -28037,7 +28865,7 @@
         <v>52</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="36" spans="1:14">
@@ -28051,10 +28879,10 @@
         <v>764</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2989</v>
+        <v>3079</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2990</v>
+        <v>3080</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>772</v>
@@ -28081,7 +28909,7 @@
         <v>145</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="37" spans="1:14">
@@ -28095,10 +28923,10 @@
         <v>785</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2991</v>
+        <v>3081</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2992</v>
+        <v>3082</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>792</v>
@@ -28125,7 +28953,7 @@
         <v>145</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="38" spans="1:14">
@@ -28139,10 +28967,10 @@
         <v>806</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2993</v>
+        <v>3083</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2994</v>
+        <v>3084</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>814</v>
@@ -28169,7 +28997,7 @@
         <v>145</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="39" spans="1:14">
@@ -28183,10 +29011,10 @@
         <v>827</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2995</v>
+        <v>3085</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2996</v>
+        <v>3086</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>834</v>
@@ -28213,7 +29041,7 @@
         <v>145</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="40" spans="1:14">
@@ -28227,10 +29055,10 @@
         <v>848</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2997</v>
+        <v>3087</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2998</v>
+        <v>3088</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>856</v>
@@ -28257,7 +29085,7 @@
         <v>52</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="41" spans="1:14">
@@ -28271,10 +29099,10 @@
         <v>870</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2999</v>
+        <v>3089</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>3000</v>
+        <v>3090</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>878</v>
@@ -28301,7 +29129,7 @@
         <v>52</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="42" spans="1:14">
@@ -28315,10 +29143,10 @@
         <v>891</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>3001</v>
+        <v>3091</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>3002</v>
+        <v>3092</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>901</v>
@@ -28345,7 +29173,7 @@
         <v>52</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="43" spans="1:14">
@@ -28359,10 +29187,10 @@
         <v>914</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>3003</v>
+        <v>3093</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>3004</v>
+        <v>3094</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>921</v>
@@ -28389,7 +29217,7 @@
         <v>52</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="44" spans="1:14">
@@ -28403,10 +29231,10 @@
         <v>933</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>3005</v>
+        <v>3095</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>3006</v>
+        <v>3096</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>940</v>
@@ -28433,7 +29261,7 @@
         <v>52</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="45" spans="1:14">
@@ -28447,10 +29275,10 @@
         <v>953</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>3007</v>
+        <v>3097</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>3008</v>
+        <v>3098</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>959</v>
@@ -28477,7 +29305,7 @@
         <v>52</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="46" spans="1:14">
@@ -28491,10 +29319,10 @@
         <v>972</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>3009</v>
+        <v>3099</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>3010</v>
+        <v>3100</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>978</v>
@@ -28521,7 +29349,7 @@
         <v>52</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="47" spans="1:14">
@@ -28535,10 +29363,10 @@
         <v>990</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>3011</v>
+        <v>3101</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>3012</v>
+        <v>3102</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>997</v>
@@ -28565,7 +29393,7 @@
         <v>52</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="48" spans="1:14">
@@ -28579,10 +29407,10 @@
         <v>1010</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>3013</v>
+        <v>3103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>3014</v>
+        <v>3104</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>1018</v>
@@ -28609,7 +29437,7 @@
         <v>52</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="49" spans="1:14">
@@ -28623,10 +29451,10 @@
         <v>1030</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>3015</v>
+        <v>3105</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>3016</v>
+        <v>3106</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>1037</v>
@@ -28653,7 +29481,7 @@
         <v>52</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="50" spans="1:14">
@@ -28667,10 +29495,10 @@
         <v>1049</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>3017</v>
+        <v>3107</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>3018</v>
+        <v>3108</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>1055</v>
@@ -28697,7 +29525,7 @@
         <v>189</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="51" spans="1:14">
@@ -28711,10 +29539,10 @@
         <v>1067</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>3019</v>
+        <v>3109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>3020</v>
+        <v>3110</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>1072</v>
@@ -28741,7 +29569,7 @@
         <v>52</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="52" spans="1:14">
@@ -28755,10 +29583,10 @@
         <v>1084</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>3021</v>
+        <v>3111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>3022</v>
+        <v>3112</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>1091</v>
@@ -28785,7 +29613,7 @@
         <v>189</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="53" spans="1:14">
@@ -28799,10 +29627,10 @@
         <v>1104</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>3023</v>
+        <v>3113</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>3024</v>
+        <v>3114</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>1109</v>
@@ -28829,7 +29657,7 @@
         <v>145</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="54" spans="1:14">
@@ -28843,10 +29671,10 @@
         <v>1121</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>3025</v>
+        <v>3115</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>3026</v>
+        <v>3116</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>1131</v>
@@ -28873,7 +29701,7 @@
         <v>52</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="55" spans="1:14">
@@ -28887,10 +29715,10 @@
         <v>1144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>3027</v>
+        <v>3117</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>3028</v>
+        <v>3118</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>1151</v>
@@ -28917,7 +29745,7 @@
         <v>52</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="56" spans="1:14">
@@ -28931,10 +29759,10 @@
         <v>1165</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>3029</v>
+        <v>3119</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>3030</v>
+        <v>3120</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>1173</v>
@@ -28961,7 +29789,7 @@
         <v>52</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="57" spans="1:14">
@@ -28975,10 +29803,10 @@
         <v>1187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>3031</v>
+        <v>3121</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>3032</v>
+        <v>3122</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>1195</v>
@@ -29005,7 +29833,7 @@
         <v>189</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="58" spans="1:14">
@@ -29019,10 +29847,10 @@
         <v>1209</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>3033</v>
+        <v>3123</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>3034</v>
+        <v>3124</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>1217</v>
@@ -29049,7 +29877,7 @@
         <v>189</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="59" spans="1:14">
@@ -29063,10 +29891,10 @@
         <v>1231</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>3035</v>
+        <v>3125</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>3036</v>
+        <v>3126</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>1239</v>
@@ -29093,7 +29921,7 @@
         <v>189</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="60" spans="1:14">
@@ -29107,10 +29935,10 @@
         <v>1252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>3037</v>
+        <v>3127</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>1261</v>
@@ -29137,7 +29965,7 @@
         <v>52</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="61" spans="1:14">
@@ -29151,10 +29979,10 @@
         <v>1275</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>3039</v>
+        <v>3129</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>3040</v>
+        <v>3130</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>1283</v>
@@ -29181,7 +30009,7 @@
         <v>52</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="62" spans="1:14">
@@ -29195,10 +30023,10 @@
         <v>1297</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>3041</v>
+        <v>3131</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>3042</v>
+        <v>3132</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>1305</v>
@@ -29225,7 +30053,7 @@
         <v>145</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="63" spans="1:14">
@@ -29239,10 +30067,10 @@
         <v>1319</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>3043</v>
+        <v>3133</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>3044</v>
+        <v>3134</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>1327</v>
@@ -29269,7 +30097,7 @@
         <v>189</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="64" spans="1:14">
@@ -29283,10 +30111,10 @@
         <v>1341</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>3045</v>
+        <v>3135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>3046</v>
+        <v>3136</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>1348</v>
@@ -29313,7 +30141,7 @@
         <v>52</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="65" spans="1:14">
@@ -29327,10 +30155,10 @@
         <v>1361</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>3047</v>
+        <v>3137</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>3048</v>
+        <v>3138</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>1368</v>
@@ -29357,7 +30185,7 @@
         <v>52</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="66" spans="1:14">
@@ -29371,10 +30199,10 @@
         <v>1382</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>3049</v>
+        <v>3139</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>3050</v>
+        <v>3140</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>1389</v>
@@ -29401,7 +30229,7 @@
         <v>52</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="67" spans="1:14">
@@ -29415,10 +30243,10 @@
         <v>1403</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>3051</v>
+        <v>3141</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>3052</v>
+        <v>3142</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>1408</v>
@@ -29445,7 +30273,7 @@
         <v>52</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="68" spans="1:14">
@@ -29459,10 +30287,10 @@
         <v>1421</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>3053</v>
+        <v>3143</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>3054</v>
+        <v>3144</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>1428</v>
@@ -29489,7 +30317,7 @@
         <v>52</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="69" spans="1:14">
@@ -29503,10 +30331,10 @@
         <v>1442</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>3055</v>
+        <v>3145</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>3056</v>
+        <v>3146</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>1448</v>
@@ -29533,7 +30361,7 @@
         <v>52</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="70" spans="1:14">
@@ -29547,10 +30375,10 @@
         <v>1460</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>3057</v>
+        <v>3147</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>3058</v>
+        <v>3148</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>1466</v>
@@ -29577,7 +30405,7 @@
         <v>52</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="71" spans="1:14">
@@ -29591,10 +30419,10 @@
         <v>1480</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>3059</v>
+        <v>3149</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>3060</v>
+        <v>3150</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>1486</v>
@@ -29621,7 +30449,7 @@
         <v>52</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="72" spans="1:14">
@@ -29635,10 +30463,10 @@
         <v>1499</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>3061</v>
+        <v>3151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>3062</v>
+        <v>3152</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>1505</v>
@@ -29665,7 +30493,7 @@
         <v>52</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="73" spans="1:14">
@@ -29679,10 +30507,10 @@
         <v>1518</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>3063</v>
+        <v>3153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>3064</v>
+        <v>3154</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>1524</v>
@@ -29709,7 +30537,7 @@
         <v>145</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="74" spans="1:14">
@@ -29723,10 +30551,10 @@
         <v>1537</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>3065</v>
+        <v>3155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>3066</v>
+        <v>3156</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>1544</v>
@@ -29753,7 +30581,7 @@
         <v>52</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="75" spans="1:14">
@@ -29767,10 +30595,10 @@
         <v>1556</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>3067</v>
+        <v>3157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>3068</v>
+        <v>3158</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>1563</v>
@@ -29797,7 +30625,7 @@
         <v>52</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="76" spans="1:14">
@@ -29811,10 +30639,10 @@
         <v>1576</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>3069</v>
+        <v>3159</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>3070</v>
+        <v>3160</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>1583</v>
@@ -29841,7 +30669,7 @@
         <v>52</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="77" spans="1:14">
@@ -29855,10 +30683,10 @@
         <v>1596</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>3071</v>
+        <v>3161</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>3072</v>
+        <v>3162</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>1602</v>
@@ -29885,7 +30713,7 @@
         <v>52</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="78" spans="1:14">
@@ -29899,10 +30727,10 @@
         <v>1615</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>3073</v>
+        <v>3163</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>3074</v>
+        <v>3164</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>1621</v>
@@ -29929,7 +30757,7 @@
         <v>52</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="79" spans="1:14">
@@ -29943,10 +30771,10 @@
         <v>1634</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>3075</v>
+        <v>3165</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>3076</v>
+        <v>3166</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>1643</v>
@@ -29973,7 +30801,7 @@
         <v>145</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="80" spans="1:14">
@@ -29987,10 +30815,10 @@
         <v>1657</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>3077</v>
+        <v>3167</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>3078</v>
+        <v>3168</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>1665</v>
@@ -30017,7 +30845,7 @@
         <v>189</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="81" spans="1:14">
@@ -30031,10 +30859,10 @@
         <v>1678</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>3079</v>
+        <v>3169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>3080</v>
+        <v>3170</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>1686</v>
@@ -30061,7 +30889,7 @@
         <v>52</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="82" spans="1:14">
@@ -30075,10 +30903,10 @@
         <v>1700</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>3081</v>
+        <v>3171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>3082</v>
+        <v>3172</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>1708</v>
@@ -30105,7 +30933,7 @@
         <v>145</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="83" spans="1:14">
@@ -30119,10 +30947,10 @@
         <v>1721</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>3083</v>
+        <v>3173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>3084</v>
+        <v>3174</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>1730</v>
@@ -30149,7 +30977,7 @@
         <v>52</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="84" spans="1:14">
@@ -30163,10 +30991,10 @@
         <v>1744</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>3085</v>
+        <v>3175</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>3086</v>
+        <v>3176</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>1751</v>
@@ -30193,7 +31021,7 @@
         <v>52</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="85" spans="1:14">
@@ -30207,10 +31035,10 @@
         <v>1765</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>3087</v>
+        <v>3177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>3088</v>
+        <v>3178</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>1773</v>
@@ -30237,7 +31065,7 @@
         <v>145</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="86" spans="1:14">
@@ -30251,10 +31079,10 @@
         <v>1785</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>3089</v>
+        <v>3179</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>3090</v>
+        <v>3180</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>1793</v>
@@ -30281,7 +31109,7 @@
         <v>52</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="110.4" r="87" spans="1:14">
@@ -30295,10 +31123,10 @@
         <v>1806</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>3091</v>
+        <v>3181</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>3092</v>
+        <v>3182</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>1813</v>
@@ -30325,7 +31153,7 @@
         <v>145</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="88" spans="1:14">
@@ -30339,10 +31167,10 @@
         <v>1826</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>3093</v>
+        <v>3183</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>3094</v>
+        <v>3184</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>1834</v>
@@ -30369,7 +31197,7 @@
         <v>52</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="89" spans="1:14">
@@ -30383,10 +31211,10 @@
         <v>1846</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>3095</v>
+        <v>3185</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>3096</v>
+        <v>3186</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>1854</v>
@@ -30413,7 +31241,7 @@
         <v>52</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="90" spans="1:14">
@@ -30427,10 +31255,10 @@
         <v>1866</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>3097</v>
+        <v>3187</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>3098</v>
+        <v>3188</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>1873</v>
@@ -30457,7 +31285,7 @@
         <v>52</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="91" spans="1:14">
@@ -30471,10 +31299,10 @@
         <v>1884</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>3099</v>
+        <v>3189</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>3100</v>
+        <v>3190</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>1892</v>
@@ -30501,7 +31329,7 @@
         <v>145</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="92" spans="1:14">
@@ -30515,10 +31343,10 @@
         <v>1904</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>3101</v>
+        <v>3191</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>3102</v>
+        <v>3192</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>1912</v>
@@ -30545,7 +31373,7 @@
         <v>189</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="93" spans="1:14">
@@ -30559,10 +31387,10 @@
         <v>1923</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>3103</v>
+        <v>3193</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>3104</v>
+        <v>3194</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>1931</v>
@@ -30589,7 +31417,7 @@
         <v>52</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="94" spans="1:14">
@@ -30603,10 +31431,10 @@
         <v>1943</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>3105</v>
+        <v>3195</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>3106</v>
+        <v>3196</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>1950</v>
@@ -30633,7 +31461,7 @@
         <v>52</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="95" spans="1:14">
@@ -30647,10 +31475,10 @@
         <v>1961</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>3107</v>
+        <v>3197</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>3108</v>
+        <v>3198</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>1968</v>
@@ -30677,7 +31505,7 @@
         <v>52</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="96" spans="1:14">
@@ -30691,10 +31519,10 @@
         <v>1980</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>3109</v>
+        <v>3199</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>3110</v>
+        <v>3200</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>1988</v>
@@ -30721,7 +31549,7 @@
         <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="97" spans="1:14">
@@ -30735,10 +31563,10 @@
         <v>2000</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>3111</v>
+        <v>3201</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>3112</v>
+        <v>3202</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>2006</v>
@@ -30765,7 +31593,7 @@
         <v>52</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="98" spans="1:14">
@@ -30779,10 +31607,10 @@
         <v>2019</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>3113</v>
+        <v>3203</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>3114</v>
+        <v>3204</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>2028</v>
@@ -30809,7 +31637,7 @@
         <v>145</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="99" spans="1:14">
@@ -30823,10 +31651,10 @@
         <v>2041</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>3115</v>
+        <v>3205</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>3116</v>
+        <v>3206</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>2049</v>
@@ -30853,7 +31681,7 @@
         <v>145</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="100" spans="1:14">
@@ -30867,10 +31695,10 @@
         <v>2062</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>3117</v>
+        <v>3207</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>3118</v>
+        <v>3208</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>2069</v>
@@ -30897,7 +31725,7 @@
         <v>145</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="101" spans="1:14">
@@ -30911,10 +31739,10 @@
         <v>2082</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>3119</v>
+        <v>3209</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>3120</v>
+        <v>3210</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>2090</v>
@@ -30941,7 +31769,7 @@
         <v>52</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="102" spans="1:14">
@@ -30955,10 +31783,10 @@
         <v>2102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>3121</v>
+        <v>3211</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>3122</v>
+        <v>3212</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>2110</v>
@@ -30985,7 +31813,7 @@
         <v>145</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="103" spans="1:14">
@@ -30999,10 +31827,10 @@
         <v>2122</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>3123</v>
+        <v>3213</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>3124</v>
+        <v>3214</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>2129</v>
@@ -31029,7 +31857,7 @@
         <v>145</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="104" spans="1:14">
@@ -31043,10 +31871,10 @@
         <v>2142</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3125</v>
+        <v>3215</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>3126</v>
+        <v>3216</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>2149</v>
@@ -31073,7 +31901,7 @@
         <v>145</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="105" spans="1:14">
@@ -31087,10 +31915,10 @@
         <v>2161</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>3127</v>
+        <v>3217</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>3128</v>
+        <v>3218</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>2168</v>
@@ -31117,7 +31945,7 @@
         <v>145</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="106" spans="1:14">
@@ -31131,10 +31959,10 @@
         <v>2181</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>3129</v>
+        <v>3219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>3130</v>
+        <v>3220</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>2187</v>
@@ -31161,7 +31989,7 @@
         <v>189</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="107" spans="1:14">
@@ -31175,10 +32003,10 @@
         <v>2201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>3131</v>
+        <v>3221</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>3132</v>
+        <v>3222</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>2209</v>
@@ -31205,7 +32033,7 @@
         <v>145</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="108" spans="1:14">
@@ -31219,10 +32047,10 @@
         <v>2222</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>3133</v>
+        <v>3223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>3134</v>
+        <v>3224</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>2228</v>
@@ -31249,7 +32077,7 @@
         <v>52</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="109" spans="1:14">
@@ -31263,10 +32091,10 @@
         <v>2241</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>3135</v>
+        <v>3225</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>3136</v>
+        <v>3226</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>2247</v>
@@ -31293,7 +32121,7 @@
         <v>52</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="110" spans="1:14">
@@ -31307,10 +32135,10 @@
         <v>2259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>3137</v>
+        <v>3227</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>3138</v>
+        <v>3228</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>2268</v>
@@ -31337,7 +32165,7 @@
         <v>145</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="111" spans="1:14">
@@ -31351,10 +32179,10 @@
         <v>2281</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>3139</v>
+        <v>3229</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>3140</v>
+        <v>3230</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>2289</v>
@@ -31381,7 +32209,7 @@
         <v>52</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="112" spans="1:14">
@@ -31395,10 +32223,10 @@
         <v>2302</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>3141</v>
+        <v>3231</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>3142</v>
+        <v>3232</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>2311</v>
@@ -31425,7 +32253,7 @@
         <v>145</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="113" spans="1:14">
@@ -31439,10 +32267,10 @@
         <v>2324</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>3143</v>
+        <v>3233</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>3144</v>
+        <v>3234</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>2331</v>
@@ -31469,7 +32297,7 @@
         <v>145</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="114" spans="1:14">
@@ -31483,10 +32311,10 @@
         <v>2343</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>3145</v>
+        <v>3235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>3146</v>
+        <v>3236</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>2350</v>
@@ -31513,7 +32341,7 @@
         <v>145</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="115" spans="1:14">
@@ -31527,10 +32355,10 @@
         <v>2362</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>3147</v>
+        <v>3237</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>3148</v>
+        <v>3238</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>2369</v>
@@ -31557,7 +32385,7 @@
         <v>52</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="116" spans="1:14">
@@ -31571,10 +32399,10 @@
         <v>2381</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>3149</v>
+        <v>3239</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>3150</v>
+        <v>3240</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>2389</v>
@@ -31601,7 +32429,7 @@
         <v>145</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="117" spans="1:14">
@@ -31615,10 +32443,10 @@
         <v>2401</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>3151</v>
+        <v>3241</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>3152</v>
+        <v>3242</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>2410</v>
@@ -31645,7 +32473,7 @@
         <v>145</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="118" spans="1:14">
@@ -31659,10 +32487,10 @@
         <v>2423</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>3153</v>
+        <v>3243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>3154</v>
+        <v>3244</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>2431</v>
@@ -31689,7 +32517,7 @@
         <v>145</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="96.59999999999999" r="119" spans="1:14">
@@ -31703,10 +32531,10 @@
         <v>2443</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>3155</v>
+        <v>3245</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>3156</v>
+        <v>3246</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>2450</v>
@@ -31733,7 +32561,7 @@
         <v>52</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>2922</v>
+        <v>3012</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="120" spans="1:14">
@@ -31747,10 +32575,10 @@
         <v>2462</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>3157</v>
+        <v>3247</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>3158</v>
+        <v>3248</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>2470</v>
@@ -31777,7 +32605,7 @@
         <v>145</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="121" spans="1:14">
@@ -31791,10 +32619,10 @@
         <v>2483</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>3160</v>
+        <v>3250</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>3161</v>
+        <v>3251</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>2492</v>
@@ -31821,7 +32649,7 @@
         <v>145</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="122" spans="1:14">
@@ -31835,10 +32663,10 @@
         <v>2503</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>3162</v>
+        <v>3252</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>3163</v>
+        <v>3253</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>2508</v>
@@ -31865,7 +32693,7 @@
         <v>52</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -31879,10 +32707,10 @@
         <v>2521</v>
       </c>
       <c r="D123" t="s">
-        <v>3164</v>
+        <v>3254</v>
       </c>
       <c r="E123" t="s">
-        <v>3165</v>
+        <v>3255</v>
       </c>
       <c r="F123" t="s">
         <v>2528</v>
@@ -31909,7 +32737,7 @@
         <v>52</v>
       </c>
       <c r="N123" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -31926,7 +32754,7 @@
         <v>2546</v>
       </c>
       <c r="E124" t="s">
-        <v>3166</v>
+        <v>3256</v>
       </c>
       <c r="F124" t="s">
         <v>2547</v>
@@ -31953,7 +32781,7 @@
         <v>52</v>
       </c>
       <c r="N124" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -31970,7 +32798,7 @@
         <v>2564</v>
       </c>
       <c r="E125" t="s">
-        <v>3167</v>
+        <v>3257</v>
       </c>
       <c r="F125" t="s">
         <v>2565</v>
@@ -31997,7 +32825,7 @@
         <v>189</v>
       </c>
       <c r="N125" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -32014,7 +32842,7 @@
         <v>2582</v>
       </c>
       <c r="E126" t="s">
-        <v>3168</v>
+        <v>3258</v>
       </c>
       <c r="F126" t="s">
         <v>2585</v>
@@ -32038,10 +32866,10 @@
         <v>2590</v>
       </c>
       <c r="M126" t="s">
-        <v>3169</v>
+        <v>3259</v>
       </c>
       <c r="N126" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -32058,7 +32886,7 @@
         <v>2601</v>
       </c>
       <c r="E127" t="s">
-        <v>3170</v>
+        <v>3260</v>
       </c>
       <c r="F127" t="s">
         <v>2603</v>
@@ -32085,7 +32913,7 @@
         <v>52</v>
       </c>
       <c r="N127" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -32099,10 +32927,10 @@
         <v>2614</v>
       </c>
       <c r="D128" t="s">
-        <v>3171</v>
+        <v>3261</v>
       </c>
       <c r="E128" t="s">
-        <v>3172</v>
+        <v>3262</v>
       </c>
       <c r="F128" t="s">
         <v>2620</v>
@@ -32126,10 +32954,10 @@
         <v>2626</v>
       </c>
       <c r="M128" t="s">
-        <v>3169</v>
+        <v>3259</v>
       </c>
       <c r="N128" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -32143,10 +32971,10 @@
         <v>2632</v>
       </c>
       <c r="D129" t="s">
-        <v>3173</v>
+        <v>3263</v>
       </c>
       <c r="E129" t="s">
-        <v>3174</v>
+        <v>3264</v>
       </c>
       <c r="F129" t="s">
         <v>2638</v>
@@ -32173,7 +33001,7 @@
         <v>52</v>
       </c>
       <c r="N129" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -32187,10 +33015,10 @@
         <v>2650</v>
       </c>
       <c r="D130" t="s">
-        <v>3175</v>
+        <v>3265</v>
       </c>
       <c r="E130" t="s">
-        <v>3176</v>
+        <v>3266</v>
       </c>
       <c r="F130" t="s">
         <v>2657</v>
@@ -32217,7 +33045,7 @@
         <v>52</v>
       </c>
       <c r="N130" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -32234,7 +33062,7 @@
         <v>2673</v>
       </c>
       <c r="E131" t="s">
-        <v>3177</v>
+        <v>3267</v>
       </c>
       <c r="F131" t="s">
         <v>2675</v>
@@ -32261,7 +33089,7 @@
         <v>52</v>
       </c>
       <c r="N131" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -32275,10 +33103,10 @@
         <v>2687</v>
       </c>
       <c r="D132" t="s">
-        <v>3178</v>
+        <v>3268</v>
       </c>
       <c r="E132" t="s">
-        <v>3179</v>
+        <v>3269</v>
       </c>
       <c r="F132" t="s">
         <v>2694</v>
@@ -32305,7 +33133,7 @@
         <v>52</v>
       </c>
       <c r="N132" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -32319,10 +33147,10 @@
         <v>2705</v>
       </c>
       <c r="D133" t="s">
-        <v>3180</v>
+        <v>3270</v>
       </c>
       <c r="E133" t="s">
-        <v>3181</v>
+        <v>3271</v>
       </c>
       <c r="F133" t="s">
         <v>2711</v>
@@ -32349,7 +33177,7 @@
         <v>52</v>
       </c>
       <c r="N133" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -32363,10 +33191,10 @@
         <v>2722</v>
       </c>
       <c r="D134" t="s">
-        <v>3182</v>
+        <v>3272</v>
       </c>
       <c r="E134" t="s">
-        <v>3183</v>
+        <v>3273</v>
       </c>
       <c r="F134" t="s">
         <v>2730</v>
@@ -32393,7 +33221,7 @@
         <v>52</v>
       </c>
       <c r="N134" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -32407,10 +33235,10 @@
         <v>2744</v>
       </c>
       <c r="D135" t="s">
-        <v>3184</v>
+        <v>3274</v>
       </c>
       <c r="E135" t="s">
-        <v>3185</v>
+        <v>3275</v>
       </c>
       <c r="F135" t="s">
         <v>2753</v>
@@ -32437,7 +33265,7 @@
         <v>52</v>
       </c>
       <c r="N135" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -32451,10 +33279,10 @@
         <v>2765</v>
       </c>
       <c r="D136" t="s">
-        <v>3186</v>
+        <v>3276</v>
       </c>
       <c r="E136" t="s">
-        <v>3187</v>
+        <v>3277</v>
       </c>
       <c r="F136" t="s">
         <v>2774</v>
@@ -32469,7 +33297,7 @@
         <v>2777</v>
       </c>
       <c r="J136" t="s">
-        <v>3188</v>
+        <v>3278</v>
       </c>
       <c r="K136" t="s">
         <v>2779</v>
@@ -32481,7 +33309,7 @@
         <v>52</v>
       </c>
       <c r="N136" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -32495,10 +33323,10 @@
         <v>2788</v>
       </c>
       <c r="D137" t="s">
-        <v>3189</v>
+        <v>3279</v>
       </c>
       <c r="E137" t="s">
-        <v>3190</v>
+        <v>3280</v>
       </c>
       <c r="F137" t="s">
         <v>2795</v>
@@ -32513,7 +33341,7 @@
         <v>2798</v>
       </c>
       <c r="J137" t="s">
-        <v>3191</v>
+        <v>3281</v>
       </c>
       <c r="K137" t="s">
         <v>2800</v>
@@ -32525,7 +33353,7 @@
         <v>52</v>
       </c>
       <c r="N137" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -32536,13 +33364,13 @@
         <v>31</v>
       </c>
       <c r="C138" t="s">
-        <v>3192</v>
+        <v>3282</v>
       </c>
       <c r="D138" t="s">
-        <v>3193</v>
+        <v>3283</v>
       </c>
       <c r="E138" t="s">
-        <v>3194</v>
+        <v>3284</v>
       </c>
       <c r="F138" t="s">
         <v>2815</v>
@@ -32557,7 +33385,7 @@
         <v>2818</v>
       </c>
       <c r="J138" t="s">
-        <v>3195</v>
+        <v>3285</v>
       </c>
       <c r="K138" t="s">
         <v>2820</v>
@@ -32569,7 +33397,7 @@
         <v>52</v>
       </c>
       <c r="N138" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -32583,10 +33411,10 @@
         <v>2828</v>
       </c>
       <c r="D139" t="s">
-        <v>3196</v>
+        <v>3286</v>
       </c>
       <c r="E139" t="s">
-        <v>3197</v>
+        <v>3287</v>
       </c>
       <c r="F139" t="s">
         <v>2835</v>
@@ -32601,7 +33429,7 @@
         <v>2838</v>
       </c>
       <c r="J139" t="s">
-        <v>3198</v>
+        <v>3288</v>
       </c>
       <c r="K139" t="s">
         <v>2840</v>
@@ -32613,7 +33441,7 @@
         <v>52</v>
       </c>
       <c r="N139" t="s">
-        <v>3159</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -32627,10 +33455,10 @@
         <v>2848</v>
       </c>
       <c r="D140" t="s">
-        <v>3199</v>
+        <v>3289</v>
       </c>
       <c r="E140" t="s">
-        <v>3200</v>
+        <v>3290</v>
       </c>
       <c r="F140" t="s">
         <v>2856</v>
@@ -32645,7 +33473,7 @@
         <v>2859</v>
       </c>
       <c r="J140" t="s">
-        <v>3201</v>
+        <v>3291</v>
       </c>
       <c r="K140" t="s">
         <v>2861</v>
@@ -32657,7 +33485,227 @@
         <v>52</v>
       </c>
       <c r="N140" t="s">
-        <v>3159</v>
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
+      <c r="A141" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B141" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" t="s">
+        <v>3292</v>
+      </c>
+      <c r="D141" t="s">
+        <v>3293</v>
+      </c>
+      <c r="E141" t="s">
+        <v>3294</v>
+      </c>
+      <c r="F141" t="s">
+        <v>2874</v>
+      </c>
+      <c r="G141" t="s">
+        <v>2875</v>
+      </c>
+      <c r="H141" t="s">
+        <v>2876</v>
+      </c>
+      <c r="I141" t="s">
+        <v>2877</v>
+      </c>
+      <c r="J141" t="s">
+        <v>2878</v>
+      </c>
+      <c r="K141" t="s">
+        <v>2879</v>
+      </c>
+      <c r="L141" t="s">
+        <v>2880</v>
+      </c>
+      <c r="M141" t="s">
+        <v>52</v>
+      </c>
+      <c r="N141" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
+      <c r="A142" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B142" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" t="s">
+        <v>3295</v>
+      </c>
+      <c r="D142" t="s">
+        <v>3296</v>
+      </c>
+      <c r="E142" t="s">
+        <v>3297</v>
+      </c>
+      <c r="F142" t="s">
+        <v>2892</v>
+      </c>
+      <c r="G142" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H142" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I142" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J142" t="s">
+        <v>2896</v>
+      </c>
+      <c r="K142" t="s">
+        <v>2897</v>
+      </c>
+      <c r="L142" t="s">
+        <v>2898</v>
+      </c>
+      <c r="M142" t="s">
+        <v>3298</v>
+      </c>
+      <c r="N142" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
+      <c r="A143" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B143" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" t="s">
+        <v>3299</v>
+      </c>
+      <c r="D143" t="s">
+        <v>3300</v>
+      </c>
+      <c r="E143" t="s">
+        <v>3301</v>
+      </c>
+      <c r="F143" t="s">
+        <v>2909</v>
+      </c>
+      <c r="G143" t="s">
+        <v>2910</v>
+      </c>
+      <c r="H143" t="s">
+        <v>2911</v>
+      </c>
+      <c r="I143" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J143" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K143" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L143" t="s">
+        <v>2915</v>
+      </c>
+      <c r="M143" t="s">
+        <v>52</v>
+      </c>
+      <c r="N143" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
+      <c r="A144" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B144" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D144" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E144" t="s">
+        <v>3304</v>
+      </c>
+      <c r="F144" t="s">
+        <v>2926</v>
+      </c>
+      <c r="G144" t="s">
+        <v>2927</v>
+      </c>
+      <c r="H144" t="s">
+        <v>2928</v>
+      </c>
+      <c r="I144" t="s">
+        <v>2929</v>
+      </c>
+      <c r="J144" t="s">
+        <v>2930</v>
+      </c>
+      <c r="K144" t="s">
+        <v>2931</v>
+      </c>
+      <c r="L144" t="s">
+        <v>2932</v>
+      </c>
+      <c r="M144" t="s">
+        <v>52</v>
+      </c>
+      <c r="N144" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
+      <c r="A145" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B145" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" t="s">
+        <v>3305</v>
+      </c>
+      <c r="D145" t="s">
+        <v>3306</v>
+      </c>
+      <c r="E145" t="s">
+        <v>3307</v>
+      </c>
+      <c r="F145" t="s">
+        <v>2942</v>
+      </c>
+      <c r="G145" t="s">
+        <v>2943</v>
+      </c>
+      <c r="H145" t="s">
+        <v>2944</v>
+      </c>
+      <c r="I145" t="s">
+        <v>2945</v>
+      </c>
+      <c r="J145" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K145" t="s">
+        <v>2947</v>
+      </c>
+      <c r="L145" t="s">
+        <v>2948</v>
+      </c>
+      <c r="M145" t="s">
+        <v>52</v>
+      </c>
+      <c r="N145" t="s">
+        <v>3249</v>
       </c>
     </row>
   </sheetData>
@@ -32671,7 +33719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="50"/>
@@ -32680,122 +33728,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>3202</v>
+        <v>3308</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>3203</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3204</v>
+        <v>3310</v>
       </c>
       <c r="B2" t="s">
-        <v>2874</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3205</v>
+        <v>3311</v>
       </c>
       <c r="B3" t="s">
-        <v>3206</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3207</v>
+        <v>3313</v>
       </c>
       <c r="B4" t="s">
-        <v>3208</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3209</v>
+        <v>3315</v>
       </c>
       <c r="B5" t="s">
-        <v>3210</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3211</v>
+        <v>3317</v>
       </c>
       <c r="B6" t="s">
-        <v>3212</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3213</v>
+        <v>3319</v>
       </c>
       <c r="B7" t="s">
-        <v>3214</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3215</v>
+        <v>3321</v>
       </c>
       <c r="B8" t="s">
-        <v>3216</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3217</v>
+        <v>3323</v>
       </c>
       <c r="B9" t="s">
-        <v>3218</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3219</v>
+        <v>3325</v>
       </c>
       <c r="B10" t="s">
-        <v>3220</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3221</v>
+        <v>3327</v>
       </c>
       <c r="B11" t="s">
-        <v>3222</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3223</v>
+        <v>3329</v>
       </c>
       <c r="B12" t="s">
-        <v>3224</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3225</v>
+        <v>3331</v>
       </c>
       <c r="B13" t="s">
-        <v>3226</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3227</v>
+        <v>3333</v>
       </c>
       <c r="B14" t="s">
-        <v>3228</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>3229</v>
+        <v>3335</v>
       </c>
       <c r="B15" t="s">
-        <v>3230</v>
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>3337</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3338</v>
       </c>
     </row>
   </sheetData>
@@ -32809,87 +33865,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <sheetData>
     <row customHeight="1" ht="27.6" r="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>3231</v>
+        <v>3339</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3232</v>
+        <v>3340</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>3233</v>
+        <v>3341</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3234</v>
+        <v>3342</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3235</v>
+        <v>3343</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>3236</v>
+        <v>3344</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3237</v>
+        <v>3345</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3238</v>
+        <v>3346</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3239</v>
+        <v>3347</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3240</v>
+        <v>3348</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3241</v>
+        <v>3349</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1681</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3238</v>
+        <v>3346</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3239</v>
+        <v>3347</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1674</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3240</v>
+        <v>3348</v>
       </c>
     </row>
     <row customHeight="1" ht="55.2" r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3242</v>
+        <v>3350</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3238</v>
+        <v>3346</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3239</v>
+        <v>3347</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>1161</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3240</v>
+        <v>3348</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="5" spans="1:6">
@@ -32900,16 +33956,16 @@
         <v>2204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="6" spans="1:6">
@@ -32920,16 +33976,16 @@
         <v>2223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="7" spans="1:6">
@@ -32940,16 +33996,16 @@
         <v>2243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="8" spans="1:6">
@@ -32960,16 +34016,16 @@
         <v>2262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="9" spans="1:6">
@@ -32980,16 +34036,16 @@
         <v>2283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="10" spans="1:6">
@@ -33000,16 +34056,16 @@
         <v>2305</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="11" spans="1:6">
@@ -33020,16 +34076,16 @@
         <v>2326</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="12" spans="1:6">
@@ -33040,16 +34096,16 @@
         <v>2346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="13" spans="1:6">
@@ -33060,16 +34116,16 @@
         <v>2364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="14" spans="1:6">
@@ -33080,16 +34136,16 @@
         <v>2383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="15" spans="1:6">
@@ -33100,16 +34156,16 @@
         <v>2404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="16" spans="1:6">
@@ -33120,16 +34176,16 @@
         <v>2425</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="82.8" r="17" spans="1:6">
@@ -33140,96 +34196,116 @@
         <v>2445</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>3244</v>
+        <v>3352</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3245</v>
+        <v>3353</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3246</v>
+        <v>3354</v>
       </c>
     </row>
     <row customHeight="1" ht="303.6" r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>3247</v>
+        <v>3355</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3248</v>
+        <v>3356</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3238</v>
+        <v>3346</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>3249</v>
+        <v>3357</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>610</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3250</v>
+        <v>3358</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>3251</v>
+        <v>3359</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3252</v>
+        <v>3360</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3253</v>
+        <v>3361</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3254</v>
+        <v>3362</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>2458</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
     </row>
     <row customHeight="1" ht="193.2" r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>3255</v>
+        <v>3363</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3256</v>
+        <v>3364</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3253</v>
+        <v>3361</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3254</v>
+        <v>3362</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>2479</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
       </c>
     </row>
     <row customHeight="1" ht="276" r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>3257</v>
+        <v>3365</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3258</v>
+        <v>3366</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3253</v>
+        <v>3361</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>3254</v>
+        <v>3362</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>3243</v>
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3367</v>
+      </c>
+      <c r="D22" t="s">
+        <v>3368</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F22" t="s">
+        <v>3369</v>
       </c>
     </row>
   </sheetData>
@@ -33243,7 +34319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="2" min="1" width="42"/>
@@ -33251,15 +34327,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>3259</v>
+        <v>3370</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3260</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3261</v>
+        <v>3372</v>
       </c>
       <c r="B2" t="n">
         <v>118</v>
@@ -33267,7 +34343,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3262</v>
+        <v>3373</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -33275,7 +34351,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3263</v>
+        <v>3374</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -33283,7 +34359,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3264</v>
+        <v>3375</v>
       </c>
       <c r="B5" t="s">
         <v>2440</v>
@@ -33291,82 +34367,90 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3265</v>
+        <v>3376</v>
       </c>
       <c r="B6" t="s">
-        <v>3266</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>3267</v>
+        <v>3378</v>
       </c>
       <c r="B7" t="s">
-        <v>3268</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>3269</v>
+        <v>3380</v>
       </c>
       <c r="B8" t="s">
-        <v>3270</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>3271</v>
+        <v>3382</v>
       </c>
       <c r="B9" t="s">
-        <v>3272</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3219</v>
+        <v>3325</v>
       </c>
       <c r="B10" t="s">
-        <v>3220</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3273</v>
+        <v>3384</v>
       </c>
       <c r="B11" t="s">
-        <v>3268</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3274</v>
+        <v>3385</v>
       </c>
       <c r="B12" t="s">
-        <v>3275</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3276</v>
+        <v>3387</v>
       </c>
       <c r="B13" t="s">
-        <v>3277</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3278</v>
+        <v>3389</v>
       </c>
       <c r="B14" t="s">
-        <v>3279</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>3280</v>
+        <v>3391</v>
       </c>
       <c r="B15" t="s">
-        <v>3275</v>
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>3392</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3393</v>
       </c>
     </row>
   </sheetData>
